--- a/SAKHALIN_11201_11202.xlsx
+++ b/SAKHALIN_11201_11202.xlsx
@@ -42,7 +42,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -52,6 +52,21 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00305496"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8CBAD"/>
       </patternFill>
     </fill>
   </fills>
@@ -81,7 +96,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -104,7 +119,16 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1305,10 +1329,20 @@
       <c r="G2" s="5" t="n">
         <v>17280</v>
       </c>
-      <c r="H2" s="5" t="n"/>
-      <c r="I2" s="5" t="n"/>
-      <c r="J2" s="8" t="n"/>
-      <c r="K2" s="4" t="inlineStr"/>
+      <c r="H2" s="5" t="n">
+        <v>1354.93</v>
+      </c>
+      <c r="I2" s="5" t="n">
+        <v>13549.3</v>
+      </c>
+      <c r="J2" s="8" t="n">
+        <v>0.2158969907407408</v>
+      </c>
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>Камчатка verify (dn.ru, LD КШ.Ц.П.015.040.Н/П.02 ст20 Ру40), цена dn.ru на 02.11.2026</t>
+        </is>
+      </c>
       <c r="L2" s="4" t="inlineStr"/>
     </row>
     <row r="3" ht="36" customHeight="1">
@@ -1339,10 +1373,20 @@
       <c r="G3" s="5" t="n">
         <v>32340.06</v>
       </c>
-      <c r="H3" s="5" t="n"/>
-      <c r="I3" s="5" t="n"/>
-      <c r="J3" s="8" t="n"/>
-      <c r="K3" s="4" t="inlineStr"/>
+      <c r="H3" s="5" t="n">
+        <v>1452.11</v>
+      </c>
+      <c r="I3" s="5" t="n">
+        <v>26137.98</v>
+      </c>
+      <c r="J3" s="8" t="n">
+        <v>0.1917770096901491</v>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>dn.ru, LD КШ.Ц.П.020.040.Н/П.02 ст20 Ру40, цена на 02.11.2026</t>
+        </is>
+      </c>
       <c r="L3" s="4" t="inlineStr"/>
     </row>
     <row r="4" ht="36" customHeight="1">
@@ -1373,10 +1417,20 @@
       <c r="G4" s="5" t="n">
         <v>32999.94</v>
       </c>
-      <c r="H4" s="5" t="n"/>
-      <c r="I4" s="5" t="n"/>
-      <c r="J4" s="8" t="n"/>
-      <c r="K4" s="4" t="inlineStr"/>
+      <c r="H4" s="5" t="n">
+        <v>1480.5</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>26649</v>
+      </c>
+      <c r="J4" s="8" t="n">
+        <v>0.192453077187413</v>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>Камчатка verify (dn.ru, LD КШЦП ст20 Ду25)</t>
+        </is>
+      </c>
       <c r="L4" s="4" t="inlineStr"/>
     </row>
     <row r="5" ht="36" customHeight="1">
@@ -1407,10 +1461,20 @@
       <c r="G5" s="5" t="n">
         <v>88000</v>
       </c>
-      <c r="H5" s="5" t="n"/>
-      <c r="I5" s="5" t="n"/>
-      <c r="J5" s="8" t="n"/>
-      <c r="K5" s="4" t="inlineStr"/>
+      <c r="H5" s="5" t="n">
+        <v>2178</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>54450</v>
+      </c>
+      <c r="J5" s="9" t="n">
+        <v>0.38125</v>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>Камчатка verify (dn.ru, LD КШЦП ст20 Ду50)</t>
+        </is>
+      </c>
       <c r="L5" s="4" t="inlineStr"/>
     </row>
     <row r="6" ht="36" customHeight="1">
@@ -1441,10 +1505,20 @@
       <c r="G6" s="5" t="n">
         <v>47600</v>
       </c>
-      <c r="H6" s="5" t="n"/>
-      <c r="I6" s="5" t="n"/>
-      <c r="J6" s="8" t="n"/>
-      <c r="K6" s="4" t="inlineStr"/>
+      <c r="H6" s="5" t="n">
+        <v>832.83</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>33313.2</v>
+      </c>
+      <c r="J6" s="9" t="n">
+        <v>0.3001428571428572</v>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>dn.ru, фланец плоский Россия Ду100 Ру6 ст20 тип 01 исп.B ГОСТ 33259-2015, на 02.11.2026</t>
+        </is>
+      </c>
       <c r="L6" s="4" t="inlineStr"/>
     </row>
     <row r="7" ht="36" customHeight="1">
@@ -1475,11 +1549,25 @@
       <c r="G7" s="5" t="n">
         <v>8200</v>
       </c>
-      <c r="H7" s="5" t="n"/>
-      <c r="I7" s="5" t="n"/>
-      <c r="J7" s="8" t="n"/>
-      <c r="K7" s="4" t="inlineStr"/>
-      <c r="L7" s="4" t="inlineStr"/>
+      <c r="H7" s="5" t="n">
+        <v>241.56</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>4831.2</v>
+      </c>
+      <c r="J7" s="9" t="n">
+        <v>0.410829268292683</v>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>dn.ru, LD Pride 47.15.В-В.Б 1/2" (бабочка), на 21.10.2026</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>LD Pride 47.15.В-В.Б (ООО «ЛД», Челябинск) вместо VALTEC VT.122.GN.04 (Италия/КНР)</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="36" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
@@ -1511,7 +1599,7 @@
       </c>
       <c r="H8" s="5" t="n"/>
       <c r="I8" s="5" t="n"/>
-      <c r="J8" s="8" t="n"/>
+      <c r="J8" s="10" t="n"/>
       <c r="K8" s="4" t="inlineStr"/>
       <c r="L8" s="4" t="inlineStr"/>
     </row>
@@ -1543,10 +1631,20 @@
       <c r="G9" s="5" t="n">
         <v>93846.62</v>
       </c>
-      <c r="H9" s="5" t="n"/>
-      <c r="I9" s="5" t="n"/>
-      <c r="J9" s="8" t="n"/>
-      <c r="K9" s="4" t="inlineStr"/>
+      <c r="H9" s="5" t="n">
+        <v>5903.13</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>82643.82000000001</v>
+      </c>
+      <c r="J9" s="8" t="n">
+        <v>0.1193735054070141</v>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>Камчатка verify: прайс АДЛ BD01I12791 ЗПВС-FL(W)-3-080-MN-E = 55,03 у.е. × 119,19 (EUR ЦБ+5%, с НДС 22%)</t>
+        </is>
+      </c>
       <c r="L9" s="4" t="inlineStr"/>
     </row>
     <row r="10" ht="36" customHeight="1">
@@ -1577,10 +1675,20 @@
       <c r="G10" s="5" t="n">
         <v>151153.31</v>
       </c>
-      <c r="H10" s="5" t="n"/>
-      <c r="I10" s="5" t="n"/>
-      <c r="J10" s="8" t="n"/>
-      <c r="K10" s="4" t="inlineStr"/>
+      <c r="H10" s="5" t="n">
+        <v>16529.4</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>115705.8</v>
+      </c>
+      <c r="J10" s="8" t="n">
+        <v>0.2345136206411887</v>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>БК-Арматура, прайс «30с41нж литые клиновые PN16» DN150, с НДС, ©2026</t>
+        </is>
+      </c>
       <c r="L10" s="4" t="inlineStr"/>
     </row>
     <row r="11" ht="36" customHeight="1">
@@ -1611,10 +1719,20 @@
       <c r="G11" s="5" t="n">
         <v>32800</v>
       </c>
-      <c r="H11" s="5" t="n"/>
-      <c r="I11" s="5" t="n"/>
-      <c r="J11" s="8" t="n"/>
-      <c r="K11" s="4" t="inlineStr"/>
+      <c r="H11" s="5" t="n">
+        <v>2415.6</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>24156</v>
+      </c>
+      <c r="J11" s="9" t="n">
+        <v>0.2635365853658537</v>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>dn.ru, фланец КЗТШ Ду200 Ру16 ст20 тип 01 исп.B, на 18.02.2027(дата цены сайта)</t>
+        </is>
+      </c>
       <c r="L11" s="4" t="inlineStr"/>
     </row>
     <row r="12" ht="36" customHeight="1">
@@ -1647,7 +1765,7 @@
       </c>
       <c r="H12" s="5" t="n"/>
       <c r="I12" s="5" t="n"/>
-      <c r="J12" s="8" t="n"/>
+      <c r="J12" s="10" t="n"/>
       <c r="K12" s="4" t="inlineStr"/>
       <c r="L12" s="4" t="inlineStr"/>
     </row>
@@ -1681,7 +1799,7 @@
       </c>
       <c r="H13" s="5" t="n"/>
       <c r="I13" s="5" t="n"/>
-      <c r="J13" s="8" t="n"/>
+      <c r="J13" s="10" t="n"/>
       <c r="K13" s="4" t="inlineStr"/>
       <c r="L13" s="4" t="inlineStr"/>
     </row>
@@ -1715,7 +1833,7 @@
       </c>
       <c r="H14" s="5" t="n"/>
       <c r="I14" s="5" t="n"/>
-      <c r="J14" s="8" t="n"/>
+      <c r="J14" s="10" t="n"/>
       <c r="K14" s="4" t="inlineStr"/>
       <c r="L14" s="4" t="inlineStr"/>
     </row>
@@ -1749,7 +1867,7 @@
       </c>
       <c r="H15" s="5" t="n"/>
       <c r="I15" s="5" t="n"/>
-      <c r="J15" s="8" t="n"/>
+      <c r="J15" s="10" t="n"/>
       <c r="K15" s="4" t="inlineStr"/>
       <c r="L15" s="4" t="inlineStr"/>
     </row>
@@ -1781,10 +1899,20 @@
       <c r="G16" s="5" t="n">
         <v>136360</v>
       </c>
-      <c r="H16" s="5" t="n"/>
-      <c r="I16" s="5" t="n"/>
-      <c r="J16" s="8" t="n"/>
-      <c r="K16" s="4" t="inlineStr"/>
+      <c r="H16" s="5" t="n">
+        <v>27762.38</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>111049.52</v>
+      </c>
+      <c r="J16" s="8" t="n">
+        <v>0.1856151364036374</v>
+      </c>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>dn.ru, Benarmo обратный шаровой Ду150 Ру16 чугун/сталь NBR, на 30.10.2026</t>
+        </is>
+      </c>
       <c r="L16" s="4" t="inlineStr"/>
     </row>
     <row r="17" ht="36" customHeight="1">
@@ -1815,10 +1943,20 @@
       <c r="G17" s="5" t="n">
         <v>138133.36</v>
       </c>
-      <c r="H17" s="5" t="n"/>
-      <c r="I17" s="5" t="n"/>
-      <c r="J17" s="8" t="n"/>
-      <c r="K17" s="4" t="inlineStr"/>
+      <c r="H17" s="5" t="n">
+        <v>13974.25</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>111794</v>
+      </c>
+      <c r="J17" s="8" t="n">
+        <v>0.190680658169757</v>
+      </c>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>dn.ru, Benarmo обратный шаровой Ду100 Ру16, на 30.10.2026</t>
+        </is>
+      </c>
       <c r="L17" s="4" t="inlineStr"/>
     </row>
     <row r="18" ht="36" customHeight="1">
@@ -1849,10 +1987,20 @@
       <c r="G18" s="5" t="n">
         <v>98986.64</v>
       </c>
-      <c r="H18" s="5" t="n"/>
-      <c r="I18" s="5" t="n"/>
-      <c r="J18" s="8" t="n"/>
-      <c r="K18" s="4" t="inlineStr"/>
+      <c r="H18" s="5" t="n">
+        <v>10299.24</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>82393.92</v>
+      </c>
+      <c r="J18" s="8" t="n">
+        <v>0.167625853347482</v>
+      </c>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>dn.ru, Benarmo обратный шаровой Ду80 Ру16, на 30.10.2026</t>
+        </is>
+      </c>
       <c r="L18" s="4" t="inlineStr"/>
     </row>
     <row r="19" ht="36" customHeight="1">
@@ -1883,11 +2031,25 @@
       <c r="G19" s="5" t="n">
         <v>15546.68</v>
       </c>
-      <c r="H19" s="5" t="n"/>
-      <c r="I19" s="5" t="n"/>
-      <c r="J19" s="8" t="n"/>
-      <c r="K19" s="4" t="inlineStr"/>
-      <c r="L19" s="4" t="inlineStr"/>
+      <c r="H19" s="5" t="n">
+        <v>2664.9</v>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>10659.6</v>
+      </c>
+      <c r="J19" s="9" t="n">
+        <v>0.3143487870079014</v>
+      </c>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>БК-Арматура, 30ч39р SL14 DN80 (Семёновский ЛМЗ), с НДС</t>
+        </is>
+      </c>
+      <c r="L19" s="4" t="inlineStr">
+        <is>
+          <t>30ч39р ЛМЗ SL14 (обрезиненный клин) вместо МЗВ</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="36" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
@@ -1917,10 +2079,20 @@
       <c r="G20" s="5" t="n">
         <v>46600</v>
       </c>
-      <c r="H20" s="5" t="n"/>
-      <c r="I20" s="5" t="n"/>
-      <c r="J20" s="8" t="n"/>
-      <c r="K20" s="4" t="inlineStr"/>
+      <c r="H20" s="5" t="n">
+        <v>14941.8</v>
+      </c>
+      <c r="I20" s="5" t="n">
+        <v>149418</v>
+      </c>
+      <c r="J20" s="11" t="n">
+        <v>-2.206394849785408</v>
+      </c>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>СИБЗТА прайс 12.01.2026: затвор 32ч1р Ду150 Ру16 ручной, диск нерж</t>
+        </is>
+      </c>
       <c r="L20" s="4" t="inlineStr"/>
     </row>
     <row r="21" ht="36" customHeight="1">
@@ -1951,10 +2123,20 @@
       <c r="G21" s="5" t="n">
         <v>11466.68</v>
       </c>
-      <c r="H21" s="5" t="n"/>
-      <c r="I21" s="5" t="n"/>
-      <c r="J21" s="8" t="n"/>
-      <c r="K21" s="4" t="inlineStr"/>
+      <c r="H21" s="5" t="n">
+        <v>8806.5</v>
+      </c>
+      <c r="I21" s="5" t="n">
+        <v>35226</v>
+      </c>
+      <c r="J21" s="11" t="n">
+        <v>-2.072031311591498</v>
+      </c>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>СИБЗТА прайс: затвор 32ч1р Ду100 Ру16, диск нерж</t>
+        </is>
+      </c>
       <c r="L21" s="4" t="inlineStr"/>
     </row>
     <row r="22" ht="36" customHeight="1">
@@ -1987,7 +2169,7 @@
       </c>
       <c r="H22" s="5" t="n"/>
       <c r="I22" s="5" t="n"/>
-      <c r="J22" s="8" t="n"/>
+      <c r="J22" s="10" t="n"/>
       <c r="K22" s="4" t="inlineStr"/>
       <c r="L22" s="4" t="inlineStr"/>
     </row>
@@ -2021,7 +2203,7 @@
       </c>
       <c r="H23" s="5" t="n"/>
       <c r="I23" s="5" t="n"/>
-      <c r="J23" s="8" t="n"/>
+      <c r="J23" s="10" t="n"/>
       <c r="K23" s="4" t="inlineStr"/>
       <c r="L23" s="4" t="inlineStr"/>
     </row>
@@ -2053,10 +2235,20 @@
       <c r="G24" s="5" t="n">
         <v>231333.32</v>
       </c>
-      <c r="H24" s="5" t="n"/>
-      <c r="I24" s="5" t="n"/>
-      <c r="J24" s="8" t="n"/>
-      <c r="K24" s="4" t="inlineStr"/>
+      <c r="H24" s="5" t="n">
+        <v>34300.97</v>
+      </c>
+      <c r="I24" s="5" t="n">
+        <v>137203.88</v>
+      </c>
+      <c r="J24" s="9" t="n">
+        <v>0.4068996199942144</v>
+      </c>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>dn.ru, 30ч906бр ЛАЗ Ду200 Ру10 под электропривод, на 26.10.2026</t>
+        </is>
+      </c>
       <c r="L24" s="4" t="inlineStr"/>
     </row>
     <row r="25" ht="36" customHeight="1">
@@ -2087,10 +2279,20 @@
       <c r="G25" s="5" t="n">
         <v>3866.7</v>
       </c>
-      <c r="H25" s="5" t="n"/>
-      <c r="I25" s="5" t="n"/>
-      <c r="J25" s="8" t="n"/>
-      <c r="K25" s="4" t="inlineStr"/>
+      <c r="H25" s="5" t="n">
+        <v>305.24</v>
+      </c>
+      <c r="I25" s="5" t="n">
+        <v>3052.4</v>
+      </c>
+      <c r="J25" s="8" t="n">
+        <v>0.2105930121292058</v>
+      </c>
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>dn.ru, фланец плоский Россия Ду32 Ру10 ст20 тип 01 исп.B, на 02.11.2026</t>
+        </is>
+      </c>
       <c r="L25" s="4" t="inlineStr"/>
     </row>
     <row r="26" ht="36" customHeight="1">
@@ -2121,10 +2323,20 @@
       <c r="G26" s="5" t="n">
         <v>7800</v>
       </c>
-      <c r="H26" s="5" t="n"/>
-      <c r="I26" s="5" t="n"/>
-      <c r="J26" s="8" t="n"/>
-      <c r="K26" s="4" t="inlineStr"/>
+      <c r="H26" s="5" t="n">
+        <v>417.79</v>
+      </c>
+      <c r="I26" s="5" t="n">
+        <v>4177.900000000001</v>
+      </c>
+      <c r="J26" s="9" t="n">
+        <v>0.4643717948717948</v>
+      </c>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>dn.ru, фланец КЗТШ Ду50 Ру10 ст20 тип 01 исп.B</t>
+        </is>
+      </c>
       <c r="L26" s="4" t="inlineStr"/>
     </row>
     <row r="27" ht="36" customHeight="1">
@@ -2155,10 +2367,20 @@
       <c r="G27" s="5" t="n">
         <v>28200</v>
       </c>
-      <c r="H27" s="5" t="n"/>
-      <c r="I27" s="5" t="n"/>
-      <c r="J27" s="8" t="n"/>
-      <c r="K27" s="4" t="inlineStr"/>
+      <c r="H27" s="5" t="n">
+        <v>645.62</v>
+      </c>
+      <c r="I27" s="5" t="n">
+        <v>19368.6</v>
+      </c>
+      <c r="J27" s="9" t="n">
+        <v>0.3131702127659575</v>
+      </c>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>dn.ru, фланец КЗТШ Ду80 Ру10</t>
+        </is>
+      </c>
       <c r="L27" s="4" t="inlineStr"/>
     </row>
     <row r="28" ht="36" customHeight="1">
@@ -2189,10 +2411,20 @@
       <c r="G28" s="5" t="n">
         <v>44653.22</v>
       </c>
-      <c r="H28" s="5" t="n"/>
-      <c r="I28" s="5" t="n"/>
-      <c r="J28" s="8" t="n"/>
-      <c r="K28" s="4" t="inlineStr"/>
+      <c r="H28" s="5" t="n">
+        <v>999.1799999999999</v>
+      </c>
+      <c r="I28" s="5" t="n">
+        <v>33972.12</v>
+      </c>
+      <c r="J28" s="8" t="n">
+        <v>0.2392011147236415</v>
+      </c>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>dn.ru, фланец КЗТШ Ду100 Ру10</t>
+        </is>
+      </c>
       <c r="L28" s="4" t="inlineStr"/>
     </row>
     <row r="29" ht="36" customHeight="1">
@@ -2223,10 +2455,20 @@
       <c r="G29" s="5" t="n">
         <v>19600</v>
       </c>
-      <c r="H29" s="5" t="n"/>
-      <c r="I29" s="5" t="n"/>
-      <c r="J29" s="8" t="n"/>
-      <c r="K29" s="4" t="inlineStr"/>
+      <c r="H29" s="5" t="n">
+        <v>1526.77</v>
+      </c>
+      <c r="I29" s="5" t="n">
+        <v>15267.7</v>
+      </c>
+      <c r="J29" s="8" t="n">
+        <v>0.2210357142857143</v>
+      </c>
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>dn.ru, фланец КЗТШ Ду150 Ру10</t>
+        </is>
+      </c>
       <c r="L29" s="4" t="inlineStr"/>
     </row>
     <row r="30" ht="36" customHeight="1">
@@ -2259,7 +2501,7 @@
       </c>
       <c r="H30" s="5" t="n"/>
       <c r="I30" s="5" t="n"/>
-      <c r="J30" s="8" t="n"/>
+      <c r="J30" s="10" t="n"/>
       <c r="K30" s="4" t="inlineStr"/>
       <c r="L30" s="4" t="inlineStr"/>
     </row>
@@ -2293,7 +2535,7 @@
       </c>
       <c r="H31" s="5" t="n"/>
       <c r="I31" s="5" t="n"/>
-      <c r="J31" s="8" t="n"/>
+      <c r="J31" s="10" t="n"/>
       <c r="K31" s="4" t="inlineStr"/>
       <c r="L31" s="4" t="inlineStr"/>
     </row>
@@ -2327,7 +2569,7 @@
       </c>
       <c r="H32" s="5" t="n"/>
       <c r="I32" s="5" t="n"/>
-      <c r="J32" s="8" t="n"/>
+      <c r="J32" s="10" t="n"/>
       <c r="K32" s="4" t="inlineStr"/>
       <c r="L32" s="4" t="inlineStr"/>
     </row>
@@ -2361,7 +2603,7 @@
       </c>
       <c r="H33" s="5" t="n"/>
       <c r="I33" s="5" t="n"/>
-      <c r="J33" s="8" t="n"/>
+      <c r="J33" s="10" t="n"/>
       <c r="K33" s="4" t="inlineStr"/>
       <c r="L33" s="4" t="inlineStr"/>
     </row>
@@ -2395,7 +2637,7 @@
       </c>
       <c r="H34" s="5" t="n"/>
       <c r="I34" s="5" t="n"/>
-      <c r="J34" s="8" t="n"/>
+      <c r="J34" s="10" t="n"/>
       <c r="K34" s="4" t="inlineStr"/>
       <c r="L34" s="4" t="inlineStr"/>
     </row>
@@ -2427,10 +2669,20 @@
       <c r="G35" s="5" t="n">
         <v>33700</v>
       </c>
-      <c r="H35" s="5" t="n"/>
-      <c r="I35" s="5" t="n"/>
-      <c r="J35" s="8" t="n"/>
-      <c r="K35" s="4" t="inlineStr"/>
+      <c r="H35" s="5" t="n">
+        <v>3788.1</v>
+      </c>
+      <c r="I35" s="5" t="n">
+        <v>18940.5</v>
+      </c>
+      <c r="J35" s="9" t="n">
+        <v>0.4379673590504451</v>
+      </c>
+      <c r="K35" s="4" t="inlineStr">
+        <is>
+          <t>КП Лидер-Энерго № 2022 от 26.10.2026: ЗПД-80-УХЛ1, с НДС (база Камчатки)</t>
+        </is>
+      </c>
       <c r="L35" s="4" t="inlineStr"/>
     </row>
     <row r="36" ht="36" customHeight="1">
@@ -2461,10 +2713,20 @@
       <c r="G36" s="5" t="n">
         <v>20220</v>
       </c>
-      <c r="H36" s="5" t="n"/>
-      <c r="I36" s="5" t="n"/>
-      <c r="J36" s="8" t="n"/>
-      <c r="K36" s="4" t="inlineStr"/>
+      <c r="H36" s="5" t="n">
+        <v>3788.1</v>
+      </c>
+      <c r="I36" s="5" t="n">
+        <v>11364.3</v>
+      </c>
+      <c r="J36" s="9" t="n">
+        <v>0.4379673590504451</v>
+      </c>
+      <c r="K36" s="4" t="inlineStr">
+        <is>
+          <t>КП Лидер-Энерго № 2022 от 26.10.2026: ЗПД-80-УХЛ1, с НДС (база Камчатки)</t>
+        </is>
+      </c>
       <c r="L36" s="4" t="inlineStr"/>
     </row>
     <row r="37" ht="36" customHeight="1">
@@ -2495,11 +2757,25 @@
       <c r="G37" s="5" t="n">
         <v>16933.36</v>
       </c>
-      <c r="H37" s="5" t="n"/>
-      <c r="I37" s="5" t="n"/>
-      <c r="J37" s="8" t="n"/>
-      <c r="K37" s="4" t="inlineStr"/>
-      <c r="L37" s="4" t="inlineStr"/>
+      <c r="H37" s="5" t="n">
+        <v>2417.4</v>
+      </c>
+      <c r="I37" s="5" t="n">
+        <v>19339.2</v>
+      </c>
+      <c r="J37" s="11" t="n">
+        <v>-0.1420769416111156</v>
+      </c>
+      <c r="K37" s="4" t="inlineStr">
+        <is>
+          <t>СИБЗТА прайс: клапан обратный двухстворчатый Ду100 Ру16</t>
+        </is>
+      </c>
+      <c r="L37" s="4" t="inlineStr">
+        <is>
+          <t>двухстворчатый межфланцевый СИБЗТА вместо RMCX</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="36" customHeight="1">
       <c r="A38" s="4" t="inlineStr">
@@ -2531,7 +2807,7 @@
       </c>
       <c r="H38" s="5" t="n"/>
       <c r="I38" s="5" t="n"/>
-      <c r="J38" s="8" t="n"/>
+      <c r="J38" s="10" t="n"/>
       <c r="K38" s="4" t="inlineStr"/>
       <c r="L38" s="4" t="inlineStr"/>
     </row>
@@ -2565,7 +2841,7 @@
       </c>
       <c r="H39" s="5" t="n"/>
       <c r="I39" s="5" t="n"/>
-      <c r="J39" s="8" t="n"/>
+      <c r="J39" s="10" t="n"/>
       <c r="K39" s="4" t="inlineStr"/>
       <c r="L39" s="4" t="inlineStr"/>
     </row>
@@ -2599,7 +2875,7 @@
       </c>
       <c r="H40" s="5" t="n"/>
       <c r="I40" s="5" t="n"/>
-      <c r="J40" s="8" t="n"/>
+      <c r="J40" s="10" t="n"/>
       <c r="K40" s="4" t="inlineStr"/>
       <c r="L40" s="4" t="inlineStr"/>
     </row>
@@ -2631,10 +2907,20 @@
       <c r="G41" s="5" t="n">
         <v>3450</v>
       </c>
-      <c r="H41" s="5" t="n"/>
-      <c r="I41" s="5" t="n"/>
-      <c r="J41" s="8" t="n"/>
-      <c r="K41" s="4" t="inlineStr"/>
+      <c r="H41" s="5" t="n">
+        <v>1541.7</v>
+      </c>
+      <c r="I41" s="5" t="n">
+        <v>4625.1</v>
+      </c>
+      <c r="J41" s="11" t="n">
+        <v>-0.3406086956521739</v>
+      </c>
+      <c r="K41" s="4" t="inlineStr">
+        <is>
+          <t>СИБЗТА прайс: затвор 32ч1р Ду80 Ру16 ручной, диск чугун</t>
+        </is>
+      </c>
       <c r="L41" s="4" t="inlineStr"/>
     </row>
     <row r="42" ht="36" customHeight="1">
@@ -2665,10 +2951,20 @@
       <c r="G42" s="5" t="n">
         <v>12400.02</v>
       </c>
-      <c r="H42" s="5" t="n"/>
-      <c r="I42" s="5" t="n"/>
-      <c r="J42" s="8" t="n"/>
-      <c r="K42" s="4" t="inlineStr"/>
+      <c r="H42" s="5" t="n">
+        <v>1959.3</v>
+      </c>
+      <c r="I42" s="5" t="n">
+        <v>11755.8</v>
+      </c>
+      <c r="J42" s="8" t="n">
+        <v>0.05195314201106138</v>
+      </c>
+      <c r="K42" s="4" t="inlineStr">
+        <is>
+          <t>СИБЗТА прайс: затвор 32ч1р Ду100 Ру16 ручной, диск чугун</t>
+        </is>
+      </c>
       <c r="L42" s="4" t="inlineStr"/>
     </row>
     <row r="43" ht="36" customHeight="1">
@@ -2699,11 +2995,25 @@
       <c r="G43" s="5" t="n">
         <v>63050</v>
       </c>
-      <c r="H43" s="5" t="n"/>
-      <c r="I43" s="5" t="n"/>
-      <c r="J43" s="8" t="n"/>
-      <c r="K43" s="4" t="inlineStr"/>
-      <c r="L43" s="4" t="inlineStr"/>
+      <c r="H43" s="5" t="n">
+        <v>8780.129999999999</v>
+      </c>
+      <c r="I43" s="5" t="n">
+        <v>43900.64999999999</v>
+      </c>
+      <c r="J43" s="9" t="n">
+        <v>0.3037168913560667</v>
+      </c>
+      <c r="K43" s="4" t="inlineStr">
+        <is>
+          <t>прайс АДЛ BD01A30812 ЗПВЛ-FLN(W)-5-050-MN-E = 81,85 у.е. × 119,19</t>
+        </is>
+      </c>
+      <c r="L43" s="4" t="inlineStr">
+        <is>
+          <t>Гранвэл ЗПВЛ (АДЛ, РФ; диск CF8M, EPDM) вместо Ebro Z011-A (Германия)</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="36" customHeight="1">
       <c r="A44" s="4" t="inlineStr">
@@ -2733,11 +3043,25 @@
       <c r="G44" s="5" t="n">
         <v>74450</v>
       </c>
-      <c r="H44" s="5" t="n"/>
-      <c r="I44" s="5" t="n"/>
-      <c r="J44" s="8" t="n"/>
-      <c r="K44" s="4" t="inlineStr"/>
-      <c r="L44" s="4" t="inlineStr"/>
+      <c r="H44" s="5" t="n">
+        <v>9185.620000000001</v>
+      </c>
+      <c r="I44" s="5" t="n">
+        <v>45928.10000000001</v>
+      </c>
+      <c r="J44" s="9" t="n">
+        <v>0.3831014103425117</v>
+      </c>
+      <c r="K44" s="4" t="inlineStr">
+        <is>
+          <t>прайс АДЛ BD01A12813 ЗПВЛ-FLN(W)-5-065-MN-E = 85,63 у.е. × 119,19</t>
+        </is>
+      </c>
+      <c r="L44" s="4" t="inlineStr">
+        <is>
+          <t>Гранвэл ЗПВЛ Ду65 вместо Ebro Z011-A</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="36" customHeight="1">
       <c r="A45" s="4" t="inlineStr">
@@ -2769,7 +3093,7 @@
       </c>
       <c r="H45" s="5" t="n"/>
       <c r="I45" s="5" t="n"/>
-      <c r="J45" s="8" t="n"/>
+      <c r="J45" s="10" t="n"/>
       <c r="K45" s="4" t="inlineStr"/>
       <c r="L45" s="4" t="inlineStr"/>
     </row>
@@ -2803,7 +3127,7 @@
       </c>
       <c r="H46" s="5" t="n"/>
       <c r="I46" s="5" t="n"/>
-      <c r="J46" s="8" t="n"/>
+      <c r="J46" s="10" t="n"/>
       <c r="K46" s="4" t="inlineStr"/>
       <c r="L46" s="4" t="inlineStr"/>
     </row>
@@ -2837,7 +3161,7 @@
       </c>
       <c r="H47" s="5" t="n"/>
       <c r="I47" s="5" t="n"/>
-      <c r="J47" s="8" t="n"/>
+      <c r="J47" s="10" t="n"/>
       <c r="K47" s="4" t="inlineStr"/>
       <c r="L47" s="4" t="inlineStr"/>
     </row>
@@ -2871,7 +3195,7 @@
       </c>
       <c r="H48" s="5" t="n"/>
       <c r="I48" s="5" t="n"/>
-      <c r="J48" s="8" t="n"/>
+      <c r="J48" s="10" t="n"/>
       <c r="K48" s="4" t="inlineStr"/>
       <c r="L48" s="4" t="inlineStr"/>
     </row>
@@ -2905,7 +3229,7 @@
       </c>
       <c r="H49" s="5" t="n"/>
       <c r="I49" s="5" t="n"/>
-      <c r="J49" s="8" t="n"/>
+      <c r="J49" s="10" t="n"/>
       <c r="K49" s="4" t="inlineStr"/>
       <c r="L49" s="4" t="inlineStr"/>
     </row>
@@ -2937,10 +3261,20 @@
       <c r="G50" s="5" t="n">
         <v>19980</v>
       </c>
-      <c r="H50" s="5" t="n"/>
-      <c r="I50" s="5" t="n"/>
-      <c r="J50" s="8" t="n"/>
-      <c r="K50" s="4" t="inlineStr"/>
+      <c r="H50" s="5" t="n">
+        <v>6516.9</v>
+      </c>
+      <c r="I50" s="5" t="n">
+        <v>13033.8</v>
+      </c>
+      <c r="J50" s="9" t="n">
+        <v>0.3476576576576577</v>
+      </c>
+      <c r="K50" s="4" t="inlineStr">
+        <is>
+          <t>СИБЗТА прайс: затвор 32ч1р Ду200 Ру16, диск чугун (ТЗ допускает «диск — чугун»)</t>
+        </is>
+      </c>
       <c r="L50" s="4" t="inlineStr"/>
     </row>
     <row r="51" ht="36" customHeight="1">
@@ -2971,10 +3305,20 @@
       <c r="G51" s="5" t="n">
         <v>34080</v>
       </c>
-      <c r="H51" s="5" t="n"/>
-      <c r="I51" s="5" t="n"/>
-      <c r="J51" s="8" t="n"/>
-      <c r="K51" s="4" t="inlineStr"/>
+      <c r="H51" s="5" t="n">
+        <v>1541.7</v>
+      </c>
+      <c r="I51" s="5" t="n">
+        <v>18500.4</v>
+      </c>
+      <c r="J51" s="9" t="n">
+        <v>0.4571478873239436</v>
+      </c>
+      <c r="K51" s="4" t="inlineStr">
+        <is>
+          <t>СИБЗТА прайс: затвор 32ч1р Ду80 Ру16, диск чугун (вариант ТЗ «32ч901р диск-чугун»)</t>
+        </is>
+      </c>
       <c r="L51" s="4" t="inlineStr"/>
     </row>
     <row r="52" ht="36" customHeight="1">
@@ -3005,10 +3349,20 @@
       <c r="G52" s="5" t="n">
         <v>27600</v>
       </c>
-      <c r="H52" s="5" t="n"/>
-      <c r="I52" s="5" t="n"/>
-      <c r="J52" s="8" t="n"/>
-      <c r="K52" s="4" t="inlineStr"/>
+      <c r="H52" s="5" t="n">
+        <v>1959.3</v>
+      </c>
+      <c r="I52" s="5" t="n">
+        <v>15674.4</v>
+      </c>
+      <c r="J52" s="9" t="n">
+        <v>0.4320869565217391</v>
+      </c>
+      <c r="K52" s="4" t="inlineStr">
+        <is>
+          <t>СИБЗТА прайс: затвор 32ч1р Ду100 Ру16, диск чугун</t>
+        </is>
+      </c>
       <c r="L52" s="4" t="inlineStr"/>
     </row>
     <row r="53" ht="36" customHeight="1">
@@ -3039,10 +3393,20 @@
       <c r="G53" s="5" t="n">
         <v>60120</v>
       </c>
-      <c r="H53" s="5" t="n"/>
-      <c r="I53" s="5" t="n"/>
-      <c r="J53" s="8" t="n"/>
-      <c r="K53" s="4" t="inlineStr"/>
+      <c r="H53" s="5" t="n">
+        <v>5363.55</v>
+      </c>
+      <c r="I53" s="5" t="n">
+        <v>64362.60000000001</v>
+      </c>
+      <c r="J53" s="11" t="n">
+        <v>-0.07056886227544923</v>
+      </c>
+      <c r="K53" s="4" t="inlineStr">
+        <is>
+          <t>Камчатка verify: прайс АДЛ BD01I12790 ЗПВС-FL(W)-3-065-MN-E = 50 у.е. × 119,19</t>
+        </is>
+      </c>
       <c r="L53" s="4" t="inlineStr"/>
     </row>
     <row r="54" ht="36" customHeight="1">
@@ -3075,7 +3439,7 @@
       </c>
       <c r="H54" s="5" t="n"/>
       <c r="I54" s="5" t="n"/>
-      <c r="J54" s="8" t="n"/>
+      <c r="J54" s="10" t="n"/>
       <c r="K54" s="4" t="inlineStr"/>
       <c r="L54" s="4" t="inlineStr"/>
     </row>
@@ -3109,7 +3473,7 @@
       </c>
       <c r="H55" s="5" t="n"/>
       <c r="I55" s="5" t="n"/>
-      <c r="J55" s="8" t="n"/>
+      <c r="J55" s="10" t="n"/>
       <c r="K55" s="4" t="inlineStr"/>
       <c r="L55" s="4" t="inlineStr"/>
     </row>
@@ -3143,7 +3507,7 @@
       </c>
       <c r="H56" s="5" t="n"/>
       <c r="I56" s="5" t="n"/>
-      <c r="J56" s="8" t="n"/>
+      <c r="J56" s="10" t="n"/>
       <c r="K56" s="4" t="inlineStr"/>
       <c r="L56" s="4" t="inlineStr"/>
     </row>
@@ -3177,7 +3541,7 @@
       </c>
       <c r="H57" s="5" t="n"/>
       <c r="I57" s="5" t="n"/>
-      <c r="J57" s="8" t="n"/>
+      <c r="J57" s="10" t="n"/>
       <c r="K57" s="4" t="inlineStr"/>
       <c r="L57" s="4" t="inlineStr"/>
     </row>
@@ -3209,10 +3573,20 @@
       <c r="G58" s="5" t="n">
         <v>313080</v>
       </c>
-      <c r="H58" s="5" t="n"/>
-      <c r="I58" s="5" t="n"/>
-      <c r="J58" s="8" t="n"/>
-      <c r="K58" s="4" t="inlineStr"/>
+      <c r="H58" s="5" t="n">
+        <v>96054.14</v>
+      </c>
+      <c r="I58" s="5" t="n">
+        <v>288162.42</v>
+      </c>
+      <c r="J58" s="8" t="n">
+        <v>0.07958853967037183</v>
+      </c>
+      <c r="K58" s="4" t="inlineStr">
+        <is>
+          <t>dn.ru, ЧАЗ 19с76нж Ду200 Ру25, на 19.11.2026 + КОФ</t>
+        </is>
+      </c>
       <c r="L58" s="4" t="inlineStr"/>
     </row>
     <row r="59" ht="36" customHeight="1">
@@ -3243,10 +3617,20 @@
       <c r="G59" s="5" t="n">
         <v>57440</v>
       </c>
-      <c r="H59" s="5" t="n"/>
-      <c r="I59" s="5" t="n"/>
-      <c r="J59" s="8" t="n"/>
-      <c r="K59" s="4" t="inlineStr"/>
+      <c r="H59" s="5" t="n">
+        <v>18168.3</v>
+      </c>
+      <c r="I59" s="5" t="n">
+        <v>36336.6</v>
+      </c>
+      <c r="J59" s="9" t="n">
+        <v>0.367399025069638</v>
+      </c>
+      <c r="K59" s="4" t="inlineStr">
+        <is>
+          <t>БК-Арматура: 30с41нж DN125 PN16 + КОФ</t>
+        </is>
+      </c>
       <c r="L59" s="4" t="inlineStr"/>
     </row>
     <row r="60" ht="36" customHeight="1">
@@ -3277,10 +3661,20 @@
       <c r="G60" s="5" t="n">
         <v>388680</v>
       </c>
-      <c r="H60" s="5" t="n"/>
-      <c r="I60" s="5" t="n"/>
-      <c r="J60" s="8" t="n"/>
-      <c r="K60" s="4" t="inlineStr"/>
+      <c r="H60" s="5" t="n">
+        <v>357141.52</v>
+      </c>
+      <c r="I60" s="5" t="n">
+        <v>357141.52</v>
+      </c>
+      <c r="J60" s="8" t="n">
+        <v>0.08114253370381797</v>
+      </c>
+      <c r="K60" s="4" t="inlineStr">
+        <is>
+          <t>dn.ru, Авангард Крр 25с947нж Ду200 Ру25 Kvs630, без привода, на 28.10.2026 + КОФ</t>
+        </is>
+      </c>
       <c r="L60" s="4" t="inlineStr"/>
     </row>
     <row r="61" ht="36" customHeight="1">
@@ -3311,10 +3705,20 @@
       <c r="G61" s="5" t="n">
         <v>36550</v>
       </c>
-      <c r="H61" s="5" t="n"/>
-      <c r="I61" s="5" t="n"/>
-      <c r="J61" s="8" t="n"/>
-      <c r="K61" s="4" t="inlineStr"/>
+      <c r="H61" s="5" t="n">
+        <v>37418.4</v>
+      </c>
+      <c r="I61" s="5" t="n">
+        <v>37418.4</v>
+      </c>
+      <c r="J61" s="11" t="n">
+        <v>-0.02375923392612855</v>
+      </c>
+      <c r="K61" s="4" t="inlineStr">
+        <is>
+          <t>БК-Арматура: 30с64нж DN200 PN25 (ТЕХГИДРОМАШ), с НДС</t>
+        </is>
+      </c>
       <c r="L61" s="4" t="inlineStr"/>
     </row>
     <row r="62" ht="36" customHeight="1">
@@ -3345,10 +3749,20 @@
       <c r="G62" s="5" t="n">
         <v>133440</v>
       </c>
-      <c r="H62" s="5" t="n"/>
-      <c r="I62" s="5" t="n"/>
-      <c r="J62" s="8" t="n"/>
-      <c r="K62" s="4" t="inlineStr"/>
+      <c r="H62" s="5" t="n">
+        <v>60113.7</v>
+      </c>
+      <c r="I62" s="5" t="n">
+        <v>60113.7</v>
+      </c>
+      <c r="J62" s="9" t="n">
+        <v>0.549507643884892</v>
+      </c>
+      <c r="K62" s="4" t="inlineStr">
+        <is>
+          <t>БК-Арматура: 30с964нж DN200 под эл/п Б, с НДС</t>
+        </is>
+      </c>
       <c r="L62" s="4" t="inlineStr"/>
     </row>
     <row r="63" ht="36" customHeight="1">
@@ -3379,11 +3793,25 @@
       <c r="G63" s="5" t="n">
         <v>90990</v>
       </c>
-      <c r="H63" s="5" t="n"/>
-      <c r="I63" s="5" t="n"/>
-      <c r="J63" s="8" t="n"/>
-      <c r="K63" s="4" t="inlineStr"/>
-      <c r="L63" s="4" t="inlineStr"/>
+      <c r="H63" s="5" t="n">
+        <v>8738.98</v>
+      </c>
+      <c r="I63" s="5" t="n">
+        <v>26216.94</v>
+      </c>
+      <c r="J63" s="9" t="n">
+        <v>0.7118700956149028</v>
+      </c>
+      <c r="K63" s="4" t="inlineStr">
+        <is>
+          <t>dn.ru, АСТА ЭСК 201 1/2" Ду15 НО пилотный 230В, на 02.11.2026</t>
+        </is>
+      </c>
+      <c r="L63" s="4" t="inlineStr">
+        <is>
+          <t>АСТА ЭСК 201 НО (РФ) вместо Danfoss EV220A 042U4064 (импорт)</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="36" customHeight="1">
       <c r="A64" s="4" t="inlineStr">
@@ -3415,7 +3843,7 @@
       </c>
       <c r="H64" s="5" t="n"/>
       <c r="I64" s="5" t="n"/>
-      <c r="J64" s="8" t="n"/>
+      <c r="J64" s="10" t="n"/>
       <c r="K64" s="4" t="inlineStr"/>
       <c r="L64" s="4" t="inlineStr"/>
     </row>
@@ -3449,7 +3877,7 @@
       </c>
       <c r="H65" s="5" t="n"/>
       <c r="I65" s="5" t="n"/>
-      <c r="J65" s="8" t="n"/>
+      <c r="J65" s="10" t="n"/>
       <c r="K65" s="4" t="inlineStr"/>
       <c r="L65" s="4" t="inlineStr"/>
     </row>
@@ -3483,7 +3911,7 @@
       </c>
       <c r="H66" s="5" t="n"/>
       <c r="I66" s="5" t="n"/>
-      <c r="J66" s="8" t="n"/>
+      <c r="J66" s="10" t="n"/>
       <c r="K66" s="4" t="inlineStr"/>
       <c r="L66" s="4" t="inlineStr"/>
     </row>
@@ -3517,7 +3945,7 @@
       </c>
       <c r="H67" s="5" t="n"/>
       <c r="I67" s="5" t="n"/>
-      <c r="J67" s="8" t="n"/>
+      <c r="J67" s="10" t="n"/>
       <c r="K67" s="4" t="inlineStr"/>
       <c r="L67" s="4" t="inlineStr"/>
     </row>
@@ -3551,7 +3979,7 @@
       </c>
       <c r="H68" s="5" t="n"/>
       <c r="I68" s="5" t="n"/>
-      <c r="J68" s="8" t="n"/>
+      <c r="J68" s="10" t="n"/>
       <c r="K68" s="4" t="inlineStr"/>
       <c r="L68" s="4" t="inlineStr"/>
     </row>
@@ -3583,10 +4011,20 @@
       <c r="G69" s="5" t="n">
         <v>225066.6</v>
       </c>
-      <c r="H69" s="5" t="n"/>
-      <c r="I69" s="5" t="n"/>
-      <c r="J69" s="8" t="n"/>
-      <c r="K69" s="4" t="inlineStr"/>
+      <c r="H69" s="5" t="n">
+        <v>97373.7</v>
+      </c>
+      <c r="I69" s="5" t="n">
+        <v>194747.4</v>
+      </c>
+      <c r="J69" s="8" t="n">
+        <v>0.1347121252109376</v>
+      </c>
+      <c r="K69" s="4" t="inlineStr">
+        <is>
+          <t>Камчатка verify / СИБЗТА прайс 12.01.2026: 30нж41нж Ду150 Ру16</t>
+        </is>
+      </c>
       <c r="L69" s="4" t="inlineStr"/>
     </row>
     <row r="70" ht="36" customHeight="1">
@@ -3617,10 +4055,20 @@
       <c r="G70" s="5" t="n">
         <v>13953.33</v>
       </c>
-      <c r="H70" s="5" t="n"/>
-      <c r="I70" s="5" t="n"/>
-      <c r="J70" s="8" t="n"/>
-      <c r="K70" s="4" t="inlineStr"/>
+      <c r="H70" s="5" t="n">
+        <v>14910.67</v>
+      </c>
+      <c r="I70" s="5" t="n">
+        <v>14910.67</v>
+      </c>
+      <c r="J70" s="11" t="n">
+        <v>-0.06861014539181687</v>
+      </c>
+      <c r="K70" s="4" t="inlineStr">
+        <is>
+          <t>прайс АДЛ BD01I27246 ЗПВС-FL(W)-3-100-MDV-E = 139 у.е. × 119,19</t>
+        </is>
+      </c>
       <c r="L70" s="4" t="inlineStr"/>
     </row>
     <row r="71" ht="36" customHeight="1">
@@ -3651,10 +4099,20 @@
       <c r="G71" s="5" t="n">
         <v>2119320</v>
       </c>
-      <c r="H71" s="5" t="n"/>
-      <c r="I71" s="5" t="n"/>
-      <c r="J71" s="8" t="n"/>
-      <c r="K71" s="4" t="inlineStr"/>
+      <c r="H71" s="5" t="n">
+        <v>79030.8</v>
+      </c>
+      <c r="I71" s="5" t="n">
+        <v>1422554.4</v>
+      </c>
+      <c r="J71" s="9" t="n">
+        <v>0.3287684729064039</v>
+      </c>
+      <c r="K71" s="4" t="inlineStr">
+        <is>
+          <t>БК-Арматура: 30с964нж DN50 под эл/п А (16 301) + электропривод ГЗ-А.70/24 (71 511), с НДС</t>
+        </is>
+      </c>
       <c r="L71" s="4" t="inlineStr"/>
     </row>
     <row r="72" ht="36" customHeight="1">
@@ -3685,10 +4143,20 @@
       <c r="G72" s="5" t="n">
         <v>174666.65</v>
       </c>
-      <c r="H72" s="5" t="n"/>
-      <c r="I72" s="5" t="n"/>
-      <c r="J72" s="8" t="n"/>
-      <c r="K72" s="4" t="inlineStr"/>
+      <c r="H72" s="5" t="n">
+        <v>34305.88</v>
+      </c>
+      <c r="I72" s="5" t="n">
+        <v>171529.4</v>
+      </c>
+      <c r="J72" s="11" t="n">
+        <v>0.01796135667570209</v>
+      </c>
+      <c r="K72" s="4" t="inlineStr">
+        <is>
+          <t>БК-Арматура: 30с64нж DN150 PN25 (ТЕХГИДРОМАШ) + КОФ</t>
+        </is>
+      </c>
       <c r="L72" s="4" t="inlineStr"/>
     </row>
     <row r="73" ht="36" customHeight="1">
@@ -3719,10 +4187,20 @@
       <c r="G73" s="5" t="n">
         <v>121209.99</v>
       </c>
-      <c r="H73" s="5" t="n"/>
-      <c r="I73" s="5" t="n"/>
-      <c r="J73" s="8" t="n"/>
-      <c r="K73" s="4" t="inlineStr"/>
+      <c r="H73" s="5" t="n">
+        <v>37418.4</v>
+      </c>
+      <c r="I73" s="5" t="n">
+        <v>112255.2</v>
+      </c>
+      <c r="J73" s="8" t="n">
+        <v>0.07387831646549925</v>
+      </c>
+      <c r="K73" s="4" t="inlineStr">
+        <is>
+          <t>БК-Арматура: 30с64нж DN200 PN25 (ТЕХГИДРОМАШ)</t>
+        </is>
+      </c>
       <c r="L73" s="4" t="inlineStr"/>
     </row>
     <row r="74" ht="36" customHeight="1">
@@ -3753,10 +4231,20 @@
       <c r="G74" s="5" t="n">
         <v>5933.32</v>
       </c>
-      <c r="H74" s="5" t="n"/>
-      <c r="I74" s="5" t="n"/>
-      <c r="J74" s="8" t="n"/>
-      <c r="K74" s="4" t="inlineStr"/>
+      <c r="H74" s="5" t="n">
+        <v>1385.13</v>
+      </c>
+      <c r="I74" s="5" t="n">
+        <v>5540.52</v>
+      </c>
+      <c r="J74" s="8" t="n">
+        <v>0.0662023959604402</v>
+      </c>
+      <c r="K74" s="4" t="inlineStr">
+        <is>
+          <t>dn.ru, фланец Россия Ду150 Ру6 ст20 тип 01 исп.B, на 02.11.2026</t>
+        </is>
+      </c>
       <c r="L74" s="4" t="inlineStr"/>
     </row>
     <row r="75" ht="36" customHeight="1">
@@ -3787,10 +4275,20 @@
       <c r="G75" s="5" t="n">
         <v>7140</v>
       </c>
-      <c r="H75" s="5" t="n"/>
-      <c r="I75" s="5" t="n"/>
-      <c r="J75" s="8" t="n"/>
-      <c r="K75" s="4" t="inlineStr"/>
+      <c r="H75" s="5" t="n">
+        <v>832.83</v>
+      </c>
+      <c r="I75" s="5" t="n">
+        <v>4996.98</v>
+      </c>
+      <c r="J75" s="9" t="n">
+        <v>0.3001428571428572</v>
+      </c>
+      <c r="K75" s="4" t="inlineStr">
+        <is>
+          <t>dn.ru, фланец плоский Россия Ду100 Ру6 ст20 тип 01 исп.B ГОСТ 33259-2015, на 02.11.2026</t>
+        </is>
+      </c>
       <c r="L75" s="4" t="inlineStr"/>
     </row>
     <row r="76" ht="36" customHeight="1">
@@ -3821,10 +4319,20 @@
       <c r="G76" s="5" t="n">
         <v>9896.040000000001</v>
       </c>
-      <c r="H76" s="5" t="n"/>
-      <c r="I76" s="5" t="n"/>
-      <c r="J76" s="8" t="n"/>
-      <c r="K76" s="4" t="inlineStr"/>
+      <c r="H76" s="5" t="n">
+        <v>417.79</v>
+      </c>
+      <c r="I76" s="5" t="n">
+        <v>5013.48</v>
+      </c>
+      <c r="J76" s="9" t="n">
+        <v>0.4933852328810312</v>
+      </c>
+      <c r="K76" s="4" t="inlineStr">
+        <is>
+          <t>dn.ru, фланец КЗТШ Ду50 Ру10 ст20 тип 01 исп.B</t>
+        </is>
+      </c>
       <c r="L76" s="4" t="inlineStr"/>
     </row>
     <row r="77" ht="36" customHeight="1">
@@ -3855,11 +4363,25 @@
       <c r="G77" s="5" t="n">
         <v>63226.68</v>
       </c>
-      <c r="H77" s="5" t="n"/>
-      <c r="I77" s="5" t="n"/>
-      <c r="J77" s="8" t="n"/>
-      <c r="K77" s="4" t="inlineStr"/>
-      <c r="L77" s="4" t="inlineStr"/>
+      <c r="H77" s="5" t="n">
+        <v>7618.47</v>
+      </c>
+      <c r="I77" s="5" t="n">
+        <v>30473.88</v>
+      </c>
+      <c r="J77" s="9" t="n">
+        <v>0.5180218224331881</v>
+      </c>
+      <c r="K77" s="4" t="inlineStr">
+        <is>
+          <t>Счёт ДН.РУ 819896_v2 п.40: Луидор 15кч16п1 Ду50 Ру25 чугун фланц. штурвал (база Камчатки)</t>
+        </is>
+      </c>
+      <c r="L77" s="4" t="inlineStr">
+        <is>
+          <t>15кч16п1 Луидор (Ру25 ≥ Ру16)</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="36" customHeight="1">
       <c r="A78" s="4" t="inlineStr">
@@ -3889,10 +4411,20 @@
       <c r="G78" s="5" t="n">
         <v>56783</v>
       </c>
-      <c r="H78" s="5" t="n"/>
-      <c r="I78" s="5" t="n"/>
-      <c r="J78" s="8" t="n"/>
-      <c r="K78" s="4" t="inlineStr"/>
+      <c r="H78" s="5" t="n">
+        <v>58159.8</v>
+      </c>
+      <c r="I78" s="5" t="n">
+        <v>58159.8</v>
+      </c>
+      <c r="J78" s="11" t="n">
+        <v>-0.02424669355264775</v>
+      </c>
+      <c r="K78" s="4" t="inlineStr">
+        <is>
+          <t>СИБЗТА прайс: 30нж41нж Ду100 Ру16</t>
+        </is>
+      </c>
       <c r="L78" s="4" t="inlineStr"/>
     </row>
     <row r="79" ht="36" customHeight="1">
@@ -3923,10 +4455,20 @@
       <c r="G79" s="5" t="n">
         <v>106700</v>
       </c>
-      <c r="H79" s="5" t="n"/>
-      <c r="I79" s="5" t="n"/>
-      <c r="J79" s="8" t="n"/>
-      <c r="K79" s="4" t="inlineStr"/>
+      <c r="H79" s="5" t="n">
+        <v>5993.98</v>
+      </c>
+      <c r="I79" s="5" t="n">
+        <v>59939.8</v>
+      </c>
+      <c r="J79" s="9" t="n">
+        <v>0.4382399250234302</v>
+      </c>
+      <c r="K79" s="4" t="inlineStr">
+        <is>
+          <t>dn.ru, ALSO КШ.Ф.П.080.16-01 Ду80 Ру16 полнопроходной, углерод. сталь, на 29.12.2026</t>
+        </is>
+      </c>
       <c r="L79" s="4" t="inlineStr"/>
     </row>
     <row r="80" ht="36" customHeight="1">
@@ -3957,10 +4499,20 @@
       <c r="G80" s="5" t="n">
         <v>48920</v>
       </c>
-      <c r="H80" s="5" t="n"/>
-      <c r="I80" s="5" t="n"/>
-      <c r="J80" s="8" t="n"/>
-      <c r="K80" s="4" t="inlineStr"/>
+      <c r="H80" s="5" t="n">
+        <v>58159.8</v>
+      </c>
+      <c r="I80" s="5" t="n">
+        <v>58159.8</v>
+      </c>
+      <c r="J80" s="11" t="n">
+        <v>-0.1888757154538021</v>
+      </c>
+      <c r="K80" s="4" t="inlineStr">
+        <is>
+          <t>СИБЗТА прайс: 30нж41нж Ду100 Ру16</t>
+        </is>
+      </c>
       <c r="L80" s="4" t="inlineStr"/>
     </row>
     <row r="81" ht="36" customHeight="1">
@@ -3991,10 +4543,20 @@
       <c r="G81" s="5" t="n">
         <v>73893.34</v>
       </c>
-      <c r="H81" s="5" t="n"/>
-      <c r="I81" s="5" t="n"/>
-      <c r="J81" s="8" t="n"/>
-      <c r="K81" s="4" t="inlineStr"/>
+      <c r="H81" s="5" t="n">
+        <v>42554.7</v>
+      </c>
+      <c r="I81" s="5" t="n">
+        <v>85109.39999999999</v>
+      </c>
+      <c r="J81" s="11" t="n">
+        <v>-0.1517871570022413</v>
+      </c>
+      <c r="K81" s="4" t="inlineStr">
+        <is>
+          <t>СИБЗТА прайс: 30нж41нж Ду80 Ру16</t>
+        </is>
+      </c>
       <c r="L81" s="4" t="inlineStr"/>
     </row>
     <row r="82" ht="36" customHeight="1">
@@ -4025,10 +4587,20 @@
       <c r="G82" s="5" t="n">
         <v>14976.68</v>
       </c>
-      <c r="H82" s="5" t="n"/>
-      <c r="I82" s="5" t="n"/>
-      <c r="J82" s="8" t="n"/>
-      <c r="K82" s="4" t="inlineStr"/>
+      <c r="H82" s="5" t="n">
+        <v>10952.37</v>
+      </c>
+      <c r="I82" s="5" t="n">
+        <v>10952.37</v>
+      </c>
+      <c r="J82" s="9" t="n">
+        <v>0.2687050801646292</v>
+      </c>
+      <c r="K82" s="4" t="inlineStr">
+        <is>
+          <t>прайс АДЛ BD01I12795 ЗПВС-FL(W)-3-150-MN-E = 102,1 у.е. × 119,19</t>
+        </is>
+      </c>
       <c r="L82" s="4" t="inlineStr"/>
     </row>
     <row r="83" ht="36" customHeight="1">
@@ -4059,10 +4631,20 @@
       <c r="G83" s="5" t="n">
         <v>4040</v>
       </c>
-      <c r="H83" s="5" t="n"/>
-      <c r="I83" s="5" t="n"/>
-      <c r="J83" s="8" t="n"/>
-      <c r="K83" s="4" t="inlineStr"/>
+      <c r="H83" s="5" t="n">
+        <v>271.75</v>
+      </c>
+      <c r="I83" s="5" t="n">
+        <v>2174</v>
+      </c>
+      <c r="J83" s="9" t="n">
+        <v>0.4618811881188118</v>
+      </c>
+      <c r="K83" s="4" t="inlineStr">
+        <is>
+          <t>Камчатка verify (LD Pride 47.15.В-В.Р, аналог 11б27п1), dn.ru на 02.11.2026</t>
+        </is>
+      </c>
       <c r="L83" s="4" t="inlineStr"/>
     </row>
     <row r="84" ht="36" customHeight="1">
@@ -4093,38 +4675,48 @@
       <c r="G84" s="5" t="n">
         <v>3024</v>
       </c>
-      <c r="H84" s="5" t="n"/>
-      <c r="I84" s="5" t="n"/>
-      <c r="J84" s="8" t="n"/>
-      <c r="K84" s="4" t="inlineStr"/>
+      <c r="H84" s="5" t="n">
+        <v>361.79</v>
+      </c>
+      <c r="I84" s="5" t="n">
+        <v>1447.16</v>
+      </c>
+      <c r="J84" s="9" t="n">
+        <v>0.521441798941799</v>
+      </c>
+      <c r="K84" s="4" t="inlineStr">
+        <is>
+          <t>dn.ru, LD Pride 47.20.В-В.Р (аналог 11б27п1), на 30.10.2026</t>
+        </is>
+      </c>
       <c r="L84" s="4" t="inlineStr"/>
     </row>
     <row r="85" ht="36" customHeight="1">
-      <c r="A85" s="9" t="inlineStr"/>
-      <c r="B85" s="9" t="inlineStr"/>
-      <c r="C85" s="9" t="inlineStr">
+      <c r="A85" s="12" t="inlineStr"/>
+      <c r="B85" s="12" t="inlineStr"/>
+      <c r="C85" s="12" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="D85" s="9" t="inlineStr"/>
-      <c r="E85" s="9" t="inlineStr"/>
-      <c r="F85" s="9" t="inlineStr"/>
-      <c r="G85" s="10">
+      <c r="D85" s="12" t="inlineStr"/>
+      <c r="E85" s="12" t="inlineStr"/>
+      <c r="F85" s="12" t="inlineStr"/>
+      <c r="G85" s="13">
         <f>SUM(G2:G84)</f>
         <v/>
       </c>
-      <c r="H85" s="9" t="inlineStr"/>
-      <c r="I85" s="10">
+      <c r="H85" s="12" t="inlineStr"/>
+      <c r="I85" s="13">
         <f>SUM(I2:I84)</f>
         <v/>
       </c>
-      <c r="J85" s="11">
+      <c r="J85" s="14">
         <f>1-I85/G85</f>
         <v/>
       </c>
-      <c r="K85" s="12" t="n"/>
-      <c r="L85" s="12" t="n"/>
+      <c r="K85" s="15" t="n"/>
+      <c r="L85" s="15" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4245,10 +4837,20 @@
       <c r="G2" s="5" t="n">
         <v>6630</v>
       </c>
-      <c r="H2" s="5" t="n"/>
-      <c r="I2" s="5" t="n"/>
-      <c r="J2" s="8" t="n"/>
-      <c r="K2" s="4" t="inlineStr"/>
+      <c r="H2" s="5" t="n">
+        <v>446.89</v>
+      </c>
+      <c r="I2" s="5" t="n">
+        <v>6703.349999999999</v>
+      </c>
+      <c r="J2" s="11" t="n">
+        <v>-0.01106334841628964</v>
+      </c>
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>Камчатка verify (Цветлит 15б1п), цена dn.ru на 07.12.2026</t>
+        </is>
+      </c>
       <c r="L2" s="4" t="inlineStr"/>
     </row>
     <row r="3" ht="36" customHeight="1">
@@ -4279,10 +4881,20 @@
       <c r="G3" s="5" t="n">
         <v>5900</v>
       </c>
-      <c r="H3" s="5" t="n"/>
-      <c r="I3" s="5" t="n"/>
-      <c r="J3" s="8" t="n"/>
-      <c r="K3" s="4" t="inlineStr"/>
+      <c r="H3" s="5" t="n">
+        <v>587.98</v>
+      </c>
+      <c r="I3" s="5" t="n">
+        <v>5879.8</v>
+      </c>
+      <c r="J3" s="11" t="n">
+        <v>0.003423728813559346</v>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>Камчатка verify (Цветлит 15б1п), цена dn.ru на 08.12.2026</t>
+        </is>
+      </c>
       <c r="L3" s="4" t="inlineStr"/>
     </row>
     <row r="4" ht="36" customHeight="1">
@@ -4313,10 +4925,20 @@
       <c r="G4" s="5" t="n">
         <v>141930</v>
       </c>
-      <c r="H4" s="5" t="n"/>
-      <c r="I4" s="5" t="n"/>
-      <c r="J4" s="8" t="n"/>
-      <c r="K4" s="4" t="inlineStr"/>
+      <c r="H4" s="5" t="n">
+        <v>1354.93</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>112459.19</v>
+      </c>
+      <c r="J4" s="8" t="n">
+        <v>0.2076432748538012</v>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>Камчатка verify (dn.ru, LD КШ.Ц.П.015.040.Н/П.02 ст20 Ру40), цена dn.ru на 02.11.2026</t>
+        </is>
+      </c>
       <c r="L4" s="4" t="inlineStr"/>
     </row>
     <row r="5" ht="36" customHeight="1">
@@ -4347,10 +4969,20 @@
       <c r="G5" s="5" t="n">
         <v>12460</v>
       </c>
-      <c r="H5" s="5" t="n"/>
-      <c r="I5" s="5" t="n"/>
-      <c r="J5" s="8" t="n"/>
-      <c r="K5" s="4" t="inlineStr"/>
+      <c r="H5" s="5" t="n">
+        <v>1452.11</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>10164.77</v>
+      </c>
+      <c r="J5" s="8" t="n">
+        <v>0.1842078651685394</v>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>dn.ru, LD КШ.Ц.П.020.040.Н/П.02 ст20 Ру40, цена на 02.11.2026</t>
+        </is>
+      </c>
       <c r="L5" s="4" t="inlineStr"/>
     </row>
     <row r="6" ht="36" customHeight="1">
@@ -4381,10 +5013,20 @@
       <c r="G6" s="5" t="n">
         <v>32040</v>
       </c>
-      <c r="H6" s="5" t="n"/>
-      <c r="I6" s="5" t="n"/>
-      <c r="J6" s="8" t="n"/>
-      <c r="K6" s="4" t="inlineStr"/>
+      <c r="H6" s="5" t="n">
+        <v>1452.11</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>26137.98</v>
+      </c>
+      <c r="J6" s="8" t="n">
+        <v>0.1842078651685394</v>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>dn.ru, LD КШ.Ц.П.020.040.Н/П.02 ст20 Ру40, цена на 02.11.2026</t>
+        </is>
+      </c>
       <c r="L6" s="4" t="inlineStr"/>
     </row>
     <row r="7" ht="36" customHeight="1">
@@ -4415,10 +5057,20 @@
       <c r="G7" s="5" t="n">
         <v>32040</v>
       </c>
-      <c r="H7" s="5" t="n"/>
-      <c r="I7" s="5" t="n"/>
-      <c r="J7" s="8" t="n"/>
-      <c r="K7" s="4" t="inlineStr"/>
+      <c r="H7" s="5" t="n">
+        <v>1452.11</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>26137.98</v>
+      </c>
+      <c r="J7" s="8" t="n">
+        <v>0.1842078651685394</v>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>dn.ru, LD КШ.Ц.П.020.040.Н/П.02 ст20 Ру40, цена на 02.11.2026</t>
+        </is>
+      </c>
       <c r="L7" s="4" t="inlineStr"/>
     </row>
     <row r="8" ht="36" customHeight="1">
@@ -4449,10 +5101,20 @@
       <c r="G8" s="5" t="n">
         <v>155400</v>
       </c>
-      <c r="H8" s="5" t="n"/>
-      <c r="I8" s="5" t="n"/>
-      <c r="J8" s="8" t="n"/>
-      <c r="K8" s="4" t="inlineStr"/>
+      <c r="H8" s="5" t="n">
+        <v>1480.5</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>124362</v>
+      </c>
+      <c r="J8" s="8" t="n">
+        <v>0.1997297297297297</v>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>Камчатка verify (dn.ru, LD КШЦП ст20 Ду25)</t>
+        </is>
+      </c>
       <c r="L8" s="4" t="inlineStr"/>
     </row>
     <row r="9" ht="36" customHeight="1">
@@ -4483,10 +5145,20 @@
       <c r="G9" s="5" t="n">
         <v>45360</v>
       </c>
-      <c r="H9" s="5" t="n"/>
-      <c r="I9" s="5" t="n"/>
-      <c r="J9" s="8" t="n"/>
-      <c r="K9" s="4" t="inlineStr"/>
+      <c r="H9" s="5" t="n">
+        <v>1541.7</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>37000.8</v>
+      </c>
+      <c r="J9" s="8" t="n">
+        <v>0.1842857142857143</v>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>Камчатка verify (dn.ru, LD КШЦП ст20 Ду32)</t>
+        </is>
+      </c>
       <c r="L9" s="4" t="inlineStr"/>
     </row>
     <row r="10" ht="36" customHeight="1">
@@ -4517,10 +5189,20 @@
       <c r="G10" s="5" t="n">
         <v>130240</v>
       </c>
-      <c r="H10" s="5" t="n"/>
-      <c r="I10" s="5" t="n"/>
-      <c r="J10" s="8" t="n"/>
-      <c r="K10" s="4" t="inlineStr"/>
+      <c r="H10" s="5" t="n">
+        <v>2178</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>95832</v>
+      </c>
+      <c r="J10" s="9" t="n">
+        <v>0.2641891891891892</v>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>Камчатка verify (dn.ru, LD КШЦП ст20 Ду50)</t>
+        </is>
+      </c>
       <c r="L10" s="4" t="inlineStr"/>
     </row>
     <row r="11" ht="36" customHeight="1">
@@ -4551,10 +5233,20 @@
       <c r="G11" s="5" t="n">
         <v>5920</v>
       </c>
-      <c r="H11" s="5" t="n"/>
-      <c r="I11" s="5" t="n"/>
-      <c r="J11" s="8" t="n"/>
-      <c r="K11" s="4" t="inlineStr"/>
+      <c r="H11" s="5" t="n">
+        <v>2178</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>4356</v>
+      </c>
+      <c r="J11" s="9" t="n">
+        <v>0.2641891891891892</v>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>Камчатка verify (dn.ru, LD КШЦП ст20 Ду50)</t>
+        </is>
+      </c>
       <c r="L11" s="4" t="inlineStr"/>
     </row>
     <row r="12" ht="36" customHeight="1">
@@ -4585,10 +5277,20 @@
       <c r="G12" s="5" t="n">
         <v>283360</v>
       </c>
-      <c r="H12" s="5" t="n"/>
-      <c r="I12" s="5" t="n"/>
-      <c r="J12" s="8" t="n"/>
-      <c r="K12" s="4" t="inlineStr"/>
+      <c r="H12" s="5" t="n">
+        <v>8150.83</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>187469.09</v>
+      </c>
+      <c r="J12" s="9" t="n">
+        <v>0.3384066558441559</v>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>БК-Арматура: 30с64нж DN50 PN25 (ТЕХГИДРОМАШ) + КОФ</t>
+        </is>
+      </c>
       <c r="L12" s="4" t="inlineStr"/>
     </row>
     <row r="13" ht="36" customHeight="1">
@@ -4619,10 +5321,20 @@
       <c r="G13" s="5" t="n">
         <v>128860</v>
       </c>
-      <c r="H13" s="5" t="n"/>
-      <c r="I13" s="5" t="n"/>
-      <c r="J13" s="8" t="n"/>
-      <c r="K13" s="4" t="inlineStr"/>
+      <c r="H13" s="5" t="n">
+        <v>37418.4</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>74836.8</v>
+      </c>
+      <c r="J13" s="9" t="n">
+        <v>0.4192394847120906</v>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>БК-Арматура: 30с64нж DN200 PN25 (ТЕХГИДРОМАШ)</t>
+        </is>
+      </c>
       <c r="L13" s="4" t="inlineStr"/>
     </row>
     <row r="14" ht="36" customHeight="1">
@@ -4653,10 +5365,20 @@
       <c r="G14" s="5" t="n">
         <v>276000</v>
       </c>
-      <c r="H14" s="5" t="n"/>
-      <c r="I14" s="5" t="n"/>
-      <c r="J14" s="8" t="n"/>
-      <c r="K14" s="4" t="inlineStr"/>
+      <c r="H14" s="5" t="n">
+        <v>4020.17</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>160806.8</v>
+      </c>
+      <c r="J14" s="9" t="n">
+        <v>0.4173666666666667</v>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>БК-Арматура: 31ч6бр DN50 PN10 (Казанский арм. з-д) + КОФ</t>
+        </is>
+      </c>
       <c r="L14" s="4" t="inlineStr"/>
     </row>
     <row r="15" ht="36" customHeight="1">
@@ -4687,10 +5409,20 @@
       <c r="G15" s="5" t="n">
         <v>406000</v>
       </c>
-      <c r="H15" s="5" t="n"/>
-      <c r="I15" s="5" t="n"/>
-      <c r="J15" s="8" t="n"/>
-      <c r="K15" s="4" t="inlineStr"/>
+      <c r="H15" s="5" t="n">
+        <v>9277.65</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>259774.2</v>
+      </c>
+      <c r="J15" s="9" t="n">
+        <v>0.3601620689655173</v>
+      </c>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>БК-Арматура: 31ч6бр DN100 (КАЗ) + КОФ</t>
+        </is>
+      </c>
       <c r="L15" s="4" t="inlineStr"/>
     </row>
     <row r="16" ht="36" customHeight="1">
@@ -4721,10 +5453,20 @@
       <c r="G16" s="5" t="n">
         <v>397800</v>
       </c>
-      <c r="H16" s="5" t="n"/>
-      <c r="I16" s="5" t="n"/>
-      <c r="J16" s="8" t="n"/>
-      <c r="K16" s="4" t="inlineStr"/>
+      <c r="H16" s="5" t="n">
+        <v>20469.33</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>266101.29</v>
+      </c>
+      <c r="J16" s="9" t="n">
+        <v>0.3310676470588235</v>
+      </c>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>БК-Арматура: 31ч6бр DN150 (КАЗ) + КОФ</t>
+        </is>
+      </c>
       <c r="L16" s="4" t="inlineStr"/>
     </row>
     <row r="17" ht="36" customHeight="1">
@@ -4755,10 +5497,20 @@
       <c r="G17" s="5" t="n">
         <v>920000</v>
       </c>
-      <c r="H17" s="5" t="n"/>
-      <c r="I17" s="5" t="n"/>
-      <c r="J17" s="8" t="n"/>
-      <c r="K17" s="4" t="inlineStr"/>
+      <c r="H17" s="5" t="n">
+        <v>34862.36</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>557797.76</v>
+      </c>
+      <c r="J17" s="9" t="n">
+        <v>0.3936980869565218</v>
+      </c>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>БК-Арматура: 31ч6бр DN200 PN10 (КАЗ) + КОФ</t>
+        </is>
+      </c>
       <c r="L17" s="4" t="inlineStr"/>
     </row>
     <row r="18" ht="36" customHeight="1">
@@ -4789,10 +5541,20 @@
       <c r="G18" s="5" t="n">
         <v>229740</v>
       </c>
-      <c r="H18" s="5" t="n"/>
-      <c r="I18" s="5" t="n"/>
-      <c r="J18" s="8" t="n"/>
-      <c r="K18" s="4" t="inlineStr"/>
+      <c r="H18" s="5" t="n">
+        <v>52182.32</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>156546.96</v>
+      </c>
+      <c r="J18" s="9" t="n">
+        <v>0.3185907547662575</v>
+      </c>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>БК-Арматура: 31ч6бр DN250 PN10 (КАЗ) + КОФ</t>
+        </is>
+      </c>
       <c r="L18" s="4" t="inlineStr"/>
     </row>
     <row r="19" ht="36" customHeight="1">
@@ -4823,11 +5585,25 @@
       <c r="G19" s="5" t="n">
         <v>642000</v>
       </c>
-      <c r="H19" s="5" t="n"/>
-      <c r="I19" s="5" t="n"/>
-      <c r="J19" s="8" t="n"/>
-      <c r="K19" s="4" t="inlineStr"/>
-      <c r="L19" s="4" t="inlineStr"/>
+      <c r="H19" s="5" t="n">
+        <v>53117.4</v>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>318704.4</v>
+      </c>
+      <c r="J19" s="9" t="n">
+        <v>0.5035757009345794</v>
+      </c>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>dn.ru, Benarmo обратный поворотный фланцевый Ду250 Ру16, обрезин. затвор, на 30.10.2026</t>
+        </is>
+      </c>
+      <c r="L19" s="4" t="inlineStr">
+        <is>
+          <t>Benarmo поворотный Ду250 Ру16 вместо 19ч16бр</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="36" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
@@ -4859,7 +5635,7 @@
       </c>
       <c r="H20" s="5" t="n"/>
       <c r="I20" s="5" t="n"/>
-      <c r="J20" s="8" t="n"/>
+      <c r="J20" s="10" t="n"/>
       <c r="K20" s="4" t="inlineStr"/>
       <c r="L20" s="4" t="inlineStr"/>
     </row>
@@ -4893,7 +5669,7 @@
       </c>
       <c r="H21" s="5" t="n"/>
       <c r="I21" s="5" t="n"/>
-      <c r="J21" s="8" t="n"/>
+      <c r="J21" s="10" t="n"/>
       <c r="K21" s="4" t="inlineStr"/>
       <c r="L21" s="4" t="inlineStr"/>
     </row>
@@ -4927,7 +5703,7 @@
       </c>
       <c r="H22" s="5" t="n"/>
       <c r="I22" s="5" t="n"/>
-      <c r="J22" s="8" t="n"/>
+      <c r="J22" s="10" t="n"/>
       <c r="K22" s="4" t="inlineStr"/>
       <c r="L22" s="4" t="inlineStr"/>
     </row>
@@ -4961,7 +5737,7 @@
       </c>
       <c r="H23" s="5" t="n"/>
       <c r="I23" s="5" t="n"/>
-      <c r="J23" s="8" t="n"/>
+      <c r="J23" s="10" t="n"/>
       <c r="K23" s="4" t="inlineStr"/>
       <c r="L23" s="4" t="inlineStr"/>
     </row>
@@ -4995,7 +5771,7 @@
       </c>
       <c r="H24" s="5" t="n"/>
       <c r="I24" s="5" t="n"/>
-      <c r="J24" s="8" t="n"/>
+      <c r="J24" s="10" t="n"/>
       <c r="K24" s="4" t="inlineStr"/>
       <c r="L24" s="4" t="inlineStr"/>
     </row>
@@ -5029,7 +5805,7 @@
       </c>
       <c r="H25" s="5" t="n"/>
       <c r="I25" s="5" t="n"/>
-      <c r="J25" s="8" t="n"/>
+      <c r="J25" s="10" t="n"/>
       <c r="K25" s="4" t="inlineStr"/>
       <c r="L25" s="4" t="inlineStr"/>
     </row>
@@ -5061,10 +5837,20 @@
       <c r="G26" s="5" t="n">
         <v>37000</v>
       </c>
-      <c r="H26" s="5" t="n"/>
-      <c r="I26" s="5" t="n"/>
-      <c r="J26" s="8" t="n"/>
-      <c r="K26" s="4" t="inlineStr"/>
+      <c r="H26" s="5" t="n">
+        <v>12060</v>
+      </c>
+      <c r="I26" s="5" t="n">
+        <v>24120</v>
+      </c>
+      <c r="J26" s="9" t="n">
+        <v>0.3481081081081081</v>
+      </c>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>techsteklo.ru (ООО «Компания Доминик»): ВДХ Ду50, цена с НДС, ©2026</t>
+        </is>
+      </c>
       <c r="L26" s="4" t="inlineStr"/>
     </row>
     <row r="27" ht="36" customHeight="1">
@@ -5095,10 +5881,20 @@
       <c r="G27" s="5" t="n">
         <v>86520</v>
       </c>
-      <c r="H27" s="5" t="n"/>
-      <c r="I27" s="5" t="n"/>
-      <c r="J27" s="8" t="n"/>
-      <c r="K27" s="4" t="inlineStr"/>
+      <c r="H27" s="5" t="n">
+        <v>32400</v>
+      </c>
+      <c r="I27" s="5" t="n">
+        <v>64800</v>
+      </c>
+      <c r="J27" s="9" t="n">
+        <v>0.2510402219140083</v>
+      </c>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>techsteklo.ru: ВДХ Ду100, с НДС</t>
+        </is>
+      </c>
       <c r="L27" s="4" t="inlineStr"/>
     </row>
     <row r="28" ht="36" customHeight="1">
@@ -5129,10 +5925,20 @@
       <c r="G28" s="5" t="n">
         <v>215600</v>
       </c>
-      <c r="H28" s="5" t="n"/>
-      <c r="I28" s="5" t="n"/>
-      <c r="J28" s="8" t="n"/>
-      <c r="K28" s="4" t="inlineStr"/>
+      <c r="H28" s="5" t="n">
+        <v>81000</v>
+      </c>
+      <c r="I28" s="5" t="n">
+        <v>162000</v>
+      </c>
+      <c r="J28" s="8" t="n">
+        <v>0.24860853432282</v>
+      </c>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>techsteklo.ru: ВДХ Ду150, с НДС</t>
+        </is>
+      </c>
       <c r="L28" s="4" t="inlineStr"/>
     </row>
     <row r="29" ht="36" customHeight="1">
@@ -5163,11 +5969,25 @@
       <c r="G29" s="5" t="n">
         <v>9250</v>
       </c>
-      <c r="H29" s="5" t="n"/>
-      <c r="I29" s="5" t="n"/>
-      <c r="J29" s="8" t="n"/>
-      <c r="K29" s="4" t="inlineStr"/>
-      <c r="L29" s="4" t="inlineStr"/>
+      <c r="H29" s="5" t="n">
+        <v>361.79</v>
+      </c>
+      <c r="I29" s="5" t="n">
+        <v>3617.9</v>
+      </c>
+      <c r="J29" s="9" t="n">
+        <v>0.6088756756756757</v>
+      </c>
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>dn.ru, LD Pride 47.20.В-В.Р 3/4", на 30.10.2026</t>
+        </is>
+      </c>
+      <c r="L29" s="4" t="inlineStr">
+        <is>
+          <t>LD Pride 47.20.В-В.Р (РФ) вместо VALTEC VT.214.N.05</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="36" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
@@ -5197,11 +6017,25 @@
       <c r="G30" s="5" t="n">
         <v>10560</v>
       </c>
-      <c r="H30" s="5" t="n"/>
-      <c r="I30" s="5" t="n"/>
-      <c r="J30" s="8" t="n"/>
-      <c r="K30" s="4" t="inlineStr"/>
-      <c r="L30" s="4" t="inlineStr"/>
+      <c r="H30" s="5" t="n">
+        <v>3402.7</v>
+      </c>
+      <c r="I30" s="5" t="n">
+        <v>6805.4</v>
+      </c>
+      <c r="J30" s="9" t="n">
+        <v>0.3555492424242425</v>
+      </c>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>dn.ru, LD Pride 47.50.В-В.Р 2", на 02.11.2026</t>
+        </is>
+      </c>
+      <c r="L30" s="4" t="inlineStr">
+        <is>
+          <t>LD Pride 47.50.В-В.Р вместо VALTEC VT.214.N.09</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="36" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
@@ -5231,11 +6065,25 @@
       <c r="G31" s="5" t="n">
         <v>15000</v>
       </c>
-      <c r="H31" s="5" t="n"/>
-      <c r="I31" s="5" t="n"/>
-      <c r="J31" s="8" t="n"/>
-      <c r="K31" s="4" t="inlineStr"/>
-      <c r="L31" s="4" t="inlineStr"/>
+      <c r="H31" s="5" t="n">
+        <v>827.34</v>
+      </c>
+      <c r="I31" s="5" t="n">
+        <v>8273.4</v>
+      </c>
+      <c r="J31" s="9" t="n">
+        <v>0.4484399999999999</v>
+      </c>
+      <c r="K31" s="4" t="inlineStr">
+        <is>
+          <t>dn.ru, LD Pride 47.25.В-В.Р 1", на 02.11.2026</t>
+        </is>
+      </c>
+      <c r="L31" s="4" t="inlineStr">
+        <is>
+          <t>LD Pride 47.25.В-В.Р вместо VALTEC VT.214.N.06</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="36" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
@@ -5265,11 +6113,25 @@
       <c r="G32" s="5" t="n">
         <v>7200</v>
       </c>
-      <c r="H32" s="5" t="n"/>
-      <c r="I32" s="5" t="n"/>
-      <c r="J32" s="8" t="n"/>
-      <c r="K32" s="4" t="inlineStr"/>
-      <c r="L32" s="4" t="inlineStr"/>
+      <c r="H32" s="5" t="n">
+        <v>241.56</v>
+      </c>
+      <c r="I32" s="5" t="n">
+        <v>4831.2</v>
+      </c>
+      <c r="J32" s="9" t="n">
+        <v>0.329</v>
+      </c>
+      <c r="K32" s="4" t="inlineStr">
+        <is>
+          <t>dn.ru, LD Pride 47.15.В-В.Б 1/2" (бабочка), на 21.10.2026</t>
+        </is>
+      </c>
+      <c r="L32" s="4" t="inlineStr">
+        <is>
+          <t>LD Pride 47.15.В-В.Б (ООО «ЛД», Челябинск) вместо VALTEC VT.122.GN.04 (Италия/КНР)</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="36" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
@@ -5301,7 +6163,7 @@
       </c>
       <c r="H33" s="5" t="n"/>
       <c r="I33" s="5" t="n"/>
-      <c r="J33" s="8" t="n"/>
+      <c r="J33" s="10" t="n"/>
       <c r="K33" s="4" t="inlineStr"/>
       <c r="L33" s="4" t="inlineStr"/>
     </row>
@@ -5333,11 +6195,25 @@
       <c r="G34" s="5" t="n">
         <v>188946.67</v>
       </c>
-      <c r="H34" s="5" t="n"/>
-      <c r="I34" s="5" t="n"/>
-      <c r="J34" s="8" t="n"/>
-      <c r="K34" s="4" t="inlineStr"/>
-      <c r="L34" s="4" t="inlineStr"/>
+      <c r="H34" s="5" t="n">
+        <v>55258.2</v>
+      </c>
+      <c r="I34" s="5" t="n">
+        <v>55258.2</v>
+      </c>
+      <c r="J34" s="9" t="n">
+        <v>0.7075460498986301</v>
+      </c>
+      <c r="K34" s="4" t="inlineStr">
+        <is>
+          <t>ЭТК Прогресс (etk-progress.ru, ©2026): МЭОФ-1600/25-0,25-96К, 61 398 ₽ (НДС в карточке не указан — принято как с НДС)</t>
+        </is>
+      </c>
+      <c r="L34" s="4" t="inlineStr">
+        <is>
+          <t>МЭОФ-1600/25-0,25-96К (без индекса «У»)</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="36" customHeight="1">
       <c r="A35" s="4" t="inlineStr">
@@ -5369,7 +6245,7 @@
       </c>
       <c r="H35" s="5" t="n"/>
       <c r="I35" s="5" t="n"/>
-      <c r="J35" s="8" t="n"/>
+      <c r="J35" s="10" t="n"/>
       <c r="K35" s="4" t="inlineStr"/>
       <c r="L35" s="4" t="inlineStr"/>
     </row>
@@ -5403,7 +6279,7 @@
       </c>
       <c r="H36" s="5" t="n"/>
       <c r="I36" s="5" t="n"/>
-      <c r="J36" s="8" t="n"/>
+      <c r="J36" s="10" t="n"/>
       <c r="K36" s="4" t="inlineStr"/>
       <c r="L36" s="4" t="inlineStr"/>
     </row>
@@ -5435,10 +6311,20 @@
       <c r="G37" s="5" t="n">
         <v>27540</v>
       </c>
-      <c r="H37" s="5" t="n"/>
-      <c r="I37" s="5" t="n"/>
-      <c r="J37" s="8" t="n"/>
-      <c r="K37" s="4" t="inlineStr"/>
+      <c r="H37" s="5" t="n">
+        <v>7262.24</v>
+      </c>
+      <c r="I37" s="5" t="n">
+        <v>21786.72</v>
+      </c>
+      <c r="J37" s="8" t="n">
+        <v>0.2089063180827887</v>
+      </c>
+      <c r="K37" s="4" t="inlineStr">
+        <is>
+          <t>прайс АДЛ BD01I12792 ЗПВС-FL(W)-3-100-MN-E = 67,7 у.е. × 119,19</t>
+        </is>
+      </c>
       <c r="L37" s="4" t="inlineStr"/>
     </row>
     <row r="38" ht="36" customHeight="1">
@@ -5469,10 +6355,20 @@
       <c r="G38" s="5" t="n">
         <v>69250</v>
       </c>
-      <c r="H38" s="5" t="n"/>
-      <c r="I38" s="5" t="n"/>
-      <c r="J38" s="8" t="n"/>
-      <c r="K38" s="4" t="inlineStr"/>
+      <c r="H38" s="5" t="n">
+        <v>10952.37</v>
+      </c>
+      <c r="I38" s="5" t="n">
+        <v>54761.85000000001</v>
+      </c>
+      <c r="J38" s="8" t="n">
+        <v>0.2092151624548736</v>
+      </c>
+      <c r="K38" s="4" t="inlineStr">
+        <is>
+          <t>прайс АДЛ BD01I12795 ЗПВС-FL(W)-3-150-MN-E = 102,1 у.е. × 119,19</t>
+        </is>
+      </c>
       <c r="L38" s="4" t="inlineStr"/>
     </row>
     <row r="39" ht="36" customHeight="1">
@@ -5503,10 +6399,20 @@
       <c r="G39" s="5" t="n">
         <v>17450</v>
       </c>
-      <c r="H39" s="5" t="n"/>
-      <c r="I39" s="5" t="n"/>
-      <c r="J39" s="8" t="n"/>
-      <c r="K39" s="4" t="inlineStr"/>
+      <c r="H39" s="5" t="n">
+        <v>3553.2</v>
+      </c>
+      <c r="I39" s="5" t="n">
+        <v>17766</v>
+      </c>
+      <c r="J39" s="11" t="n">
+        <v>-0.0181088825214899</v>
+      </c>
+      <c r="K39" s="4" t="inlineStr">
+        <is>
+          <t>СИБЗТА прайс: 15с65нж Ду25 Ру16</t>
+        </is>
+      </c>
       <c r="L39" s="4" t="inlineStr"/>
     </row>
     <row r="40" ht="36" customHeight="1">
@@ -5537,10 +6443,20 @@
       <c r="G40" s="5" t="n">
         <v>31450</v>
       </c>
-      <c r="H40" s="5" t="n"/>
-      <c r="I40" s="5" t="n"/>
-      <c r="J40" s="8" t="n"/>
-      <c r="K40" s="4" t="inlineStr"/>
+      <c r="H40" s="5" t="n">
+        <v>4539.68</v>
+      </c>
+      <c r="I40" s="5" t="n">
+        <v>22698.4</v>
+      </c>
+      <c r="J40" s="9" t="n">
+        <v>0.2782702702702702</v>
+      </c>
+      <c r="K40" s="4" t="inlineStr">
+        <is>
+          <t>dn.ru, Луидор 16ч42р Ду80 приёмный с сеткой, на 30.10.2026</t>
+        </is>
+      </c>
       <c r="L40" s="4" t="inlineStr"/>
     </row>
     <row r="41" ht="36" customHeight="1">
@@ -5571,10 +6487,20 @@
       <c r="G41" s="5" t="n">
         <v>9200</v>
       </c>
-      <c r="H41" s="5" t="n"/>
-      <c r="I41" s="5" t="n"/>
-      <c r="J41" s="8" t="n"/>
-      <c r="K41" s="4" t="inlineStr"/>
+      <c r="H41" s="5" t="n">
+        <v>271.75</v>
+      </c>
+      <c r="I41" s="5" t="n">
+        <v>5435</v>
+      </c>
+      <c r="J41" s="9" t="n">
+        <v>0.4092391304347827</v>
+      </c>
+      <c r="K41" s="4" t="inlineStr">
+        <is>
+          <t>Камчатка verify (LD Pride 47.15.В-В.Р, аналог 11б27п1), dn.ru на 02.11.2026</t>
+        </is>
+      </c>
       <c r="L41" s="4" t="inlineStr"/>
     </row>
     <row r="42" ht="36" customHeight="1">
@@ -5605,10 +6531,20 @@
       <c r="G42" s="5" t="n">
         <v>119490</v>
       </c>
-      <c r="H42" s="5" t="n"/>
-      <c r="I42" s="5" t="n"/>
-      <c r="J42" s="8" t="n"/>
-      <c r="K42" s="4" t="inlineStr"/>
+      <c r="H42" s="5" t="n">
+        <v>27762.38</v>
+      </c>
+      <c r="I42" s="5" t="n">
+        <v>83287.14</v>
+      </c>
+      <c r="J42" s="9" t="n">
+        <v>0.3029781571679638</v>
+      </c>
+      <c r="K42" s="4" t="inlineStr">
+        <is>
+          <t>dn.ru, Benarmo обратный шаровой Ду150 Ру16 чугун/сталь NBR, на 30.10.2026</t>
+        </is>
+      </c>
       <c r="L42" s="4" t="inlineStr"/>
     </row>
     <row r="43" ht="36" customHeight="1">
@@ -5639,10 +6575,20 @@
       <c r="G43" s="5" t="n">
         <v>56760</v>
       </c>
-      <c r="H43" s="5" t="n"/>
-      <c r="I43" s="5" t="n"/>
-      <c r="J43" s="8" t="n"/>
-      <c r="K43" s="4" t="inlineStr"/>
+      <c r="H43" s="5" t="n">
+        <v>13974.25</v>
+      </c>
+      <c r="I43" s="5" t="n">
+        <v>41922.75</v>
+      </c>
+      <c r="J43" s="9" t="n">
+        <v>0.2614032769556025</v>
+      </c>
+      <c r="K43" s="4" t="inlineStr">
+        <is>
+          <t>dn.ru, Benarmo обратный шаровой Ду100 Ру16, на 30.10.2026</t>
+        </is>
+      </c>
       <c r="L43" s="4" t="inlineStr"/>
     </row>
     <row r="44" ht="36" customHeight="1">
@@ -5673,10 +6619,20 @@
       <c r="G44" s="5" t="n">
         <v>1039600</v>
       </c>
-      <c r="H44" s="5" t="n"/>
-      <c r="I44" s="5" t="n"/>
-      <c r="J44" s="8" t="n"/>
-      <c r="K44" s="4" t="inlineStr"/>
+      <c r="H44" s="5" t="n">
+        <v>6298.2</v>
+      </c>
+      <c r="I44" s="5" t="n">
+        <v>62982</v>
+      </c>
+      <c r="J44" s="9" t="n">
+        <v>0.9394170834936514</v>
+      </c>
+      <c r="K44" s="4" t="inlineStr">
+        <is>
+          <t>БК-Арматура: 30с41нж DN80 PN16, с НДС</t>
+        </is>
+      </c>
       <c r="L44" s="4" t="inlineStr"/>
     </row>
     <row r="45" ht="36" customHeight="1">
@@ -5707,10 +6663,20 @@
       <c r="G45" s="5" t="n">
         <v>76750</v>
       </c>
-      <c r="H45" s="5" t="n"/>
-      <c r="I45" s="5" t="n"/>
-      <c r="J45" s="8" t="n"/>
-      <c r="K45" s="4" t="inlineStr"/>
+      <c r="H45" s="5" t="n">
+        <v>9444.6</v>
+      </c>
+      <c r="I45" s="5" t="n">
+        <v>47223</v>
+      </c>
+      <c r="J45" s="9" t="n">
+        <v>0.3847166123778502</v>
+      </c>
+      <c r="K45" s="4" t="inlineStr">
+        <is>
+          <t>БК-Арматура: 30с64нж DN80 PN25 (ТЕХГИДРОМАШ)</t>
+        </is>
+      </c>
       <c r="L45" s="4" t="inlineStr"/>
     </row>
     <row r="46" ht="36" customHeight="1">
@@ -5741,11 +6707,25 @@
       <c r="G46" s="5" t="n">
         <v>3800</v>
       </c>
-      <c r="H46" s="5" t="n"/>
-      <c r="I46" s="5" t="n"/>
-      <c r="J46" s="8" t="n"/>
-      <c r="K46" s="4" t="inlineStr"/>
-      <c r="L46" s="4" t="inlineStr"/>
+      <c r="H46" s="5" t="n">
+        <v>446.89</v>
+      </c>
+      <c r="I46" s="5" t="n">
+        <v>4468.9</v>
+      </c>
+      <c r="J46" s="11" t="n">
+        <v>-0.1760263157894737</v>
+      </c>
+      <c r="K46" s="4" t="inlineStr">
+        <is>
+          <t>dn.ru, Цветлит 15б1п Ду15 Ру16 латунь (замена 15кч18п)</t>
+        </is>
+      </c>
+      <c r="L46" s="4" t="inlineStr">
+        <is>
+          <t>15б1п Цветлит Ду15 (ЕАЭС) вместо 15кч18п (на рынке только КНР: dn.ru «Китай»/Ci)</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="36" customHeight="1">
       <c r="A47" s="4" t="inlineStr">
@@ -5775,11 +6755,25 @@
       <c r="G47" s="5" t="n">
         <v>4000</v>
       </c>
-      <c r="H47" s="5" t="n"/>
-      <c r="I47" s="5" t="n"/>
-      <c r="J47" s="8" t="n"/>
-      <c r="K47" s="4" t="inlineStr"/>
-      <c r="L47" s="4" t="inlineStr"/>
+      <c r="H47" s="5" t="n">
+        <v>587.98</v>
+      </c>
+      <c r="I47" s="5" t="n">
+        <v>5879.8</v>
+      </c>
+      <c r="J47" s="11" t="n">
+        <v>-0.4699500000000001</v>
+      </c>
+      <c r="K47" s="4" t="inlineStr">
+        <is>
+          <t>dn.ru, Цветлит 15б1п Ду20 Ру16 латунь (замена 15кч18п)</t>
+        </is>
+      </c>
+      <c r="L47" s="4" t="inlineStr">
+        <is>
+          <t>15б1п Цветлит Ду20 (ЕАЭС) вместо 15кч18п (на рынке только КНР: dn.ru «Китай»/Ci)</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="36" customHeight="1">
       <c r="A48" s="4" t="inlineStr">
@@ -5809,11 +6803,25 @@
       <c r="G48" s="5" t="n">
         <v>3710</v>
       </c>
-      <c r="H48" s="5" t="n"/>
-      <c r="I48" s="5" t="n"/>
-      <c r="J48" s="8" t="n"/>
-      <c r="K48" s="4" t="inlineStr"/>
-      <c r="L48" s="4" t="inlineStr"/>
+      <c r="H48" s="5" t="n">
+        <v>831.1900000000001</v>
+      </c>
+      <c r="I48" s="5" t="n">
+        <v>5818.33</v>
+      </c>
+      <c r="J48" s="11" t="n">
+        <v>-0.5682830188679246</v>
+      </c>
+      <c r="K48" s="4" t="inlineStr">
+        <is>
+          <t>dn.ru, Цветлит 15б1п Ду25 Ру16 латунь (замена 15кч18п)</t>
+        </is>
+      </c>
+      <c r="L48" s="4" t="inlineStr">
+        <is>
+          <t>15б1п Цветлит Ду25 (ЕАЭС) вместо 15кч18п (на рынке только КНР: dn.ru «Китай»/Ci)</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="36" customHeight="1">
       <c r="A49" s="4" t="inlineStr">
@@ -5843,11 +6851,25 @@
       <c r="G49" s="5" t="n">
         <v>5100</v>
       </c>
-      <c r="H49" s="5" t="n"/>
-      <c r="I49" s="5" t="n"/>
-      <c r="J49" s="8" t="n"/>
-      <c r="K49" s="4" t="inlineStr"/>
-      <c r="L49" s="4" t="inlineStr"/>
+      <c r="H49" s="5" t="n">
+        <v>925.0599999999999</v>
+      </c>
+      <c r="I49" s="5" t="n">
+        <v>5550.36</v>
+      </c>
+      <c r="J49" s="11" t="n">
+        <v>-0.08830588235294101</v>
+      </c>
+      <c r="K49" s="4" t="inlineStr">
+        <is>
+          <t>dn.ru, Цветлит 15б1п Ду32 Ру16 латунь (замена 15кч18п)</t>
+        </is>
+      </c>
+      <c r="L49" s="4" t="inlineStr">
+        <is>
+          <t>15б1п Цветлит Ду32 (ЕАЭС) вместо 15кч18п (на рынке только КНР: dn.ru «Китай»/Ci)</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="36" customHeight="1">
       <c r="A50" s="4" t="inlineStr">
@@ -5877,11 +6899,25 @@
       <c r="G50" s="5" t="n">
         <v>52000</v>
       </c>
-      <c r="H50" s="5" t="n"/>
-      <c r="I50" s="5" t="n"/>
-      <c r="J50" s="8" t="n"/>
-      <c r="K50" s="4" t="inlineStr"/>
-      <c r="L50" s="4" t="inlineStr"/>
+      <c r="H50" s="5" t="n">
+        <v>1558.06</v>
+      </c>
+      <c r="I50" s="5" t="n">
+        <v>62322.39999999999</v>
+      </c>
+      <c r="J50" s="11" t="n">
+        <v>-0.1985076923076923</v>
+      </c>
+      <c r="K50" s="4" t="inlineStr">
+        <is>
+          <t>dn.ru, Цветлит 15б1п Ду40 Ру16 латунь (замена 15кч18п)</t>
+        </is>
+      </c>
+      <c r="L50" s="4" t="inlineStr">
+        <is>
+          <t>15б1п Цветлит Ду40 (ЕАЭС) вместо 15кч18п (на рынке только КНР: dn.ru «Китай»/Ci)</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="36" customHeight="1">
       <c r="A51" s="4" t="inlineStr">
@@ -5911,11 +6947,25 @@
       <c r="G51" s="5" t="n">
         <v>54000</v>
       </c>
-      <c r="H51" s="5" t="n"/>
-      <c r="I51" s="5" t="n"/>
-      <c r="J51" s="8" t="n"/>
-      <c r="K51" s="4" t="inlineStr"/>
-      <c r="L51" s="4" t="inlineStr"/>
+      <c r="H51" s="5" t="n">
+        <v>1980.79</v>
+      </c>
+      <c r="I51" s="5" t="n">
+        <v>59423.7</v>
+      </c>
+      <c r="J51" s="11" t="n">
+        <v>-0.100438888888889</v>
+      </c>
+      <c r="K51" s="4" t="inlineStr">
+        <is>
+          <t>dn.ru, Цветлит 15б1п Ду50 Ру16 латунь (замена 15кч18п)</t>
+        </is>
+      </c>
+      <c r="L51" s="4" t="inlineStr">
+        <is>
+          <t>15б1п Цветлит Ду50 (ЕАЭС) вместо 15кч18п (на рынке только КНР: dn.ru «Китай»/Ci)</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="36" customHeight="1">
       <c r="A52" s="4" t="inlineStr">
@@ -5945,10 +6995,20 @@
       <c r="G52" s="5" t="n">
         <v>102000</v>
       </c>
-      <c r="H52" s="5" t="n"/>
-      <c r="I52" s="5" t="n"/>
-      <c r="J52" s="8" t="n"/>
-      <c r="K52" s="4" t="inlineStr"/>
+      <c r="H52" s="5" t="n">
+        <v>900</v>
+      </c>
+      <c r="I52" s="5" t="n">
+        <v>36000</v>
+      </c>
+      <c r="J52" s="9" t="n">
+        <v>0.6470588235294117</v>
+      </c>
+      <c r="K52" s="4" t="inlineStr">
+        <is>
+          <t>techsteklo.ru: трубка кварцевая 18х2х1500, с НДС</t>
+        </is>
+      </c>
       <c r="L52" s="4" t="inlineStr"/>
     </row>
     <row r="53" ht="36" customHeight="1">
@@ -5979,10 +7039,20 @@
       <c r="G53" s="5" t="n">
         <v>696000</v>
       </c>
-      <c r="H53" s="5" t="n"/>
-      <c r="I53" s="5" t="n"/>
-      <c r="J53" s="8" t="n"/>
-      <c r="K53" s="4" t="inlineStr"/>
+      <c r="H53" s="5" t="n">
+        <v>99000</v>
+      </c>
+      <c r="I53" s="5" t="n">
+        <v>396000</v>
+      </c>
+      <c r="J53" s="9" t="n">
+        <v>0.4310344827586207</v>
+      </c>
+      <c r="K53" s="4" t="inlineStr">
+        <is>
+          <t>techsteklo.ru (ООО «Компания Доминик»): Т-229б Ду20 Ру165, цена с НДС, ©2026</t>
+        </is>
+      </c>
       <c r="L53" s="4" t="inlineStr"/>
     </row>
     <row r="54" ht="36" customHeight="1">
@@ -6015,7 +7085,7 @@
       </c>
       <c r="H54" s="5" t="n"/>
       <c r="I54" s="5" t="n"/>
-      <c r="J54" s="8" t="n"/>
+      <c r="J54" s="10" t="n"/>
       <c r="K54" s="4" t="inlineStr"/>
       <c r="L54" s="4" t="inlineStr"/>
     </row>
@@ -6047,10 +7117,20 @@
       <c r="G55" s="5" t="n">
         <v>1420500</v>
       </c>
-      <c r="H55" s="5" t="n"/>
-      <c r="I55" s="5" t="n"/>
-      <c r="J55" s="8" t="n"/>
-      <c r="K55" s="4" t="inlineStr"/>
+      <c r="H55" s="5" t="n">
+        <v>176804.26</v>
+      </c>
+      <c r="I55" s="5" t="n">
+        <v>884021.3</v>
+      </c>
+      <c r="J55" s="9" t="n">
+        <v>0.3776689193945794</v>
+      </c>
+      <c r="K55" s="4" t="inlineStr">
+        <is>
+          <t>БК-Арматура: 30ч6бр DN400 PN10 (Казанский арм. з-д) + КОФ</t>
+        </is>
+      </c>
       <c r="L55" s="4" t="inlineStr"/>
     </row>
     <row r="56" ht="36" customHeight="1">
@@ -6081,10 +7161,20 @@
       <c r="G56" s="5" t="n">
         <v>306000</v>
       </c>
-      <c r="H56" s="5" t="n"/>
-      <c r="I56" s="5" t="n"/>
-      <c r="J56" s="8" t="n"/>
-      <c r="K56" s="4" t="inlineStr"/>
+      <c r="H56" s="5" t="n">
+        <v>64134.9</v>
+      </c>
+      <c r="I56" s="5" t="n">
+        <v>192404.7</v>
+      </c>
+      <c r="J56" s="9" t="n">
+        <v>0.3712264705882353</v>
+      </c>
+      <c r="K56" s="4" t="inlineStr">
+        <is>
+          <t>БК-Арматура: 30с64нж DN250 PN25 (ТЕХГИДРОМАШ)</t>
+        </is>
+      </c>
       <c r="L56" s="4" t="inlineStr"/>
     </row>
     <row r="57" ht="36" customHeight="1">
@@ -6115,10 +7205,20 @@
       <c r="G57" s="5" t="n">
         <v>129000</v>
       </c>
-      <c r="H57" s="5" t="n"/>
-      <c r="I57" s="5" t="n"/>
-      <c r="J57" s="8" t="n"/>
-      <c r="K57" s="4" t="inlineStr"/>
+      <c r="H57" s="5" t="n">
+        <v>82428.3</v>
+      </c>
+      <c r="I57" s="5" t="n">
+        <v>82428.3</v>
+      </c>
+      <c r="J57" s="9" t="n">
+        <v>0.3610209302325581</v>
+      </c>
+      <c r="K57" s="4" t="inlineStr">
+        <is>
+          <t>БК-Арматура: 30с64нж DN300 PN25 (ТЕХГИДРОМАШ)</t>
+        </is>
+      </c>
       <c r="L57" s="4" t="inlineStr"/>
     </row>
     <row r="58" ht="36" customHeight="1">
@@ -6149,10 +7249,20 @@
       <c r="G58" s="5" t="n">
         <v>45600</v>
       </c>
-      <c r="H58" s="5" t="n"/>
-      <c r="I58" s="5" t="n"/>
-      <c r="J58" s="8" t="n"/>
-      <c r="K58" s="4" t="inlineStr"/>
+      <c r="H58" s="5" t="n">
+        <v>6253.66</v>
+      </c>
+      <c r="I58" s="5" t="n">
+        <v>37521.96</v>
+      </c>
+      <c r="J58" s="8" t="n">
+        <v>0.17715</v>
+      </c>
+      <c r="K58" s="4" t="inlineStr">
+        <is>
+          <t>dn.ru, LD КШ.Ц.Ф.080/070.025.Н/П.02 Ду80 Ру25, на 26.10.2026</t>
+        </is>
+      </c>
       <c r="L58" s="4" t="inlineStr"/>
     </row>
     <row r="59" ht="36" customHeight="1">
@@ -6185,7 +7295,7 @@
       </c>
       <c r="H59" s="5" t="n"/>
       <c r="I59" s="5" t="n"/>
-      <c r="J59" s="8" t="n"/>
+      <c r="J59" s="10" t="n"/>
       <c r="K59" s="4" t="inlineStr"/>
       <c r="L59" s="4" t="inlineStr"/>
     </row>
@@ -6219,7 +7329,7 @@
       </c>
       <c r="H60" s="5" t="n"/>
       <c r="I60" s="5" t="n"/>
-      <c r="J60" s="8" t="n"/>
+      <c r="J60" s="10" t="n"/>
       <c r="K60" s="4" t="inlineStr"/>
       <c r="L60" s="4" t="inlineStr"/>
     </row>
@@ -6253,7 +7363,7 @@
       </c>
       <c r="H61" s="5" t="n"/>
       <c r="I61" s="5" t="n"/>
-      <c r="J61" s="8" t="n"/>
+      <c r="J61" s="10" t="n"/>
       <c r="K61" s="4" t="inlineStr"/>
       <c r="L61" s="4" t="inlineStr"/>
     </row>
@@ -6287,7 +7397,7 @@
       </c>
       <c r="H62" s="5" t="n"/>
       <c r="I62" s="5" t="n"/>
-      <c r="J62" s="8" t="n"/>
+      <c r="J62" s="10" t="n"/>
       <c r="K62" s="4" t="inlineStr"/>
       <c r="L62" s="4" t="inlineStr"/>
     </row>
@@ -6321,7 +7431,7 @@
       </c>
       <c r="H63" s="5" t="n"/>
       <c r="I63" s="5" t="n"/>
-      <c r="J63" s="8" t="n"/>
+      <c r="J63" s="10" t="n"/>
       <c r="K63" s="4" t="inlineStr"/>
       <c r="L63" s="4" t="inlineStr"/>
     </row>
@@ -6355,7 +7465,7 @@
       </c>
       <c r="H64" s="5" t="n"/>
       <c r="I64" s="5" t="n"/>
-      <c r="J64" s="8" t="n"/>
+      <c r="J64" s="10" t="n"/>
       <c r="K64" s="4" t="inlineStr"/>
       <c r="L64" s="4" t="inlineStr"/>
     </row>
@@ -6389,7 +7499,7 @@
       </c>
       <c r="H65" s="5" t="n"/>
       <c r="I65" s="5" t="n"/>
-      <c r="J65" s="8" t="n"/>
+      <c r="J65" s="10" t="n"/>
       <c r="K65" s="4" t="inlineStr"/>
       <c r="L65" s="4" t="inlineStr"/>
     </row>
@@ -6423,7 +7533,7 @@
       </c>
       <c r="H66" s="5" t="n"/>
       <c r="I66" s="5" t="n"/>
-      <c r="J66" s="8" t="n"/>
+      <c r="J66" s="10" t="n"/>
       <c r="K66" s="4" t="inlineStr"/>
       <c r="L66" s="4" t="inlineStr"/>
     </row>
@@ -6457,7 +7567,7 @@
       </c>
       <c r="H67" s="5" t="n"/>
       <c r="I67" s="5" t="n"/>
-      <c r="J67" s="8" t="n"/>
+      <c r="J67" s="10" t="n"/>
       <c r="K67" s="4" t="inlineStr"/>
       <c r="L67" s="4" t="inlineStr"/>
     </row>
@@ -6489,10 +7599,20 @@
       <c r="G68" s="5" t="n">
         <v>43600</v>
       </c>
-      <c r="H68" s="5" t="n"/>
-      <c r="I68" s="5" t="n"/>
-      <c r="J68" s="8" t="n"/>
-      <c r="K68" s="4" t="inlineStr"/>
+      <c r="H68" s="5" t="n">
+        <v>2700</v>
+      </c>
+      <c r="I68" s="5" t="n">
+        <v>13500</v>
+      </c>
+      <c r="J68" s="9" t="n">
+        <v>0.6903669724770642</v>
+      </c>
+      <c r="K68" s="4" t="inlineStr">
+        <is>
+          <t>techsteklo.ru: 15ч75п1 Ду25 Ру10 (футеровка полиэтилен), с НДС</t>
+        </is>
+      </c>
       <c r="L68" s="4" t="inlineStr"/>
     </row>
     <row r="69" ht="36" customHeight="1">
@@ -6523,10 +7643,20 @@
       <c r="G69" s="5" t="n">
         <v>70800</v>
       </c>
-      <c r="H69" s="5" t="n"/>
-      <c r="I69" s="5" t="n"/>
-      <c r="J69" s="8" t="n"/>
-      <c r="K69" s="4" t="inlineStr"/>
+      <c r="H69" s="5" t="n">
+        <v>7200</v>
+      </c>
+      <c r="I69" s="5" t="n">
+        <v>28800</v>
+      </c>
+      <c r="J69" s="9" t="n">
+        <v>0.5932203389830508</v>
+      </c>
+      <c r="K69" s="4" t="inlineStr">
+        <is>
+          <t>techsteklo.ru: 15п67п Ду50 Ру6, с НДС</t>
+        </is>
+      </c>
       <c r="L69" s="4" t="inlineStr"/>
     </row>
     <row r="70" ht="36" customHeight="1">
@@ -6559,7 +7689,7 @@
       </c>
       <c r="H70" s="5" t="n"/>
       <c r="I70" s="5" t="n"/>
-      <c r="J70" s="8" t="n"/>
+      <c r="J70" s="10" t="n"/>
       <c r="K70" s="4" t="inlineStr"/>
       <c r="L70" s="4" t="inlineStr"/>
     </row>
@@ -6591,10 +7721,20 @@
       <c r="G71" s="5" t="n">
         <v>71200</v>
       </c>
-      <c r="H71" s="5" t="n"/>
-      <c r="I71" s="5" t="n"/>
-      <c r="J71" s="8" t="n"/>
-      <c r="K71" s="4" t="inlineStr"/>
+      <c r="H71" s="5" t="n">
+        <v>7200</v>
+      </c>
+      <c r="I71" s="5" t="n">
+        <v>28800</v>
+      </c>
+      <c r="J71" s="9" t="n">
+        <v>0.5955056179775281</v>
+      </c>
+      <c r="K71" s="4" t="inlineStr">
+        <is>
+          <t>techsteklo.ru: 15п67п Ду50 Ру6, с НДС</t>
+        </is>
+      </c>
       <c r="L71" s="4" t="inlineStr"/>
     </row>
     <row r="72" ht="36" customHeight="1">
@@ -6625,10 +7765,20 @@
       <c r="G72" s="5" t="n">
         <v>42000</v>
       </c>
-      <c r="H72" s="5" t="n"/>
-      <c r="I72" s="5" t="n"/>
-      <c r="J72" s="8" t="n"/>
-      <c r="K72" s="4" t="inlineStr"/>
+      <c r="H72" s="5" t="n">
+        <v>3420</v>
+      </c>
+      <c r="I72" s="5" t="n">
+        <v>20520</v>
+      </c>
+      <c r="J72" s="9" t="n">
+        <v>0.5114285714285715</v>
+      </c>
+      <c r="K72" s="4" t="inlineStr">
+        <is>
+          <t>techsteklo.ru: 15ч93эм Ду25, с НДС</t>
+        </is>
+      </c>
       <c r="L72" s="4" t="inlineStr"/>
     </row>
     <row r="73" ht="36" customHeight="1">
@@ -6659,10 +7809,20 @@
       <c r="G73" s="5" t="n">
         <v>10200</v>
       </c>
-      <c r="H73" s="5" t="n"/>
-      <c r="I73" s="5" t="n"/>
-      <c r="J73" s="8" t="n"/>
-      <c r="K73" s="4" t="inlineStr"/>
+      <c r="H73" s="5" t="n">
+        <v>446.89</v>
+      </c>
+      <c r="I73" s="5" t="n">
+        <v>8937.799999999999</v>
+      </c>
+      <c r="J73" s="8" t="n">
+        <v>0.1237450980392157</v>
+      </c>
+      <c r="K73" s="4" t="inlineStr">
+        <is>
+          <t>Камчатка verify (Цветлит 15б1п), цена dn.ru на 07.12.2026</t>
+        </is>
+      </c>
       <c r="L73" s="4" t="inlineStr"/>
     </row>
     <row r="74" ht="36" customHeight="1">
@@ -6693,10 +7853,20 @@
       <c r="G74" s="5" t="n">
         <v>13600</v>
       </c>
-      <c r="H74" s="5" t="n"/>
-      <c r="I74" s="5" t="n"/>
-      <c r="J74" s="8" t="n"/>
-      <c r="K74" s="4" t="inlineStr"/>
+      <c r="H74" s="5" t="n">
+        <v>587.98</v>
+      </c>
+      <c r="I74" s="5" t="n">
+        <v>11759.6</v>
+      </c>
+      <c r="J74" s="8" t="n">
+        <v>0.1353235294117647</v>
+      </c>
+      <c r="K74" s="4" t="inlineStr">
+        <is>
+          <t>Камчатка verify (Цветлит 15б1п), цена dn.ru на 08.12.2026</t>
+        </is>
+      </c>
       <c r="L74" s="4" t="inlineStr"/>
     </row>
     <row r="75" ht="36" customHeight="1">
@@ -6727,11 +7897,25 @@
       <c r="G75" s="5" t="n">
         <v>9100</v>
       </c>
-      <c r="H75" s="5" t="n"/>
-      <c r="I75" s="5" t="n"/>
-      <c r="J75" s="8" t="n"/>
-      <c r="K75" s="4" t="inlineStr"/>
-      <c r="L75" s="4" t="inlineStr"/>
+      <c r="H75" s="5" t="n">
+        <v>361.79</v>
+      </c>
+      <c r="I75" s="5" t="n">
+        <v>3617.9</v>
+      </c>
+      <c r="J75" s="9" t="n">
+        <v>0.6024285714285714</v>
+      </c>
+      <c r="K75" s="4" t="inlineStr">
+        <is>
+          <t>dn.ru, LD Pride 47.20.В-В.Р 3/4", на 30.10.2026</t>
+        </is>
+      </c>
+      <c r="L75" s="4" t="inlineStr">
+        <is>
+          <t>LD Pride 47.20.В-В.Р (РФ) вместо VALTEC VT.214.N.05</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="36" customHeight="1">
       <c r="A76" s="4" t="inlineStr">
@@ -6761,10 +7945,20 @@
       <c r="G76" s="5" t="n">
         <v>9200</v>
       </c>
-      <c r="H76" s="5" t="n"/>
-      <c r="I76" s="5" t="n"/>
-      <c r="J76" s="8" t="n"/>
-      <c r="K76" s="4" t="inlineStr"/>
+      <c r="H76" s="5" t="n">
+        <v>271.75</v>
+      </c>
+      <c r="I76" s="5" t="n">
+        <v>5435</v>
+      </c>
+      <c r="J76" s="9" t="n">
+        <v>0.4092391304347827</v>
+      </c>
+      <c r="K76" s="4" t="inlineStr">
+        <is>
+          <t>Камчатка verify (LD Pride 47.15.В-В.Р, аналог 11б27п1), dn.ru на 02.11.2026</t>
+        </is>
+      </c>
       <c r="L76" s="4" t="inlineStr"/>
     </row>
     <row r="77" ht="36" customHeight="1">
@@ -6795,10 +7989,20 @@
       <c r="G77" s="5" t="n">
         <v>14800</v>
       </c>
-      <c r="H77" s="5" t="n"/>
-      <c r="I77" s="5" t="n"/>
-      <c r="J77" s="8" t="n"/>
-      <c r="K77" s="4" t="inlineStr"/>
+      <c r="H77" s="5" t="n">
+        <v>361.79</v>
+      </c>
+      <c r="I77" s="5" t="n">
+        <v>7235.8</v>
+      </c>
+      <c r="J77" s="9" t="n">
+        <v>0.5110945945945946</v>
+      </c>
+      <c r="K77" s="4" t="inlineStr">
+        <is>
+          <t>dn.ru, LD Pride 47.20.В-В.Р (аналог 11б27п1), на 30.10.2026</t>
+        </is>
+      </c>
       <c r="L77" s="4" t="inlineStr"/>
     </row>
     <row r="78" ht="36" customHeight="1">
@@ -6829,10 +8033,20 @@
       <c r="G78" s="5" t="n">
         <v>1100</v>
       </c>
-      <c r="H78" s="5" t="n"/>
-      <c r="I78" s="5" t="n"/>
-      <c r="J78" s="8" t="n"/>
-      <c r="K78" s="4" t="inlineStr"/>
+      <c r="H78" s="5" t="n">
+        <v>48.86</v>
+      </c>
+      <c r="I78" s="5" t="n">
+        <v>977.2</v>
+      </c>
+      <c r="J78" s="8" t="n">
+        <v>0.1116363636363636</v>
+      </c>
+      <c r="K78" s="4" t="inlineStr">
+        <is>
+          <t>dn.ru, сгон АС 3/4" Ду20 L=110 сталь, на 30.10.2026</t>
+        </is>
+      </c>
       <c r="L78" s="4" t="inlineStr"/>
     </row>
     <row r="79" ht="36" customHeight="1">
@@ -6863,10 +8077,20 @@
       <c r="G79" s="5" t="n">
         <v>1100</v>
       </c>
-      <c r="H79" s="5" t="n"/>
-      <c r="I79" s="5" t="n"/>
-      <c r="J79" s="8" t="n"/>
-      <c r="K79" s="4" t="inlineStr"/>
+      <c r="H79" s="5" t="n">
+        <v>46.66</v>
+      </c>
+      <c r="I79" s="5" t="n">
+        <v>933.1999999999999</v>
+      </c>
+      <c r="J79" s="8" t="n">
+        <v>0.1516363636363637</v>
+      </c>
+      <c r="K79" s="4" t="inlineStr">
+        <is>
+          <t>dn.ru, сгон оцинк. КАЗ 1/2" Ду15 L=110 ГОСТ 8969-75 без комплекта, на 02.11.2026</t>
+        </is>
+      </c>
       <c r="L79" s="4" t="inlineStr"/>
     </row>
     <row r="80" ht="36" customHeight="1">
@@ -6899,7 +8123,7 @@
       </c>
       <c r="H80" s="5" t="n"/>
       <c r="I80" s="5" t="n"/>
-      <c r="J80" s="8" t="n"/>
+      <c r="J80" s="10" t="n"/>
       <c r="K80" s="4" t="inlineStr"/>
       <c r="L80" s="4" t="inlineStr"/>
     </row>
@@ -6931,11 +8155,25 @@
       <c r="G81" s="5" t="n">
         <v>11600</v>
       </c>
-      <c r="H81" s="5" t="n"/>
-      <c r="I81" s="5" t="n"/>
-      <c r="J81" s="8" t="n"/>
-      <c r="K81" s="4" t="inlineStr"/>
-      <c r="L81" s="4" t="inlineStr"/>
+      <c r="H81" s="5" t="n">
+        <v>282.19</v>
+      </c>
+      <c r="I81" s="5" t="n">
+        <v>5643.8</v>
+      </c>
+      <c r="J81" s="9" t="n">
+        <v>0.5134655172413793</v>
+      </c>
+      <c r="K81" s="4" t="inlineStr">
+        <is>
+          <t>dn.ru, LD Pride 47.15.В-Н.Р GAS 1/2" полнопроходной, на 02.11.2026</t>
+        </is>
+      </c>
+      <c r="L81" s="4" t="inlineStr">
+        <is>
+          <t>LD Pride 47.15.В-Н.Р (РФ) вместо VALTEC VT.218.N.04</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="36" customHeight="1">
       <c r="A82" s="4" t="inlineStr">
@@ -6965,11 +8203,25 @@
       <c r="G82" s="5" t="n">
         <v>18200</v>
       </c>
-      <c r="H82" s="5" t="n"/>
-      <c r="I82" s="5" t="n"/>
-      <c r="J82" s="8" t="n"/>
-      <c r="K82" s="4" t="inlineStr"/>
-      <c r="L82" s="4" t="inlineStr"/>
+      <c r="H82" s="5" t="n">
+        <v>449.08</v>
+      </c>
+      <c r="I82" s="5" t="n">
+        <v>8981.6</v>
+      </c>
+      <c r="J82" s="9" t="n">
+        <v>0.5065054945054945</v>
+      </c>
+      <c r="K82" s="4" t="inlineStr">
+        <is>
+          <t>dn.ru, LD Pride 47.20.В-Н.Р GAS 3/4" полнопроходной, на 02.11.2026</t>
+        </is>
+      </c>
+      <c r="L82" s="4" t="inlineStr">
+        <is>
+          <t>LD Pride 47.20.В-Н.Р вместо VALTEC VT.218.N.05</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="36" customHeight="1">
       <c r="A83" s="4" t="inlineStr">
@@ -6999,11 +8251,25 @@
       <c r="G83" s="5" t="n">
         <v>9000</v>
       </c>
-      <c r="H83" s="5" t="n"/>
-      <c r="I83" s="5" t="n"/>
-      <c r="J83" s="8" t="n"/>
-      <c r="K83" s="4" t="inlineStr"/>
-      <c r="L83" s="4" t="inlineStr"/>
+      <c r="H83" s="5" t="n">
+        <v>458.42</v>
+      </c>
+      <c r="I83" s="5" t="n">
+        <v>4584.2</v>
+      </c>
+      <c r="J83" s="9" t="n">
+        <v>0.4906444444444444</v>
+      </c>
+      <c r="K83" s="4" t="inlineStr">
+        <is>
+          <t>dn.ru, LD Pride 47.15.В-ГШ.Р 1/2" (с полусгоном), на 24.11.2026</t>
+        </is>
+      </c>
+      <c r="L83" s="4" t="inlineStr">
+        <is>
+          <t>LD Pride 47.15.В-ГШ.Р вместо VALTEC VT.226.N.04</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="36" customHeight="1">
       <c r="A84" s="4" t="inlineStr">
@@ -7033,11 +8299,25 @@
       <c r="G84" s="5" t="n">
         <v>13200</v>
       </c>
-      <c r="H84" s="5" t="n"/>
-      <c r="I84" s="5" t="n"/>
-      <c r="J84" s="8" t="n"/>
-      <c r="K84" s="4" t="inlineStr"/>
-      <c r="L84" s="4" t="inlineStr"/>
+      <c r="H84" s="5" t="n">
+        <v>622.5700000000001</v>
+      </c>
+      <c r="I84" s="5" t="n">
+        <v>6225.700000000001</v>
+      </c>
+      <c r="J84" s="9" t="n">
+        <v>0.5283560606060606</v>
+      </c>
+      <c r="K84" s="4" t="inlineStr">
+        <is>
+          <t>dn.ru, LD Pride 47.20.В-НкГк.Р 3/4" полнопроходной, на 26.10.2026</t>
+        </is>
+      </c>
+      <c r="L84" s="4" t="inlineStr">
+        <is>
+          <t>LD Pride 47.20.В-НкГк.Р вместо VALTEC VT.226.N.05</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="36" customHeight="1">
       <c r="A85" s="4" t="inlineStr">
@@ -7069,7 +8349,7 @@
       </c>
       <c r="H85" s="5" t="n"/>
       <c r="I85" s="5" t="n"/>
-      <c r="J85" s="8" t="n"/>
+      <c r="J85" s="10" t="n"/>
       <c r="K85" s="4" t="inlineStr"/>
       <c r="L85" s="4" t="inlineStr"/>
     </row>
@@ -7103,7 +8383,7 @@
       </c>
       <c r="H86" s="5" t="n"/>
       <c r="I86" s="5" t="n"/>
-      <c r="J86" s="8" t="n"/>
+      <c r="J86" s="10" t="n"/>
       <c r="K86" s="4" t="inlineStr"/>
       <c r="L86" s="4" t="inlineStr"/>
     </row>
@@ -7137,7 +8417,7 @@
       </c>
       <c r="H87" s="5" t="n"/>
       <c r="I87" s="5" t="n"/>
-      <c r="J87" s="8" t="n"/>
+      <c r="J87" s="10" t="n"/>
       <c r="K87" s="4" t="inlineStr"/>
       <c r="L87" s="4" t="inlineStr"/>
     </row>
@@ -7169,38 +8449,48 @@
       <c r="G88" s="5" t="n">
         <v>9600</v>
       </c>
-      <c r="H88" s="5" t="n"/>
-      <c r="I88" s="5" t="n"/>
-      <c r="J88" s="8" t="n"/>
-      <c r="K88" s="4" t="inlineStr"/>
+      <c r="H88" s="5" t="n">
+        <v>552.29</v>
+      </c>
+      <c r="I88" s="5" t="n">
+        <v>5522.9</v>
+      </c>
+      <c r="J88" s="9" t="n">
+        <v>0.4246979166666667</v>
+      </c>
+      <c r="K88" s="4" t="inlineStr">
+        <is>
+          <t>dn.ru, ГАЛЛОП Практик 120 1" Ду25 Ру16, на 01.12.2026</t>
+        </is>
+      </c>
       <c r="L88" s="4" t="inlineStr"/>
     </row>
     <row r="89" ht="36" customHeight="1">
-      <c r="A89" s="9" t="inlineStr"/>
-      <c r="B89" s="9" t="inlineStr"/>
-      <c r="C89" s="9" t="inlineStr">
+      <c r="A89" s="12" t="inlineStr"/>
+      <c r="B89" s="12" t="inlineStr"/>
+      <c r="C89" s="12" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="D89" s="9" t="inlineStr"/>
-      <c r="E89" s="9" t="inlineStr"/>
-      <c r="F89" s="9" t="inlineStr"/>
-      <c r="G89" s="10">
+      <c r="D89" s="12" t="inlineStr"/>
+      <c r="E89" s="12" t="inlineStr"/>
+      <c r="F89" s="12" t="inlineStr"/>
+      <c r="G89" s="13">
         <f>SUM(G2:G88)</f>
         <v/>
       </c>
-      <c r="H89" s="9" t="inlineStr"/>
-      <c r="I89" s="10">
+      <c r="H89" s="12" t="inlineStr"/>
+      <c r="I89" s="13">
         <f>SUM(I2:I88)</f>
         <v/>
       </c>
-      <c r="J89" s="11">
+      <c r="J89" s="14">
         <f>1-I89/G89</f>
         <v/>
       </c>
-      <c r="K89" s="12" t="n"/>
-      <c r="L89" s="12" t="n"/>
+      <c r="K89" s="15" t="n"/>
+      <c r="L89" s="15" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/SAKHALIN_11201_11202.xlsx
+++ b/SAKHALIN_11201_11202.xlsx
@@ -96,7 +96,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -123,9 +123,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1597,10 +1594,20 @@
       <c r="G8" s="5" t="n">
         <v>20766.7</v>
       </c>
-      <c r="H8" s="5" t="n"/>
-      <c r="I8" s="5" t="n"/>
-      <c r="J8" s="10" t="n"/>
-      <c r="K8" s="4" t="inlineStr"/>
+      <c r="H8" s="5" t="n">
+        <v>1938.16</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>19381.6</v>
+      </c>
+      <c r="J8" s="8" t="n">
+        <v>0.06669812729032532</v>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>[ОЦЕНКА] цена с НДС = НМЦ×1,22×0.85 (публичной цены нет; ПК65 Цветлит ZW80003 (Беларусь, ЕАЭС) — цена только у дилеров п</t>
+        </is>
+      </c>
       <c r="L8" s="4" t="inlineStr"/>
     </row>
     <row r="9" ht="36" customHeight="1">
@@ -1763,10 +1770,20 @@
       <c r="G12" s="5" t="n">
         <v>393400</v>
       </c>
-      <c r="H12" s="5" t="n"/>
-      <c r="I12" s="5" t="n"/>
-      <c r="J12" s="10" t="n"/>
-      <c r="K12" s="4" t="inlineStr"/>
+      <c r="H12" s="5" t="n">
+        <v>5245.15</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>367160.5</v>
+      </c>
+      <c r="J12" s="8" t="n">
+        <v>0.06669928825622784</v>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[ОЦЕНКА] цена с НДС = НМЦ×1,22×0.85 (публичной цены нет; спецдеталь к указателю уровня Т-229Б (ДТКЗ, Дорогобужкотломаш) </t>
+        </is>
+      </c>
       <c r="L12" s="4" t="inlineStr"/>
     </row>
     <row r="13" ht="36" customHeight="1">
@@ -1797,10 +1814,20 @@
       <c r="G13" s="5" t="n">
         <v>89133.8</v>
       </c>
-      <c r="H13" s="5" t="n"/>
-      <c r="I13" s="5" t="n"/>
-      <c r="J13" s="10" t="n"/>
-      <c r="K13" s="4" t="inlineStr"/>
+      <c r="H13" s="5" t="n">
+        <v>594.21</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>83189.40000000001</v>
+      </c>
+      <c r="J13" s="8" t="n">
+        <v>0.06669075031020766</v>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[ОЦЕНКА] цена с НДС = НМЦ×1,22×0.85 (публичной цены нет; спецдеталь к указателю уровня Т-229Б (ДТКЗ, Дорогобужкотломаш) </t>
+        </is>
+      </c>
       <c r="L13" s="4" t="inlineStr"/>
     </row>
     <row r="14" ht="36" customHeight="1">
@@ -1831,11 +1858,25 @@
       <c r="G14" s="5" t="n">
         <v>47706.68</v>
       </c>
-      <c r="H14" s="5" t="n"/>
-      <c r="I14" s="5" t="n"/>
-      <c r="J14" s="10" t="n"/>
-      <c r="K14" s="4" t="inlineStr"/>
-      <c r="L14" s="4" t="inlineStr"/>
+      <c r="H14" s="5" t="n">
+        <v>15015.7</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>60062.8</v>
+      </c>
+      <c r="J14" s="10" t="n">
+        <v>-0.2590018840128887</v>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>[ПРОКСИ] dn.ru на 27.10.2026: PA-DA-052 (F03/F05, кв.11) 6 791,13 + пневмораспределитель 4M310-08 DC24V 3 753,33 + БКВ A</t>
+        </is>
+      </c>
+      <c r="L14" s="4" t="inlineStr">
+        <is>
+          <t>DN.ru PA-DA-052 + 4M310-08 DC24V + ALS200D (КНР)</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="36" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
@@ -1865,11 +1906,25 @@
       <c r="G15" s="5" t="n">
         <v>62453.32</v>
       </c>
-      <c r="H15" s="5" t="n"/>
-      <c r="I15" s="5" t="n"/>
-      <c r="J15" s="10" t="n"/>
-      <c r="K15" s="4" t="inlineStr"/>
-      <c r="L15" s="4" t="inlineStr"/>
+      <c r="H15" s="5" t="n">
+        <v>19368.72</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>77474.88</v>
+      </c>
+      <c r="J15" s="10" t="n">
+        <v>-0.2405246030155004</v>
+      </c>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>[ПРОКСИ] dn.ru на 27.10.2026: PA-DA-083 (F05/F07, кв.17, нужна втулка на кв.14) 11 627,82 + 4M310-08 DC24V 3 753,33 + AL</t>
+        </is>
+      </c>
+      <c r="L15" s="4" t="inlineStr">
+        <is>
+          <t>DN.ru PA-DA-083 + 4M310-08 DC24V + ALS200D (КНР)</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="36" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
@@ -2085,7 +2140,7 @@
       <c r="I20" s="5" t="n">
         <v>149418</v>
       </c>
-      <c r="J20" s="11" t="n">
+      <c r="J20" s="10" t="n">
         <v>-2.206394849785408</v>
       </c>
       <c r="K20" s="4" t="inlineStr">
@@ -2129,7 +2184,7 @@
       <c r="I21" s="5" t="n">
         <v>35226</v>
       </c>
-      <c r="J21" s="11" t="n">
+      <c r="J21" s="10" t="n">
         <v>-2.072031311591498</v>
       </c>
       <c r="K21" s="4" t="inlineStr">
@@ -2167,11 +2222,25 @@
       <c r="G22" s="5" t="n">
         <v>26450</v>
       </c>
-      <c r="H22" s="5" t="n"/>
-      <c r="I22" s="5" t="n"/>
-      <c r="J22" s="10" t="n"/>
-      <c r="K22" s="4" t="inlineStr"/>
-      <c r="L22" s="4" t="inlineStr"/>
+      <c r="H22" s="5" t="n">
+        <v>4603.96</v>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>23019.8</v>
+      </c>
+      <c r="J22" s="8" t="n">
+        <v>0.1296862003780719</v>
+      </c>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>[ПРОКСИ] pimtasplast.ru на 27.10.2026: кран ПВХ Pimtas PN16 EPDM&amp;PTFE d63 (DN50) 5 115,51 (клеевой; резьбовой ВР — уточн</t>
+        </is>
+      </c>
+      <c r="L22" s="4" t="inlineStr">
+        <is>
+          <t>Pimtas PVC-U PN16 EPDM</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="36" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
@@ -2201,11 +2270,25 @@
       <c r="G23" s="5" t="n">
         <v>8966.65</v>
       </c>
-      <c r="H23" s="5" t="n"/>
-      <c r="I23" s="5" t="n"/>
-      <c r="J23" s="10" t="n"/>
-      <c r="K23" s="4" t="inlineStr"/>
-      <c r="L23" s="4" t="inlineStr"/>
+      <c r="H23" s="5" t="n">
+        <v>1548.71</v>
+      </c>
+      <c r="I23" s="5" t="n">
+        <v>7743.55</v>
+      </c>
+      <c r="J23" s="8" t="n">
+        <v>0.13640545800271</v>
+      </c>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>[ПРОКСИ] pimtasplast.ru на 27.10.2026: кран ПВХ Pimtas PN16 EPDM&amp;PTFE d20 (DN15) 1 720,79</t>
+        </is>
+      </c>
+      <c r="L23" s="4" t="inlineStr">
+        <is>
+          <t>Pimtas PVC-U PN16 EPDM</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="36" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
@@ -2499,10 +2582,20 @@
       <c r="G30" s="5" t="n">
         <v>24866.7</v>
       </c>
-      <c r="H30" s="5" t="n"/>
-      <c r="I30" s="5" t="n"/>
-      <c r="J30" s="10" t="n"/>
-      <c r="K30" s="4" t="inlineStr"/>
+      <c r="H30" s="5" t="n">
+        <v>2320.81</v>
+      </c>
+      <c r="I30" s="5" t="n">
+        <v>23208.1</v>
+      </c>
+      <c r="J30" s="8" t="n">
+        <v>0.06669964249377691</v>
+      </c>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>[ОЦЕНКА] цена с НДС = НМЦ×1,22×0.85 (публичной цены нет; шар 3010.СB02 Ду100 — запчасть Benarmo, отдельно не продаётся в</t>
+        </is>
+      </c>
       <c r="L30" s="4" t="inlineStr"/>
     </row>
     <row r="31" ht="36" customHeight="1">
@@ -2533,10 +2626,20 @@
       <c r="G31" s="5" t="n">
         <v>11600</v>
       </c>
-      <c r="H31" s="5" t="n"/>
-      <c r="I31" s="5" t="n"/>
-      <c r="J31" s="10" t="n"/>
-      <c r="K31" s="4" t="inlineStr"/>
+      <c r="H31" s="5" t="n">
+        <v>1082.63</v>
+      </c>
+      <c r="I31" s="5" t="n">
+        <v>10826.3</v>
+      </c>
+      <c r="J31" s="8" t="n">
+        <v>0.06669827586206889</v>
+      </c>
+      <c r="K31" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[ОЦЕНКА] цена с НДС = НМЦ×1,22×0.85 (публичной цены нет; шар 3010.СB02 Ду80 — запчасть Benarmo, отдельно не продаётся в </t>
+        </is>
+      </c>
       <c r="L31" s="4" t="inlineStr"/>
     </row>
     <row r="32" ht="36" customHeight="1">
@@ -2567,10 +2670,20 @@
       <c r="G32" s="5" t="n">
         <v>5500.02</v>
       </c>
-      <c r="H32" s="5" t="n"/>
-      <c r="I32" s="5" t="n"/>
-      <c r="J32" s="10" t="n"/>
-      <c r="K32" s="4" t="inlineStr"/>
+      <c r="H32" s="5" t="n">
+        <v>855.53</v>
+      </c>
+      <c r="I32" s="5" t="n">
+        <v>5133.18</v>
+      </c>
+      <c r="J32" s="8" t="n">
+        <v>0.06669793928022083</v>
+      </c>
+      <c r="K32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[ОЦЕНКА] цена с НДС = НМЦ×1,22×0.85 (публичной цены нет; шар 3010.СB02 Ду65 — запчасть Benarmo, отдельно не продаётся в </t>
+        </is>
+      </c>
       <c r="L32" s="4" t="inlineStr"/>
     </row>
     <row r="33" ht="36" customHeight="1">
@@ -2601,10 +2714,20 @@
       <c r="G33" s="5" t="n">
         <v>3960</v>
       </c>
-      <c r="H33" s="5" t="n"/>
-      <c r="I33" s="5" t="n"/>
-      <c r="J33" s="10" t="n"/>
-      <c r="K33" s="4" t="inlineStr"/>
+      <c r="H33" s="5" t="n">
+        <v>615.98</v>
+      </c>
+      <c r="I33" s="5" t="n">
+        <v>3695.88</v>
+      </c>
+      <c r="J33" s="8" t="n">
+        <v>0.0666969696969697</v>
+      </c>
+      <c r="K33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[ОЦЕНКА] цена с НДС = НМЦ×1,22×0.85 (публичной цены нет; шар 3010.СB02 Ду50 — запчасть Benarmo, отдельно не продаётся в </t>
+        </is>
+      </c>
       <c r="L33" s="4" t="inlineStr"/>
     </row>
     <row r="34" ht="36" customHeight="1">
@@ -2635,10 +2758,20 @@
       <c r="G34" s="5" t="n">
         <v>457539.99</v>
       </c>
-      <c r="H34" s="5" t="n"/>
-      <c r="I34" s="5" t="n"/>
-      <c r="J34" s="10" t="n"/>
-      <c r="K34" s="4" t="inlineStr"/>
+      <c r="H34" s="5" t="n">
+        <v>142340.69</v>
+      </c>
+      <c r="I34" s="5" t="n">
+        <v>427022.07</v>
+      </c>
+      <c r="J34" s="8" t="n">
+        <v>0.0667000058289986</v>
+      </c>
+      <c r="K34" s="4" t="inlineStr">
+        <is>
+          <t>[ОЦЕНКА] цена с НДС = НМЦ×1,22×0.85 (публичной цены нет; КО 200.16.3311 исп.F (пульпа) — обозначение не найдено в открыт</t>
+        </is>
+      </c>
       <c r="L34" s="4" t="inlineStr"/>
     </row>
     <row r="35" ht="36" customHeight="1">
@@ -2763,7 +2896,7 @@
       <c r="I37" s="5" t="n">
         <v>19339.2</v>
       </c>
-      <c r="J37" s="11" t="n">
+      <c r="J37" s="10" t="n">
         <v>-0.1420769416111156</v>
       </c>
       <c r="K37" s="4" t="inlineStr">
@@ -2805,10 +2938,20 @@
       <c r="G38" s="5" t="n">
         <v>477666.65</v>
       </c>
-      <c r="H38" s="5" t="n"/>
-      <c r="I38" s="5" t="n"/>
-      <c r="J38" s="10" t="n"/>
-      <c r="K38" s="4" t="inlineStr"/>
+      <c r="H38" s="5" t="n">
+        <v>89161.25</v>
+      </c>
+      <c r="I38" s="5" t="n">
+        <v>445806.25</v>
+      </c>
+      <c r="J38" s="8" t="n">
+        <v>0.06670007211095852</v>
+      </c>
+      <c r="K38" s="4" t="inlineStr">
+        <is>
+          <t>[ОЦЕНКА] цена с НДС = НМЦ×1,22×0.85 (публичной цены нет; АРМАТЭК серия АМ с пневмоприводом/ЭПР/БКВ — цены только по опро</t>
+        </is>
+      </c>
       <c r="L38" s="4" t="inlineStr"/>
     </row>
     <row r="39" ht="36" customHeight="1">
@@ -2839,10 +2982,20 @@
       <c r="G39" s="5" t="n">
         <v>454900</v>
       </c>
-      <c r="H39" s="5" t="n"/>
-      <c r="I39" s="5" t="n"/>
-      <c r="J39" s="10" t="n"/>
-      <c r="K39" s="4" t="inlineStr"/>
+      <c r="H39" s="5" t="n">
+        <v>84911.63</v>
+      </c>
+      <c r="I39" s="5" t="n">
+        <v>424558.15</v>
+      </c>
+      <c r="J39" s="8" t="n">
+        <v>0.06670004396570672</v>
+      </c>
+      <c r="K39" s="4" t="inlineStr">
+        <is>
+          <t>[ОЦЕНКА] цена с НДС = НМЦ×1,22×0.85 (публичной цены нет; АРМАТЭК серия АМ с пневмоприводом/ЭПР/БКВ — цены только по опро</t>
+        </is>
+      </c>
       <c r="L39" s="4" t="inlineStr"/>
     </row>
     <row r="40" ht="36" customHeight="1">
@@ -2873,10 +3026,20 @@
       <c r="G40" s="5" t="n">
         <v>1493299.95</v>
       </c>
-      <c r="H40" s="5" t="n"/>
-      <c r="I40" s="5" t="n"/>
-      <c r="J40" s="10" t="n"/>
-      <c r="K40" s="4" t="inlineStr"/>
+      <c r="H40" s="5" t="n">
+        <v>92913.12</v>
+      </c>
+      <c r="I40" s="5" t="n">
+        <v>1393696.8</v>
+      </c>
+      <c r="J40" s="8" t="n">
+        <v>0.06670002901962202</v>
+      </c>
+      <c r="K40" s="4" t="inlineStr">
+        <is>
+          <t>[ОЦЕНКА] цена с НДС = НМЦ×1,22×0.85 (публичной цены нет; АРМАТЭК серия АМ с пневмоприводом/ЭПР/БКВ — цены только по опро</t>
+        </is>
+      </c>
       <c r="L40" s="4" t="inlineStr"/>
     </row>
     <row r="41" ht="36" customHeight="1">
@@ -2913,7 +3076,7 @@
       <c r="I41" s="5" t="n">
         <v>4625.1</v>
       </c>
-      <c r="J41" s="11" t="n">
+      <c r="J41" s="10" t="n">
         <v>-0.3406086956521739</v>
       </c>
       <c r="K41" s="4" t="inlineStr">
@@ -3091,11 +3254,25 @@
       <c r="G45" s="5" t="n">
         <v>11600</v>
       </c>
-      <c r="H45" s="5" t="n"/>
-      <c r="I45" s="5" t="n"/>
-      <c r="J45" s="10" t="n"/>
-      <c r="K45" s="4" t="inlineStr"/>
-      <c r="L45" s="4" t="inlineStr"/>
+      <c r="H45" s="5" t="n">
+        <v>3510.95</v>
+      </c>
+      <c r="I45" s="5" t="n">
+        <v>35109.5</v>
+      </c>
+      <c r="J45" s="10" t="n">
+        <v>-2.026681034482758</v>
+      </c>
+      <c r="K45" s="4" t="inlineStr">
+        <is>
+          <t>[ПРОКСИ] pimtasplast.ru на 27.10.2026: кран ПВХ Pimtas промышл.  клеевой  PN16  FKM&amp;PTFE d25 — 3 901.05</t>
+        </is>
+      </c>
+      <c r="L45" s="4" t="inlineStr">
+        <is>
+          <t>Pimtas PVC-U PN16 FKM/PTFE</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="36" customHeight="1">
       <c r="A46" s="4" t="inlineStr">
@@ -3125,11 +3302,25 @@
       <c r="G46" s="5" t="n">
         <v>17400</v>
       </c>
-      <c r="H46" s="5" t="n"/>
-      <c r="I46" s="5" t="n"/>
-      <c r="J46" s="10" t="n"/>
-      <c r="K46" s="4" t="inlineStr"/>
-      <c r="L46" s="4" t="inlineStr"/>
+      <c r="H46" s="5" t="n">
+        <v>4180.7</v>
+      </c>
+      <c r="I46" s="5" t="n">
+        <v>41807</v>
+      </c>
+      <c r="J46" s="10" t="n">
+        <v>-1.402701149425287</v>
+      </c>
+      <c r="K46" s="4" t="inlineStr">
+        <is>
+          <t>[ПРОКСИ] pimtasplast.ru на 27.10.2026: кран ПВХ Pimtas промышл.  клеевой  PN16  FKM&amp;PTFE d32 — 4 645.22</t>
+        </is>
+      </c>
+      <c r="L46" s="4" t="inlineStr">
+        <is>
+          <t>Pimtas PVC-U PN16 FKM/PTFE</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="36" customHeight="1">
       <c r="A47" s="4" t="inlineStr">
@@ -3159,11 +3350,25 @@
       <c r="G47" s="5" t="n">
         <v>23400</v>
       </c>
-      <c r="H47" s="5" t="n"/>
-      <c r="I47" s="5" t="n"/>
-      <c r="J47" s="10" t="n"/>
-      <c r="K47" s="4" t="inlineStr"/>
-      <c r="L47" s="4" t="inlineStr"/>
+      <c r="H47" s="5" t="n">
+        <v>5418.05</v>
+      </c>
+      <c r="I47" s="5" t="n">
+        <v>54180.5</v>
+      </c>
+      <c r="J47" s="10" t="n">
+        <v>-1.315405982905983</v>
+      </c>
+      <c r="K47" s="4" t="inlineStr">
+        <is>
+          <t>[ПРОКСИ] pimtasplast.ru на 27.10.2026: кран ПВХ Pimtas промышл.  клеевой  PN16  FKM&amp;PTFE d40 — 6 020.05</t>
+        </is>
+      </c>
+      <c r="L47" s="4" t="inlineStr">
+        <is>
+          <t>Pimtas PVC-U PN16 FKM/PTFE</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="36" customHeight="1">
       <c r="A48" s="4" t="inlineStr">
@@ -3193,11 +3398,25 @@
       <c r="G48" s="5" t="n">
         <v>24800</v>
       </c>
-      <c r="H48" s="5" t="n"/>
-      <c r="I48" s="5" t="n"/>
-      <c r="J48" s="10" t="n"/>
-      <c r="K48" s="4" t="inlineStr"/>
-      <c r="L48" s="4" t="inlineStr"/>
+      <c r="H48" s="5" t="n">
+        <v>6756.74</v>
+      </c>
+      <c r="I48" s="5" t="n">
+        <v>67567.39999999999</v>
+      </c>
+      <c r="J48" s="10" t="n">
+        <v>-1.724491935483871</v>
+      </c>
+      <c r="K48" s="4" t="inlineStr">
+        <is>
+          <t>[ПРОКСИ] pimtasplast.ru на 27.10.2026: кран ПВХ Pimtas промышл.  клеевой  PN16  FKM&amp;PTFE d50 — 7 507.49</t>
+        </is>
+      </c>
+      <c r="L48" s="4" t="inlineStr">
+        <is>
+          <t>Pimtas PVC-U PN16 FKM/PTFE</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="36" customHeight="1">
       <c r="A49" s="4" t="inlineStr">
@@ -3227,10 +3446,20 @@
       <c r="G49" s="5" t="n">
         <v>60660</v>
       </c>
-      <c r="H49" s="5" t="n"/>
-      <c r="I49" s="5" t="n"/>
-      <c r="J49" s="10" t="n"/>
-      <c r="K49" s="4" t="inlineStr"/>
+      <c r="H49" s="5" t="n">
+        <v>28306.99</v>
+      </c>
+      <c r="I49" s="5" t="n">
+        <v>56613.98</v>
+      </c>
+      <c r="J49" s="8" t="n">
+        <v>0.06669996702934378</v>
+      </c>
+      <c r="K49" s="4" t="inlineStr">
+        <is>
+          <t>[ОЦЕНКА] цена с НДС = НМЦ×1,22×0.85 (публичной цены нет; CFB-A27T-R1 — производитель не установлен (вероятно импорт); РФ</t>
+        </is>
+      </c>
       <c r="L49" s="4" t="inlineStr"/>
     </row>
     <row r="50" ht="36" customHeight="1">
@@ -3399,7 +3628,7 @@
       <c r="I53" s="5" t="n">
         <v>64362.60000000001</v>
       </c>
-      <c r="J53" s="11" t="n">
+      <c r="J53" s="10" t="n">
         <v>-0.07056886227544923</v>
       </c>
       <c r="K53" s="4" t="inlineStr">
@@ -3437,10 +3666,20 @@
       <c r="G54" s="5" t="n">
         <v>108920</v>
       </c>
-      <c r="H54" s="5" t="n"/>
-      <c r="I54" s="5" t="n"/>
-      <c r="J54" s="10" t="n"/>
-      <c r="K54" s="4" t="inlineStr"/>
+      <c r="H54" s="5" t="n">
+        <v>25413.76</v>
+      </c>
+      <c r="I54" s="5" t="n">
+        <v>101655.04</v>
+      </c>
+      <c r="J54" s="8" t="n">
+        <v>0.06669996327579886</v>
+      </c>
+      <c r="K54" s="4" t="inlineStr">
+        <is>
+          <t>[ОЦЕНКА] цена с НДС = НМЦ×1,22×0.85 (публичной цены нет; диск тормозной ЯЛБИ.741224.046 к МЭОФ-1600 — запчасть ЗЭиМ, тол</t>
+        </is>
+      </c>
       <c r="L54" s="4" t="inlineStr"/>
     </row>
     <row r="55" ht="36" customHeight="1">
@@ -3471,10 +3710,20 @@
       <c r="G55" s="5" t="n">
         <v>38900</v>
       </c>
-      <c r="H55" s="5" t="n"/>
-      <c r="I55" s="5" t="n"/>
-      <c r="J55" s="10" t="n"/>
-      <c r="K55" s="4" t="inlineStr"/>
+      <c r="H55" s="5" t="n">
+        <v>3630.54</v>
+      </c>
+      <c r="I55" s="5" t="n">
+        <v>36305.4</v>
+      </c>
+      <c r="J55" s="8" t="n">
+        <v>0.06669922879177381</v>
+      </c>
+      <c r="K55" s="4" t="inlineStr">
+        <is>
+          <t>[ОЦЕНКА] цена с НДС = НМЦ×1,22×0.85 (публичной цены нет; ЗИП к затворам АРМАТЭК серии АМ — только у производителя)</t>
+        </is>
+      </c>
       <c r="L55" s="4" t="inlineStr"/>
     </row>
     <row r="56" ht="36" customHeight="1">
@@ -3505,10 +3754,20 @@
       <c r="G56" s="5" t="n">
         <v>41600</v>
       </c>
-      <c r="H56" s="5" t="n"/>
-      <c r="I56" s="5" t="n"/>
-      <c r="J56" s="10" t="n"/>
-      <c r="K56" s="4" t="inlineStr"/>
+      <c r="H56" s="5" t="n">
+        <v>3882.53</v>
+      </c>
+      <c r="I56" s="5" t="n">
+        <v>38825.3</v>
+      </c>
+      <c r="J56" s="8" t="n">
+        <v>0.06669951923076922</v>
+      </c>
+      <c r="K56" s="4" t="inlineStr">
+        <is>
+          <t>[ОЦЕНКА] цена с НДС = НМЦ×1,22×0.85 (публичной цены нет; ЗИП к затворам АРМАТЭК серии АМ — только у производителя)</t>
+        </is>
+      </c>
       <c r="L56" s="4" t="inlineStr"/>
     </row>
     <row r="57" ht="36" customHeight="1">
@@ -3539,10 +3798,20 @@
       <c r="G57" s="5" t="n">
         <v>44700</v>
       </c>
-      <c r="H57" s="5" t="n"/>
-      <c r="I57" s="5" t="n"/>
-      <c r="J57" s="10" t="n"/>
-      <c r="K57" s="4" t="inlineStr"/>
+      <c r="H57" s="5" t="n">
+        <v>4171.85</v>
+      </c>
+      <c r="I57" s="5" t="n">
+        <v>41718.5</v>
+      </c>
+      <c r="J57" s="8" t="n">
+        <v>0.06670022371364648</v>
+      </c>
+      <c r="K57" s="4" t="inlineStr">
+        <is>
+          <t>[ОЦЕНКА] цена с НДС = НМЦ×1,22×0.85 (публичной цены нет; ЗИП к затворам АРМАТЭК серии АМ — только у производителя)</t>
+        </is>
+      </c>
       <c r="L57" s="4" t="inlineStr"/>
     </row>
     <row r="58" ht="36" customHeight="1">
@@ -3711,7 +3980,7 @@
       <c r="I61" s="5" t="n">
         <v>37418.4</v>
       </c>
-      <c r="J61" s="11" t="n">
+      <c r="J61" s="10" t="n">
         <v>-0.02375923392612855</v>
       </c>
       <c r="K61" s="4" t="inlineStr">
@@ -3841,10 +4110,20 @@
       <c r="G64" s="5" t="n">
         <v>563720</v>
       </c>
-      <c r="H64" s="5" t="n"/>
-      <c r="I64" s="5" t="n"/>
-      <c r="J64" s="10" t="n"/>
-      <c r="K64" s="4" t="inlineStr"/>
+      <c r="H64" s="5" t="n">
+        <v>131529.97</v>
+      </c>
+      <c r="I64" s="5" t="n">
+        <v>526119.88</v>
+      </c>
+      <c r="J64" s="8" t="n">
+        <v>0.06669999290427875</v>
+      </c>
+      <c r="K64" s="4" t="inlineStr">
+        <is>
+          <t>[ОЦЕНКА] цена с НДС = НМЦ×1,22×0.85 (публичной цены нет; КО 200.16.3312 — обозначение не найдено в открытых каталогах; К</t>
+        </is>
+      </c>
       <c r="L64" s="4" t="inlineStr"/>
     </row>
     <row r="65" ht="36" customHeight="1">
@@ -3875,10 +4154,20 @@
       <c r="G65" s="5" t="n">
         <v>1013110</v>
       </c>
-      <c r="H65" s="5" t="n"/>
-      <c r="I65" s="5" t="n"/>
-      <c r="J65" s="10" t="n"/>
-      <c r="K65" s="4" t="inlineStr"/>
+      <c r="H65" s="5" t="n">
+        <v>594107.91</v>
+      </c>
+      <c r="I65" s="5" t="n">
+        <v>594107.91</v>
+      </c>
+      <c r="J65" s="9" t="n">
+        <v>0.4135800554727522</v>
+      </c>
+      <c r="K65" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[ПРОКСИ] задвижка 30с946нж Ду500 Ру6 «от 294 397» (vkomplekt.spb.ru, +10% к «от») + ПЭМ-В-1000 с КИМ2 ≈ ГЗ-В.900/24 280 </t>
+        </is>
+      </c>
       <c r="L65" s="4" t="inlineStr"/>
     </row>
     <row r="66" ht="36" customHeight="1">
@@ -3909,10 +4198,20 @@
       <c r="G66" s="5" t="n">
         <v>230880</v>
       </c>
-      <c r="H66" s="5" t="n"/>
-      <c r="I66" s="5" t="n"/>
-      <c r="J66" s="10" t="n"/>
-      <c r="K66" s="4" t="inlineStr"/>
+      <c r="H66" s="5" t="n">
+        <v>8978.35</v>
+      </c>
+      <c r="I66" s="5" t="n">
+        <v>215480.4</v>
+      </c>
+      <c r="J66" s="8" t="n">
+        <v>0.06669958419958422</v>
+      </c>
+      <c r="K66" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[ОЦЕНКА] цена с НДС = НМЦ×1,22×0.85 (публичной цены нет; спецдеталь к указателю уровня Т-229Б (ДТКЗ, Дорогобужкотломаш) </t>
+        </is>
+      </c>
       <c r="L66" s="4" t="inlineStr"/>
     </row>
     <row r="67" ht="36" customHeight="1">
@@ -3943,10 +4242,20 @@
       <c r="G67" s="5" t="n">
         <v>232920</v>
       </c>
-      <c r="H67" s="5" t="n"/>
-      <c r="I67" s="5" t="n"/>
-      <c r="J67" s="10" t="n"/>
-      <c r="K67" s="4" t="inlineStr"/>
+      <c r="H67" s="5" t="n">
+        <v>54346.06</v>
+      </c>
+      <c r="I67" s="5" t="n">
+        <v>217384.24</v>
+      </c>
+      <c r="J67" s="8" t="n">
+        <v>0.06669998282672163</v>
+      </c>
+      <c r="K67" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[ОЦЕНКА] цена с НДС = НМЦ×1,22×0.85 (публичной цены нет; 1с-13-3ЭД под AUMA SA10.2 (энергетический вентиль, ЧЗЭМ) — цен </t>
+        </is>
+      </c>
       <c r="L67" s="4" t="inlineStr"/>
     </row>
     <row r="68" ht="36" customHeight="1">
@@ -3977,10 +4286,20 @@
       <c r="G68" s="5" t="n">
         <v>556640</v>
       </c>
-      <c r="H68" s="5" t="n"/>
-      <c r="I68" s="5" t="n"/>
-      <c r="J68" s="10" t="n"/>
-      <c r="K68" s="4" t="inlineStr"/>
+      <c r="H68" s="5" t="n">
+        <v>345046.5</v>
+      </c>
+      <c r="I68" s="5" t="n">
+        <v>345046.5</v>
+      </c>
+      <c r="J68" s="9" t="n">
+        <v>0.3801262934751365</v>
+      </c>
+      <c r="K68" s="4" t="inlineStr">
+        <is>
+          <t>[ПРОКСИ] МЭО-1600/25-0,25У-92КБ 127 795 (elaparat.shop, ЧЗ Электроаппарат, на 27.10.2026) ×3 за фланцевое исполнение + и</t>
+        </is>
+      </c>
       <c r="L68" s="4" t="inlineStr"/>
     </row>
     <row r="69" ht="36" customHeight="1">
@@ -4061,7 +4380,7 @@
       <c r="I70" s="5" t="n">
         <v>14910.67</v>
       </c>
-      <c r="J70" s="11" t="n">
+      <c r="J70" s="10" t="n">
         <v>-0.06861014539181687</v>
       </c>
       <c r="K70" s="4" t="inlineStr">
@@ -4149,7 +4468,7 @@
       <c r="I72" s="5" t="n">
         <v>171529.4</v>
       </c>
-      <c r="J72" s="11" t="n">
+      <c r="J72" s="10" t="n">
         <v>0.01796135667570209</v>
       </c>
       <c r="K72" s="4" t="inlineStr">
@@ -4417,7 +4736,7 @@
       <c r="I78" s="5" t="n">
         <v>58159.8</v>
       </c>
-      <c r="J78" s="11" t="n">
+      <c r="J78" s="10" t="n">
         <v>-0.02424669355264775</v>
       </c>
       <c r="K78" s="4" t="inlineStr">
@@ -4505,7 +4824,7 @@
       <c r="I80" s="5" t="n">
         <v>58159.8</v>
       </c>
-      <c r="J80" s="11" t="n">
+      <c r="J80" s="10" t="n">
         <v>-0.1888757154538021</v>
       </c>
       <c r="K80" s="4" t="inlineStr">
@@ -4549,7 +4868,7 @@
       <c r="I81" s="5" t="n">
         <v>85109.39999999999</v>
       </c>
-      <c r="J81" s="11" t="n">
+      <c r="J81" s="10" t="n">
         <v>-0.1517871570022413</v>
       </c>
       <c r="K81" s="4" t="inlineStr">
@@ -4692,31 +5011,31 @@
       <c r="L84" s="4" t="inlineStr"/>
     </row>
     <row r="85" ht="36" customHeight="1">
-      <c r="A85" s="12" t="inlineStr"/>
-      <c r="B85" s="12" t="inlineStr"/>
-      <c r="C85" s="12" t="inlineStr">
+      <c r="A85" s="11" t="inlineStr"/>
+      <c r="B85" s="11" t="inlineStr"/>
+      <c r="C85" s="11" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="D85" s="12" t="inlineStr"/>
-      <c r="E85" s="12" t="inlineStr"/>
-      <c r="F85" s="12" t="inlineStr"/>
-      <c r="G85" s="13">
+      <c r="D85" s="11" t="inlineStr"/>
+      <c r="E85" s="11" t="inlineStr"/>
+      <c r="F85" s="11" t="inlineStr"/>
+      <c r="G85" s="12">
         <f>SUM(G2:G84)</f>
         <v/>
       </c>
-      <c r="H85" s="12" t="inlineStr"/>
-      <c r="I85" s="13">
+      <c r="H85" s="11" t="inlineStr"/>
+      <c r="I85" s="12">
         <f>SUM(I2:I84)</f>
         <v/>
       </c>
-      <c r="J85" s="14">
+      <c r="J85" s="13">
         <f>1-I85/G85</f>
         <v/>
       </c>
-      <c r="K85" s="15" t="n"/>
-      <c r="L85" s="15" t="n"/>
+      <c r="K85" s="14" t="n"/>
+      <c r="L85" s="14" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4843,7 +5162,7 @@
       <c r="I2" s="5" t="n">
         <v>6703.349999999999</v>
       </c>
-      <c r="J2" s="11" t="n">
+      <c r="J2" s="10" t="n">
         <v>-0.01106334841628964</v>
       </c>
       <c r="K2" s="4" t="inlineStr">
@@ -4887,7 +5206,7 @@
       <c r="I3" s="5" t="n">
         <v>5879.8</v>
       </c>
-      <c r="J3" s="11" t="n">
+      <c r="J3" s="10" t="n">
         <v>0.003423728813559346</v>
       </c>
       <c r="K3" s="4" t="inlineStr">
@@ -5633,10 +5952,20 @@
       <c r="G20" s="5" t="n">
         <v>173400</v>
       </c>
-      <c r="H20" s="5" t="n"/>
-      <c r="I20" s="5" t="n"/>
-      <c r="J20" s="10" t="n"/>
-      <c r="K20" s="4" t="inlineStr"/>
+      <c r="H20" s="5" t="n">
+        <v>16183.42</v>
+      </c>
+      <c r="I20" s="5" t="n">
+        <v>161834.2</v>
+      </c>
+      <c r="J20" s="8" t="n">
+        <v>0.06670011534025377</v>
+      </c>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>[ОЦЕНКА] цена с НДС = НМЦ×1,22×0.85 (публичной цены нет; ЗИП к затворам АРМАТЭК серии АМ — только у производителя)</t>
+        </is>
+      </c>
       <c r="L20" s="4" t="inlineStr"/>
     </row>
     <row r="21" ht="36" customHeight="1">
@@ -5667,10 +5996,20 @@
       <c r="G21" s="5" t="n">
         <v>260000</v>
       </c>
-      <c r="H21" s="5" t="n"/>
-      <c r="I21" s="5" t="n"/>
-      <c r="J21" s="10" t="n"/>
-      <c r="K21" s="4" t="inlineStr"/>
+      <c r="H21" s="5" t="n">
+        <v>30332.25</v>
+      </c>
+      <c r="I21" s="5" t="n">
+        <v>242658</v>
+      </c>
+      <c r="J21" s="8" t="n">
+        <v>0.06669999999999998</v>
+      </c>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>[ОЦЕНКА] цена с НДС = НМЦ×1,22×0.85 (публичной цены нет; ЗИП к затворам АРМАТЭК серии АМ — только у производителя)</t>
+        </is>
+      </c>
       <c r="L21" s="4" t="inlineStr"/>
     </row>
     <row r="22" ht="36" customHeight="1">
@@ -5701,10 +6040,20 @@
       <c r="G22" s="5" t="n">
         <v>97200</v>
       </c>
-      <c r="H22" s="5" t="n"/>
-      <c r="I22" s="5" t="n"/>
-      <c r="J22" s="10" t="n"/>
-      <c r="K22" s="4" t="inlineStr"/>
+      <c r="H22" s="5" t="n">
+        <v>9071.68</v>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>90716.8</v>
+      </c>
+      <c r="J22" s="8" t="n">
+        <v>0.06669958847736623</v>
+      </c>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>[ОЦЕНКА] цена с НДС = НМЦ×1,22×0.85 (публичной цены нет; ЗИП к затворам АРМАТЭК серии АМ — только у производителя)</t>
+        </is>
+      </c>
       <c r="L22" s="4" t="inlineStr"/>
     </row>
     <row r="23" ht="36" customHeight="1">
@@ -5735,10 +6084,20 @@
       <c r="G23" s="5" t="n">
         <v>120000</v>
       </c>
-      <c r="H23" s="5" t="n"/>
-      <c r="I23" s="5" t="n"/>
-      <c r="J23" s="10" t="n"/>
-      <c r="K23" s="4" t="inlineStr"/>
+      <c r="H23" s="5" t="n">
+        <v>11199.6</v>
+      </c>
+      <c r="I23" s="5" t="n">
+        <v>111996</v>
+      </c>
+      <c r="J23" s="8" t="n">
+        <v>0.06669999999999998</v>
+      </c>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>[ОЦЕНКА] цена с НДС = НМЦ×1,22×0.85 (публичной цены нет; ЗИП к затворам АРМАТЭК серии АМ — только у производителя)</t>
+        </is>
+      </c>
       <c r="L23" s="4" t="inlineStr"/>
     </row>
     <row r="24" ht="36" customHeight="1">
@@ -5769,10 +6128,20 @@
       <c r="G24" s="5" t="n">
         <v>11080</v>
       </c>
-      <c r="H24" s="5" t="n"/>
-      <c r="I24" s="5" t="n"/>
-      <c r="J24" s="10" t="n"/>
-      <c r="K24" s="4" t="inlineStr"/>
+      <c r="H24" s="5" t="n">
+        <v>5170.48</v>
+      </c>
+      <c r="I24" s="5" t="n">
+        <v>10340.96</v>
+      </c>
+      <c r="J24" s="8" t="n">
+        <v>0.06670036101083043</v>
+      </c>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>[ОЦЕНКА] цена с НДС = НМЦ×1,22×0.85 (публичной цены нет; ЗИП к затворам АРМАТЭК серии АМ — только у производителя)</t>
+        </is>
+      </c>
       <c r="L24" s="4" t="inlineStr"/>
     </row>
     <row r="25" ht="36" customHeight="1">
@@ -5803,10 +6172,20 @@
       <c r="G25" s="5" t="n">
         <v>93400</v>
       </c>
-      <c r="H25" s="5" t="n"/>
-      <c r="I25" s="5" t="n"/>
-      <c r="J25" s="10" t="n"/>
-      <c r="K25" s="4" t="inlineStr"/>
+      <c r="H25" s="5" t="n">
+        <v>43585.11</v>
+      </c>
+      <c r="I25" s="5" t="n">
+        <v>87170.22</v>
+      </c>
+      <c r="J25" s="8" t="n">
+        <v>0.06669999999999998</v>
+      </c>
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>[ОЦЕНКА] цена с НДС = НМЦ×1,22×0.85 (публичной цены нет; ЗИП к клапану КМР-Э (ЛГ Автоматика) — по запросу)</t>
+        </is>
+      </c>
       <c r="L25" s="4" t="inlineStr"/>
     </row>
     <row r="26" ht="36" customHeight="1">
@@ -6161,10 +6540,20 @@
       <c r="G33" s="5" t="n">
         <v>13440</v>
       </c>
-      <c r="H33" s="5" t="n"/>
-      <c r="I33" s="5" t="n"/>
-      <c r="J33" s="10" t="n"/>
-      <c r="K33" s="4" t="inlineStr"/>
+      <c r="H33" s="5" t="n">
+        <v>1045.3</v>
+      </c>
+      <c r="I33" s="5" t="n">
+        <v>12543.6</v>
+      </c>
+      <c r="J33" s="8" t="n">
+        <v>0.06669642857142866</v>
+      </c>
+      <c r="K33" s="4" t="inlineStr">
+        <is>
+          <t>[ОЦЕНКА] цена с НДС = НМЦ×1,22×0.85 (публичной цены нет; прокладка СНП Д-3-73-6,3-4,5 (Силур/Унихимтек и др.) — карточки</t>
+        </is>
+      </c>
       <c r="L33" s="4" t="inlineStr"/>
     </row>
     <row r="34" ht="36" customHeight="1">
@@ -6243,10 +6632,20 @@
       <c r="G35" s="5" t="n">
         <v>82120</v>
       </c>
-      <c r="H35" s="5" t="n"/>
-      <c r="I35" s="5" t="n"/>
-      <c r="J35" s="10" t="n"/>
-      <c r="K35" s="4" t="inlineStr"/>
+      <c r="H35" s="5" t="n">
+        <v>38321.3</v>
+      </c>
+      <c r="I35" s="5" t="n">
+        <v>76642.60000000001</v>
+      </c>
+      <c r="J35" s="8" t="n">
+        <v>0.06669995129079387</v>
+      </c>
+      <c r="K35" s="4" t="inlineStr">
+        <is>
+          <t>[ОЦЕНКА] цена с НДС = НМЦ×1,22×0.85 (публичной цены нет; ЗИП к затворам АРМАТЭК серии АМ — только у производителя)</t>
+        </is>
+      </c>
       <c r="L35" s="4" t="inlineStr"/>
     </row>
     <row r="36" ht="36" customHeight="1">
@@ -6277,10 +6676,20 @@
       <c r="G36" s="5" t="n">
         <v>142880</v>
       </c>
-      <c r="H36" s="5" t="n"/>
-      <c r="I36" s="5" t="n"/>
-      <c r="J36" s="10" t="n"/>
-      <c r="K36" s="4" t="inlineStr"/>
+      <c r="H36" s="5" t="n">
+        <v>66674.95</v>
+      </c>
+      <c r="I36" s="5" t="n">
+        <v>133349.9</v>
+      </c>
+      <c r="J36" s="8" t="n">
+        <v>0.06670002799552077</v>
+      </c>
+      <c r="K36" s="4" t="inlineStr">
+        <is>
+          <t>[ОЦЕНКА] цена с НДС = НМЦ×1,22×0.85 (публичной цены нет; ЗИП к затворам АРМАТЭК серии АМ — только у производителя)</t>
+        </is>
+      </c>
       <c r="L36" s="4" t="inlineStr"/>
     </row>
     <row r="37" ht="36" customHeight="1">
@@ -6405,7 +6814,7 @@
       <c r="I39" s="5" t="n">
         <v>17766</v>
       </c>
-      <c r="J39" s="11" t="n">
+      <c r="J39" s="10" t="n">
         <v>-0.0181088825214899</v>
       </c>
       <c r="K39" s="4" t="inlineStr">
@@ -6713,7 +7122,7 @@
       <c r="I46" s="5" t="n">
         <v>4468.9</v>
       </c>
-      <c r="J46" s="11" t="n">
+      <c r="J46" s="10" t="n">
         <v>-0.1760263157894737</v>
       </c>
       <c r="K46" s="4" t="inlineStr">
@@ -6761,7 +7170,7 @@
       <c r="I47" s="5" t="n">
         <v>5879.8</v>
       </c>
-      <c r="J47" s="11" t="n">
+      <c r="J47" s="10" t="n">
         <v>-0.4699500000000001</v>
       </c>
       <c r="K47" s="4" t="inlineStr">
@@ -6809,7 +7218,7 @@
       <c r="I48" s="5" t="n">
         <v>5818.33</v>
       </c>
-      <c r="J48" s="11" t="n">
+      <c r="J48" s="10" t="n">
         <v>-0.5682830188679246</v>
       </c>
       <c r="K48" s="4" t="inlineStr">
@@ -6857,7 +7266,7 @@
       <c r="I49" s="5" t="n">
         <v>5550.36</v>
       </c>
-      <c r="J49" s="11" t="n">
+      <c r="J49" s="10" t="n">
         <v>-0.08830588235294101</v>
       </c>
       <c r="K49" s="4" t="inlineStr">
@@ -6905,7 +7314,7 @@
       <c r="I50" s="5" t="n">
         <v>62322.39999999999</v>
       </c>
-      <c r="J50" s="11" t="n">
+      <c r="J50" s="10" t="n">
         <v>-0.1985076923076923</v>
       </c>
       <c r="K50" s="4" t="inlineStr">
@@ -6953,7 +7362,7 @@
       <c r="I51" s="5" t="n">
         <v>59423.7</v>
       </c>
-      <c r="J51" s="11" t="n">
+      <c r="J51" s="10" t="n">
         <v>-0.100438888888889</v>
       </c>
       <c r="K51" s="4" t="inlineStr">
@@ -7083,11 +7492,25 @@
       <c r="G54" s="5" t="n">
         <v>4270000</v>
       </c>
-      <c r="H54" s="5" t="n"/>
-      <c r="I54" s="5" t="n"/>
-      <c r="J54" s="10" t="n"/>
-      <c r="K54" s="4" t="inlineStr"/>
-      <c r="L54" s="4" t="inlineStr"/>
+      <c r="H54" s="5" t="n">
+        <v>1131417.62</v>
+      </c>
+      <c r="I54" s="5" t="n">
+        <v>2262835.24</v>
+      </c>
+      <c r="J54" s="9" t="n">
+        <v>0.4700620046838407</v>
+      </c>
+      <c r="K54" s="4" t="inlineStr">
+        <is>
+          <t>[ПРОКСИ] dn.ru на 27.10.2026: задвижка 30лс964нж Авангард Ду500 Ру25 (фланц., голый шток, Россия, 982 кг) 761 200,09 + Э</t>
+        </is>
+      </c>
+      <c r="L54" s="4" t="inlineStr">
+        <is>
+          <t>30лс964нж Авангард (РФ) + Тулаэлектропривод ЭП4</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="36" customHeight="1">
       <c r="A55" s="4" t="inlineStr">
@@ -7293,10 +7716,20 @@
       <c r="G59" s="5" t="n">
         <v>30000</v>
       </c>
-      <c r="H59" s="5" t="n"/>
-      <c r="I59" s="5" t="n"/>
-      <c r="J59" s="10" t="n"/>
-      <c r="K59" s="4" t="inlineStr"/>
+      <c r="H59" s="5" t="n">
+        <v>13999.5</v>
+      </c>
+      <c r="I59" s="5" t="n">
+        <v>27999</v>
+      </c>
+      <c r="J59" s="8" t="n">
+        <v>0.06669999999999998</v>
+      </c>
+      <c r="K59" s="4" t="inlineStr">
+        <is>
+          <t>[ОЦЕНКА] цена с НДС = НМЦ×1,22×0.85 (публичной цены нет; краны ЗАРД/ЗАРДП Ярдос (РФ) — у дилеров «цена договорная» (petr</t>
+        </is>
+      </c>
       <c r="L59" s="4" t="inlineStr"/>
     </row>
     <row r="60" ht="36" customHeight="1">
@@ -7327,10 +7760,20 @@
       <c r="G60" s="5" t="n">
         <v>15720</v>
       </c>
-      <c r="H60" s="5" t="n"/>
-      <c r="I60" s="5" t="n"/>
-      <c r="J60" s="10" t="n"/>
-      <c r="K60" s="4" t="inlineStr"/>
+      <c r="H60" s="5" t="n">
+        <v>7335.74</v>
+      </c>
+      <c r="I60" s="5" t="n">
+        <v>14671.48</v>
+      </c>
+      <c r="J60" s="8" t="n">
+        <v>0.06669974554707381</v>
+      </c>
+      <c r="K60" s="4" t="inlineStr">
+        <is>
+          <t>[ОЦЕНКА] цена с НДС = НМЦ×1,22×0.85 (публичной цены нет; краны ЗАРД/ЗАРДП Ярдос (РФ) — у дилеров «цена договорная» (petr</t>
+        </is>
+      </c>
       <c r="L60" s="4" t="inlineStr"/>
     </row>
     <row r="61" ht="36" customHeight="1">
@@ -7361,10 +7804,20 @@
       <c r="G61" s="5" t="n">
         <v>429240</v>
       </c>
-      <c r="H61" s="5" t="n"/>
-      <c r="I61" s="5" t="n"/>
-      <c r="J61" s="10" t="n"/>
-      <c r="K61" s="4" t="inlineStr"/>
+      <c r="H61" s="5" t="n">
+        <v>200304.85</v>
+      </c>
+      <c r="I61" s="5" t="n">
+        <v>400609.7</v>
+      </c>
+      <c r="J61" s="8" t="n">
+        <v>0.06669998136240796</v>
+      </c>
+      <c r="K61" s="4" t="inlineStr">
+        <is>
+          <t>[ОЦЕНКА] цена с НДС = НМЦ×1,22×0.85 (публичной цены нет; краны ЗАРД/ЗАРДП Ярдос (РФ) — у дилеров «цена договорная» (petr</t>
+        </is>
+      </c>
       <c r="L61" s="4" t="inlineStr"/>
     </row>
     <row r="62" ht="36" customHeight="1">
@@ -7395,10 +7848,20 @@
       <c r="G62" s="5" t="n">
         <v>45440</v>
       </c>
-      <c r="H62" s="5" t="n"/>
-      <c r="I62" s="5" t="n"/>
-      <c r="J62" s="10" t="n"/>
-      <c r="K62" s="4" t="inlineStr"/>
+      <c r="H62" s="5" t="n">
+        <v>21204.58</v>
+      </c>
+      <c r="I62" s="5" t="n">
+        <v>42409.16</v>
+      </c>
+      <c r="J62" s="8" t="n">
+        <v>0.06669982394366192</v>
+      </c>
+      <c r="K62" s="4" t="inlineStr">
+        <is>
+          <t>[ОЦЕНКА] цена с НДС = НМЦ×1,22×0.85 (публичной цены нет; краны ЗАРД/ЗАРДП Ярдос (РФ) — у дилеров «цена договорная» (petr</t>
+        </is>
+      </c>
       <c r="L62" s="4" t="inlineStr"/>
     </row>
     <row r="63" ht="36" customHeight="1">
@@ -7429,10 +7892,20 @@
       <c r="G63" s="5" t="n">
         <v>22000</v>
       </c>
-      <c r="H63" s="5" t="n"/>
-      <c r="I63" s="5" t="n"/>
-      <c r="J63" s="10" t="n"/>
-      <c r="K63" s="4" t="inlineStr"/>
+      <c r="H63" s="5" t="n">
+        <v>10266.3</v>
+      </c>
+      <c r="I63" s="5" t="n">
+        <v>20532.6</v>
+      </c>
+      <c r="J63" s="8" t="n">
+        <v>0.06670000000000009</v>
+      </c>
+      <c r="K63" s="4" t="inlineStr">
+        <is>
+          <t>[ОЦЕНКА] цена с НДС = НМЦ×1,22×0.85 (публичной цены нет; краны ЗАРД/ЗАРДП Ярдос (РФ) — у дилеров «цена договорная» (petr</t>
+        </is>
+      </c>
       <c r="L63" s="4" t="inlineStr"/>
     </row>
     <row r="64" ht="36" customHeight="1">
@@ -7463,10 +7936,20 @@
       <c r="G64" s="5" t="n">
         <v>58000</v>
       </c>
-      <c r="H64" s="5" t="n"/>
-      <c r="I64" s="5" t="n"/>
-      <c r="J64" s="10" t="n"/>
-      <c r="K64" s="4" t="inlineStr"/>
+      <c r="H64" s="5" t="n">
+        <v>27065.7</v>
+      </c>
+      <c r="I64" s="5" t="n">
+        <v>54131.4</v>
+      </c>
+      <c r="J64" s="8" t="n">
+        <v>0.06669999999999998</v>
+      </c>
+      <c r="K64" s="4" t="inlineStr">
+        <is>
+          <t>[ОЦЕНКА] цена с НДС = НМЦ×1,22×0.85 (публичной цены нет; краны ЗАРД/ЗАРДП Ярдос (РФ) — у дилеров «цена договорная» (petr</t>
+        </is>
+      </c>
       <c r="L64" s="4" t="inlineStr"/>
     </row>
     <row r="65" ht="36" customHeight="1">
@@ -7497,11 +7980,25 @@
       <c r="G65" s="5" t="n">
         <v>192000</v>
       </c>
-      <c r="H65" s="5" t="n"/>
-      <c r="I65" s="5" t="n"/>
-      <c r="J65" s="10" t="n"/>
-      <c r="K65" s="4" t="inlineStr"/>
-      <c r="L65" s="4" t="inlineStr"/>
+      <c r="H65" s="5" t="n">
+        <v>64287.9</v>
+      </c>
+      <c r="I65" s="5" t="n">
+        <v>128575.8</v>
+      </c>
+      <c r="J65" s="9" t="n">
+        <v>0.330334375</v>
+      </c>
+      <c r="K65" s="4" t="inlineStr">
+        <is>
+          <t>[ЦЕНА-аналог] elaparat.shop на 27.10.2026: МЭО-250/25-0,25У-99К ЧЗ Электроаппарат 71 431 (фланцевый МЭОФ-250/63-0,25И-99</t>
+        </is>
+      </c>
+      <c r="L65" s="4" t="inlineStr">
+        <is>
+          <t>МЭОФ-250/25-0,25У-99К ЧЗЭА (РФ)</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="36" customHeight="1">
       <c r="A66" s="4" t="inlineStr">
@@ -7531,10 +8028,20 @@
       <c r="G66" s="5" t="n">
         <v>253140</v>
       </c>
-      <c r="H66" s="5" t="n"/>
-      <c r="I66" s="5" t="n"/>
-      <c r="J66" s="10" t="n"/>
-      <c r="K66" s="4" t="inlineStr"/>
+      <c r="H66" s="5" t="n">
+        <v>78751.85000000001</v>
+      </c>
+      <c r="I66" s="5" t="n">
+        <v>236255.55</v>
+      </c>
+      <c r="J66" s="8" t="n">
+        <v>0.06670004740459823</v>
+      </c>
+      <c r="K66" s="4" t="inlineStr">
+        <is>
+          <t>[ОЦЕНКА] цена с НДС = НМЦ×1,22×0.85 (публичной цены нет; клапан ЭМ НО Ду20 с ЭУ-6ГМ1 (цапковый, под приварку) — спецарма</t>
+        </is>
+      </c>
       <c r="L66" s="4" t="inlineStr"/>
     </row>
     <row r="67" ht="36" customHeight="1">
@@ -7565,10 +8072,20 @@
       <c r="G67" s="5" t="n">
         <v>226080</v>
       </c>
-      <c r="H67" s="5" t="n"/>
-      <c r="I67" s="5" t="n"/>
-      <c r="J67" s="10" t="n"/>
-      <c r="K67" s="4" t="inlineStr"/>
+      <c r="H67" s="5" t="n">
+        <v>70333.49000000001</v>
+      </c>
+      <c r="I67" s="5" t="n">
+        <v>211000.47</v>
+      </c>
+      <c r="J67" s="8" t="n">
+        <v>0.06669997346072176</v>
+      </c>
+      <c r="K67" s="4" t="inlineStr">
+        <is>
+          <t>[ОЦЕНКА] цена с НДС = НМЦ×1,22×0.85 (публичной цены нет; клапан ЭМ НЗ Ду15 с ЭУ-6ГМ2 — цены нет)</t>
+        </is>
+      </c>
       <c r="L67" s="4" t="inlineStr"/>
     </row>
     <row r="68" ht="36" customHeight="1">
@@ -7687,10 +8204,20 @@
       <c r="G70" s="5" t="n">
         <v>133640</v>
       </c>
-      <c r="H70" s="5" t="n"/>
-      <c r="I70" s="5" t="n"/>
-      <c r="J70" s="10" t="n"/>
-      <c r="K70" s="4" t="inlineStr"/>
+      <c r="H70" s="5" t="n">
+        <v>62363.11</v>
+      </c>
+      <c r="I70" s="5" t="n">
+        <v>124726.22</v>
+      </c>
+      <c r="J70" s="8" t="n">
+        <v>0.06669994013768332</v>
+      </c>
+      <c r="K70" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[ОЦЕНКА] цена с НДС = НМЦ×1,22×0.85 (публичной цены нет; Классик ФБ39.210.050.000-02 — карточки с ценой нет; РФ-аналог: </t>
+        </is>
+      </c>
       <c r="L70" s="4" t="inlineStr"/>
     </row>
     <row r="71" ht="36" customHeight="1">
@@ -8121,10 +8648,20 @@
       <c r="G80" s="5" t="n">
         <v>114000</v>
       </c>
-      <c r="H80" s="5" t="n"/>
-      <c r="I80" s="5" t="n"/>
-      <c r="J80" s="10" t="n"/>
-      <c r="K80" s="4" t="inlineStr"/>
+      <c r="H80" s="5" t="n">
+        <v>17732.7</v>
+      </c>
+      <c r="I80" s="5" t="n">
+        <v>106396.2</v>
+      </c>
+      <c r="J80" s="8" t="n">
+        <v>0.06669999999999998</v>
+      </c>
+      <c r="K80" s="4" t="inlineStr">
+        <is>
+          <t>[ОЦЕНКА] цена с НДС = НМЦ×1,22×0.85 (публичной цены нет; КШ250.8Д1-Н23Б1ГН (манометрический) — производитель не установл</t>
+        </is>
+      </c>
       <c r="L80" s="4" t="inlineStr"/>
     </row>
     <row r="81" ht="36" customHeight="1">
@@ -8347,10 +8884,20 @@
       <c r="G85" s="5" t="n">
         <v>124500</v>
       </c>
-      <c r="H85" s="5" t="n"/>
-      <c r="I85" s="5" t="n"/>
-      <c r="J85" s="10" t="n"/>
-      <c r="K85" s="4" t="inlineStr"/>
+      <c r="H85" s="5" t="n">
+        <v>4908.61</v>
+      </c>
+      <c r="I85" s="5" t="n">
+        <v>24543.05</v>
+      </c>
+      <c r="J85" s="9" t="n">
+        <v>0.8028670682730924</v>
+      </c>
+      <c r="K85" s="4" t="inlineStr">
+        <is>
+          <t>[ПРОКСИ] dn.ru (справочно, Камчатка-база): Flamco Clean Smart 3/4 5 454,01 с НДС</t>
+        </is>
+      </c>
       <c r="L85" s="4" t="inlineStr"/>
     </row>
     <row r="86" ht="36" customHeight="1">
@@ -8381,10 +8928,20 @@
       <c r="G86" s="5" t="n">
         <v>195500</v>
       </c>
-      <c r="H86" s="5" t="n"/>
-      <c r="I86" s="5" t="n"/>
-      <c r="J86" s="10" t="n"/>
-      <c r="K86" s="4" t="inlineStr"/>
+      <c r="H86" s="5" t="n">
+        <v>8501.809999999999</v>
+      </c>
+      <c r="I86" s="5" t="n">
+        <v>42509.05</v>
+      </c>
+      <c r="J86" s="9" t="n">
+        <v>0.7825624040920716</v>
+      </c>
+      <c r="K86" s="4" t="inlineStr">
+        <is>
+          <t>[ПРОКСИ] dn.ru (справочно, Камчатка-база): Flamco Flamcovent Clean Smart 3/4 9 446,46 с НДС</t>
+        </is>
+      </c>
       <c r="L86" s="4" t="inlineStr"/>
     </row>
     <row r="87" ht="36" customHeight="1">
@@ -8415,11 +8972,25 @@
       <c r="G87" s="5" t="n">
         <v>11180</v>
       </c>
-      <c r="H87" s="5" t="n"/>
-      <c r="I87" s="5" t="n"/>
-      <c r="J87" s="10" t="n"/>
-      <c r="K87" s="4" t="inlineStr"/>
-      <c r="L87" s="4" t="inlineStr"/>
+      <c r="H87" s="5" t="n">
+        <v>942.08</v>
+      </c>
+      <c r="I87" s="5" t="n">
+        <v>3768.32</v>
+      </c>
+      <c r="J87" s="9" t="n">
+        <v>0.6629409660107335</v>
+      </c>
+      <c r="K87" s="4" t="inlineStr">
+        <is>
+          <t>dn.ru на 27.10.2026: коллектор Пензапромарматура 3/4″ Ду20 3 отвода 1/2″ ВР/НР с регулирующими клапанами 1 046,76 с НДС</t>
+        </is>
+      </c>
+      <c r="L87" s="4" t="inlineStr">
+        <is>
+          <t>Коллектор Пензапромарматура 3/4″×3×1/2″ (РФ)</t>
+        </is>
+      </c>
     </row>
     <row r="88" ht="36" customHeight="1">
       <c r="A88" s="4" t="inlineStr">
@@ -8466,31 +9037,31 @@
       <c r="L88" s="4" t="inlineStr"/>
     </row>
     <row r="89" ht="36" customHeight="1">
-      <c r="A89" s="12" t="inlineStr"/>
-      <c r="B89" s="12" t="inlineStr"/>
-      <c r="C89" s="12" t="inlineStr">
+      <c r="A89" s="11" t="inlineStr"/>
+      <c r="B89" s="11" t="inlineStr"/>
+      <c r="C89" s="11" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="D89" s="12" t="inlineStr"/>
-      <c r="E89" s="12" t="inlineStr"/>
-      <c r="F89" s="12" t="inlineStr"/>
-      <c r="G89" s="13">
+      <c r="D89" s="11" t="inlineStr"/>
+      <c r="E89" s="11" t="inlineStr"/>
+      <c r="F89" s="11" t="inlineStr"/>
+      <c r="G89" s="12">
         <f>SUM(G2:G88)</f>
         <v/>
       </c>
-      <c r="H89" s="12" t="inlineStr"/>
-      <c r="I89" s="13">
+      <c r="H89" s="11" t="inlineStr"/>
+      <c r="I89" s="12">
         <f>SUM(I2:I88)</f>
         <v/>
       </c>
-      <c r="J89" s="14">
+      <c r="J89" s="13">
         <f>1-I89/G89</f>
         <v/>
       </c>
-      <c r="K89" s="15" t="n"/>
-      <c r="L89" s="15" t="n"/>
+      <c r="K89" s="14" t="n"/>
+      <c r="L89" s="14" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/SAKHALIN_11201_11202.xlsx
+++ b/SAKHALIN_11201_11202.xlsx
@@ -872,7 +872,7 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>нужны договоры + УПД с обеих сторон. Если своего опыта нет — коллективный участник (соглашение с партнёром, у кого есть опыт)</t>
+          <t>ОПЫТ ЕСТЬ (подтверждено 28.10): приложить договоры + УПД с обеих сторон, справка по форме 7</t>
         </is>
       </c>
     </row>

--- a/SAKHALIN_11201_11202.xlsx
+++ b/SAKHALIN_11201_11202.xlsx
@@ -1503,17 +1503,17 @@
         <v>47600</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>832.83</v>
+        <v>859.75</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>33313.2</v>
+        <v>34390</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>0.3001428571428572</v>
+        <v>0.2775210084033614</v>
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>dn.ru, фланец плоский Россия Ду100 Ру6 ст20 тип 01 исп.B ГОСТ 33259-2015, на 02.11.2026</t>
+          <t>КП ВФЗ: Счёт № УТ-10448 от 28.10.2026 — Фланец плоский 100-6-01-1-B-Ст.20-IV ГОСТ 33259-2015</t>
         </is>
       </c>
       <c r="L6" s="4" t="inlineStr"/>
@@ -1727,17 +1727,17 @@
         <v>32800</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>2415.6</v>
+        <v>1937.43</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>24156</v>
+        <v>19374.3</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>0.2635365853658537</v>
+        <v>0.4093201219512195</v>
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>dn.ru, фланец КЗТШ Ду200 Ру16 ст20 тип 01 исп.B, на 18.02.2027(дата цены сайта)</t>
+          <t>КП ВФЗ: Счёт № УТ-10448 от 28.10.2026 — Фланец плоский 200-16-01-1-B-Ст.20-IV ГОСТ 33259-2015</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr"/>
@@ -2363,17 +2363,17 @@
         <v>3866.7</v>
       </c>
       <c r="H25" s="5" t="n">
-        <v>305.24</v>
+        <v>251.16</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>3052.4</v>
-      </c>
-      <c r="J25" s="8" t="n">
-        <v>0.2105930121292058</v>
+        <v>2511.6</v>
+      </c>
+      <c r="J25" s="9" t="n">
+        <v>0.350453875397626</v>
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>dn.ru, фланец плоский Россия Ду32 Ру10 ст20 тип 01 исп.B, на 02.11.2026</t>
+          <t>КП ВФЗ: Счёт № УТ-10448 от 28.10.2026 — Фланец плоский 32-16-01-1-B-Ст.20-IV ГОСТ 33259-2015</t>
         </is>
       </c>
       <c r="L25" s="4" t="inlineStr"/>
@@ -2407,17 +2407,17 @@
         <v>7800</v>
       </c>
       <c r="H26" s="5" t="n">
-        <v>417.79</v>
+        <v>402.99</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>4177.900000000001</v>
+        <v>4029.9</v>
       </c>
       <c r="J26" s="9" t="n">
-        <v>0.4643717948717948</v>
+        <v>0.4833461538461539</v>
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>dn.ru, фланец КЗТШ Ду50 Ру10 ст20 тип 01 исп.B</t>
+          <t>КП ВФЗ: Счёт № УТ-10448 от 28.10.2026 — Фланец плоский 50-10-01-1-B-Ст.20-IV ГОСТ 33259-2015</t>
         </is>
       </c>
       <c r="L26" s="4" t="inlineStr"/>
@@ -2451,17 +2451,17 @@
         <v>28200</v>
       </c>
       <c r="H27" s="5" t="n">
-        <v>645.62</v>
+        <v>499.04</v>
       </c>
       <c r="I27" s="5" t="n">
-        <v>19368.6</v>
+        <v>14971.2</v>
       </c>
       <c r="J27" s="9" t="n">
-        <v>0.3131702127659575</v>
+        <v>0.4691063829787234</v>
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>dn.ru, фланец КЗТШ Ду80 Ру10</t>
+          <t>КП ВФЗ: Счёт № УТ-10448 от 28.10.2026 — Фланец плоский 80-10-01-1-B-Ст.20-IV ГОСТ 33259-2015</t>
         </is>
       </c>
       <c r="L27" s="4" t="inlineStr"/>
@@ -2495,17 +2495,17 @@
         <v>44653.22</v>
       </c>
       <c r="H28" s="5" t="n">
-        <v>999.1799999999999</v>
+        <v>645.8099999999999</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>33972.12</v>
-      </c>
-      <c r="J28" s="8" t="n">
-        <v>0.2392011147236415</v>
+        <v>21957.54</v>
+      </c>
+      <c r="J28" s="9" t="n">
+        <v>0.5082652494041864</v>
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>dn.ru, фланец КЗТШ Ду100 Ру10</t>
+          <t>КП ВФЗ: Счёт № УТ-10448 от 28.10.2026 — Фланец плоский 100-10-01-1-B-Ст.20-IV ГОСТ 33259-2015</t>
         </is>
       </c>
       <c r="L28" s="4" t="inlineStr"/>
@@ -2539,17 +2539,17 @@
         <v>19600</v>
       </c>
       <c r="H29" s="5" t="n">
-        <v>1526.77</v>
+        <v>1174.2</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>15267.7</v>
-      </c>
-      <c r="J29" s="8" t="n">
-        <v>0.2210357142857143</v>
+        <v>11742</v>
+      </c>
+      <c r="J29" s="9" t="n">
+        <v>0.4009183673469388</v>
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>dn.ru, фланец КЗТШ Ду150 Ру10</t>
+          <t>КП ВФЗ: Счёт № УТ-10448 от 28.10.2026 — Фланец плоский 150-10-01-1-B-Ст.20-IV ГОСТ 33259-2015</t>
         </is>
       </c>
       <c r="L29" s="4" t="inlineStr"/>
@@ -2803,17 +2803,17 @@
         <v>33700</v>
       </c>
       <c r="H35" s="5" t="n">
-        <v>3788.1</v>
+        <v>4209</v>
       </c>
       <c r="I35" s="5" t="n">
-        <v>18940.5</v>
+        <v>21045</v>
       </c>
       <c r="J35" s="9" t="n">
-        <v>0.4379673590504451</v>
+        <v>0.3755192878338279</v>
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>КП Лидер-Энерго № 2022 от 26.10.2026: ЗПД-80-УХЛ1, с НДС (база Камчатки)</t>
+          <t>КП Лидер-Энерго: КП № 2035 от 28.10.2026 — Затвор поворотный дисковый ЗПД-80-УХЛ1</t>
         </is>
       </c>
       <c r="L35" s="4" t="inlineStr"/>
@@ -2847,17 +2847,17 @@
         <v>20220</v>
       </c>
       <c r="H36" s="5" t="n">
-        <v>3788.1</v>
+        <v>4209</v>
       </c>
       <c r="I36" s="5" t="n">
-        <v>11364.3</v>
+        <v>12627</v>
       </c>
       <c r="J36" s="9" t="n">
-        <v>0.4379673590504451</v>
+        <v>0.3755192878338279</v>
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>КП Лидер-Энерго № 2022 от 26.10.2026: ЗПД-80-УХЛ1, с НДС (база Камчатки)</t>
+          <t>КП Лидер-Энерго: КП № 2035 от 28.10.2026 — Затвор поворотный дисковый ЗПД-80-УХЛ1</t>
         </is>
       </c>
       <c r="L36" s="4" t="inlineStr"/>
@@ -2939,17 +2939,17 @@
         <v>477666.65</v>
       </c>
       <c r="H38" s="5" t="n">
-        <v>89161.25</v>
+        <v>83496.8</v>
       </c>
       <c r="I38" s="5" t="n">
-        <v>445806.25</v>
+        <v>417484</v>
       </c>
       <c r="J38" s="8" t="n">
-        <v>0.06670007211095852</v>
+        <v>0.1259929911372293</v>
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>[ОЦЕНКА] цена с НДС = НМЦ×1,22×0.85 (публичной цены нет; АРМАТЭК серия АМ с пневмоприводом/ЭПР/БКВ — цены только по опро</t>
+          <t>КП АРМАТЭК: КП № 3484 от 28.10.2026 — Затвор АРМАТЭК DN065 с ПП ДД АМ6.710.1433-УК, ЭПР 5/2 24VDC, БКВ А250 (вода до +</t>
         </is>
       </c>
       <c r="L38" s="4" t="inlineStr"/>
@@ -2983,17 +2983,17 @@
         <v>454900</v>
       </c>
       <c r="H39" s="5" t="n">
-        <v>84911.63</v>
+        <v>127050.8</v>
       </c>
       <c r="I39" s="5" t="n">
-        <v>424558.15</v>
-      </c>
-      <c r="J39" s="8" t="n">
-        <v>0.06670004396570672</v>
+        <v>635254</v>
+      </c>
+      <c r="J39" s="10" t="n">
+        <v>-0.3964695537480765</v>
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>[ОЦЕНКА] цена с НДС = НМЦ×1,22×0.85 (публичной цены нет; АРМАТЭК серия АМ с пневмоприводом/ЭПР/БКВ — цены только по опро</t>
+          <t xml:space="preserve">КП АРМАТЭК: КП № 3484 от 28.10.2026 — Затвор АРМАТЭК DN065 с пневмоприводом ДД АН6.610.1433-УК, ЭПР 5/2, БКВ А250, РД </t>
         </is>
       </c>
       <c r="L39" s="4" t="inlineStr"/>
@@ -3027,17 +3027,17 @@
         <v>1493299.95</v>
       </c>
       <c r="H40" s="5" t="n">
-        <v>92913.12</v>
+        <v>86607.8</v>
       </c>
       <c r="I40" s="5" t="n">
-        <v>1393696.8</v>
+        <v>1299117</v>
       </c>
       <c r="J40" s="8" t="n">
-        <v>0.06670002901962202</v>
+        <v>0.1300361323925578</v>
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>[ОЦЕНКА] цена с НДС = НМЦ×1,22×0.85 (публичной цены нет; АРМАТЭК серия АМ с пневмоприводом/ЭПР/БКВ — цены только по опро</t>
+          <t xml:space="preserve">КП АРМАТЭК: КП № 3484 от 28.10.2026 — Затвор АРМАТЭК DN080 с ПП ДД АМ6.711.1433-УК, ЭПР 5/2, БКВ А250 (воздух с золой </t>
         </is>
       </c>
       <c r="L40" s="4" t="inlineStr"/>
@@ -3711,17 +3711,17 @@
         <v>38900</v>
       </c>
       <c r="H55" s="5" t="n">
-        <v>3630.54</v>
+        <v>3416</v>
       </c>
       <c r="I55" s="5" t="n">
-        <v>36305.4</v>
+        <v>34160</v>
       </c>
       <c r="J55" s="8" t="n">
-        <v>0.06669922879177381</v>
+        <v>0.1218508997429306</v>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>[ОЦЕНКА] цена с НДС = НМЦ×1,22×0.85 (публичной цены нет; ЗИП к затворам АРМАТЭК серии АМ — только у производителя)</t>
+          <t>КП АРМАТЭК: КП № 3484 от 28.10.2026 — Комплект ЗИП АМ DN065 41100УУ</t>
         </is>
       </c>
       <c r="L55" s="4" t="inlineStr"/>
@@ -3755,17 +3755,17 @@
         <v>41600</v>
       </c>
       <c r="H56" s="5" t="n">
-        <v>3882.53</v>
+        <v>3647.8</v>
       </c>
       <c r="I56" s="5" t="n">
-        <v>38825.3</v>
+        <v>36478</v>
       </c>
       <c r="J56" s="8" t="n">
-        <v>0.06669951923076922</v>
+        <v>0.1231249999999999</v>
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>[ОЦЕНКА] цена с НДС = НМЦ×1,22×0.85 (публичной цены нет; ЗИП к затворам АРМАТЭК серии АМ — только у производителя)</t>
+          <t>КП АРМАТЭК: КП № 3484 от 28.10.2026 — Комплект ЗИП АН DN065 31100УУ</t>
         </is>
       </c>
       <c r="L56" s="4" t="inlineStr"/>
@@ -3799,17 +3799,17 @@
         <v>44700</v>
       </c>
       <c r="H57" s="5" t="n">
-        <v>4171.85</v>
+        <v>3916.2</v>
       </c>
       <c r="I57" s="5" t="n">
-        <v>41718.5</v>
+        <v>39162</v>
       </c>
       <c r="J57" s="8" t="n">
-        <v>0.06670022371364648</v>
+        <v>0.1238926174496645</v>
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>[ОЦЕНКА] цена с НДС = НМЦ×1,22×0.85 (публичной цены нет; ЗИП к затворам АРМАТЭК серии АМ — только у производителя)</t>
+          <t>КП АРМАТЭК: КП № 3484 от 28.10.2026 — Комплект ЗИП АМ DN080 41110УУ</t>
         </is>
       </c>
       <c r="L57" s="4" t="inlineStr"/>
@@ -4287,17 +4287,17 @@
         <v>556640</v>
       </c>
       <c r="H68" s="5" t="n">
-        <v>345046.5</v>
+        <v>314729.5</v>
       </c>
       <c r="I68" s="5" t="n">
-        <v>345046.5</v>
+        <v>314729.5</v>
       </c>
       <c r="J68" s="9" t="n">
-        <v>0.3801262934751365</v>
+        <v>0.4345905791894222</v>
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>[ПРОКСИ] МЭО-1600/25-0,25У-92КБ 127 795 (elaparat.shop, ЧЗ Электроаппарат, на 27.10.2026) ×3 за фланцевое исполнение + и</t>
+          <t>КП ПЭК: КП № П-8596 от 28.10.2026 — МЭОФ-1600/25-0,25-ЕА-20К У2, 380В, IP65 (встроенный блок управления 4-20мА, пози</t>
         </is>
       </c>
       <c r="L68" s="4" t="inlineStr"/>
@@ -4551,17 +4551,17 @@
         <v>5933.32</v>
       </c>
       <c r="H74" s="5" t="n">
-        <v>1385.13</v>
+        <v>975</v>
       </c>
       <c r="I74" s="5" t="n">
-        <v>5540.52</v>
-      </c>
-      <c r="J74" s="8" t="n">
-        <v>0.0662023959604402</v>
+        <v>3900</v>
+      </c>
+      <c r="J74" s="9" t="n">
+        <v>0.3426951521239373</v>
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>dn.ru, фланец Россия Ду150 Ру6 ст20 тип 01 исп.B, на 02.11.2026</t>
+          <t>КП ВФЗ: Счёт № УТ-10448 от 28.10.2026 — Фланец плоский 150-6-01-1-B-Ст.20-IV ГОСТ 33259-2015</t>
         </is>
       </c>
       <c r="L74" s="4" t="inlineStr"/>
@@ -4595,17 +4595,17 @@
         <v>7140</v>
       </c>
       <c r="H75" s="5" t="n">
-        <v>832.83</v>
+        <v>859.75</v>
       </c>
       <c r="I75" s="5" t="n">
-        <v>4996.98</v>
+        <v>5158.5</v>
       </c>
       <c r="J75" s="9" t="n">
-        <v>0.3001428571428572</v>
+        <v>0.2775210084033614</v>
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>dn.ru, фланец плоский Россия Ду100 Ру6 ст20 тип 01 исп.B ГОСТ 33259-2015, на 02.11.2026</t>
+          <t>КП ВФЗ: Счёт № УТ-10448 от 28.10.2026 — Фланец плоский 100-6-01-1-B-Ст.20-IV ГОСТ 33259-2015</t>
         </is>
       </c>
       <c r="L75" s="4" t="inlineStr"/>
@@ -4639,17 +4639,17 @@
         <v>9896.040000000001</v>
       </c>
       <c r="H76" s="5" t="n">
-        <v>417.79</v>
+        <v>402.99</v>
       </c>
       <c r="I76" s="5" t="n">
-        <v>5013.48</v>
+        <v>4835.88</v>
       </c>
       <c r="J76" s="9" t="n">
-        <v>0.4933852328810312</v>
+        <v>0.5113318054494524</v>
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>dn.ru, фланец КЗТШ Ду50 Ру10 ст20 тип 01 исп.B</t>
+          <t>КП ВФЗ: Счёт № УТ-10448 от 28.10.2026 — Фланец плоский 50-10-01-1-B-Ст.20-IV ГОСТ 33259-2015</t>
         </is>
       </c>
       <c r="L76" s="4" t="inlineStr"/>
@@ -5953,17 +5953,17 @@
         <v>173400</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>16183.42</v>
+        <v>14603.4</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>161834.2</v>
+        <v>146034</v>
       </c>
       <c r="J20" s="8" t="n">
-        <v>0.06670011534025377</v>
+        <v>0.1578200692041523</v>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>[ОЦЕНКА] цена с НДС = НМЦ×1,22×0.85 (публичной цены нет; ЗИП к затворам АРМАТЭК серии АМ — только у производителя)</t>
+          <t>КП АРМАТЭК: КП № 3484 от 28.10.2026 — Комплект ЗИП АМ DN150 41140ZZ</t>
         </is>
       </c>
       <c r="L20" s="4" t="inlineStr"/>
@@ -5997,17 +5997,17 @@
         <v>260000</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>30332.25</v>
+        <v>27474.4</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>242658</v>
+        <v>219795.2</v>
       </c>
       <c r="J21" s="8" t="n">
-        <v>0.06669999999999998</v>
+        <v>0.1546338461538461</v>
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>[ОЦЕНКА] цена с НДС = НМЦ×1,22×0.85 (публичной цены нет; ЗИП к затворам АРМАТЭК серии АМ — только у производителя)</t>
+          <t>КП АРМАТЭК: КП № 3484 от 28.10.2026 — Комплект ЗИП АМ DN250 41160ZZ</t>
         </is>
       </c>
       <c r="L21" s="4" t="inlineStr"/>
@@ -6041,17 +6041,17 @@
         <v>97200</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>9071.68</v>
+        <v>8235</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>90716.8</v>
+        <v>82350</v>
       </c>
       <c r="J22" s="8" t="n">
-        <v>0.06669958847736623</v>
+        <v>0.1527777777777778</v>
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>[ОЦЕНКА] цена с НДС = НМЦ×1,22×0.85 (публичной цены нет; ЗИП к затворам АРМАТЭК серии АМ — только у производителя)</t>
+          <t>КП АРМАТЭК: КП № 3484 от 28.10.2026 — Комплект ЗИП АМ DN100 41120ZZ</t>
         </is>
       </c>
       <c r="L22" s="4" t="inlineStr"/>
@@ -6085,17 +6085,17 @@
         <v>120000</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>11199.6</v>
+        <v>10223.6</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>111996</v>
+        <v>102236</v>
       </c>
       <c r="J23" s="8" t="n">
-        <v>0.06669999999999998</v>
+        <v>0.1480333333333334</v>
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>[ОЦЕНКА] цена с НДС = НМЦ×1,22×0.85 (публичной цены нет; ЗИП к затворам АРМАТЭК серии АМ — только у производителя)</t>
+          <t>КП АРМАТЭК: КП № 3484 от 28.10.2026 — Комплект ЗИП АМ DN125 41130ZZ</t>
         </is>
       </c>
       <c r="L23" s="4" t="inlineStr"/>
@@ -6129,17 +6129,17 @@
         <v>11080</v>
       </c>
       <c r="H24" s="5" t="n">
-        <v>5170.48</v>
+        <v>4733.6</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>10340.96</v>
+        <v>9467.200000000001</v>
       </c>
       <c r="J24" s="8" t="n">
-        <v>0.06670036101083043</v>
+        <v>0.1455595667870035</v>
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>[ОЦЕНКА] цена с НДС = НМЦ×1,22×0.85 (публичной цены нет; ЗИП к затворам АРМАТЭК серии АМ — только у производителя)</t>
+          <t>КП АРМАТЭК: КП № 3484 от 28.10.2026 — Комплект ЗИП АМ DN50 41090ZZ</t>
         </is>
       </c>
       <c r="L24" s="4" t="inlineStr"/>
@@ -6585,17 +6585,17 @@
         <v>188946.67</v>
       </c>
       <c r="H34" s="5" t="n">
-        <v>55258.2</v>
+        <v>172099.3</v>
       </c>
       <c r="I34" s="5" t="n">
-        <v>55258.2</v>
-      </c>
-      <c r="J34" s="9" t="n">
-        <v>0.7075460498986301</v>
+        <v>172099.3</v>
+      </c>
+      <c r="J34" s="8" t="n">
+        <v>0.08916468334689376</v>
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>ЭТК Прогресс (etk-progress.ru, ©2026): МЭОФ-1600/25-0,25-96К, 61 398 ₽ (НДС в карточке не указан — принято как с НДС)</t>
+          <t>КП ПЭК: КП № П-8596 от 28.10.2026 — МЭОФ-1600/25-0,25У-96К У2, 380В, IP65</t>
         </is>
       </c>
       <c r="L34" s="4" t="inlineStr">
@@ -6633,17 +6633,17 @@
         <v>82120</v>
       </c>
       <c r="H35" s="5" t="n">
-        <v>38321.3</v>
+        <v>35245.8</v>
       </c>
       <c r="I35" s="5" t="n">
-        <v>76642.60000000001</v>
+        <v>70491.60000000001</v>
       </c>
       <c r="J35" s="8" t="n">
-        <v>0.06669995129079387</v>
+        <v>0.141602532878714</v>
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>[ОЦЕНКА] цена с НДС = НМЦ×1,22×0.85 (публичной цены нет; ЗИП к затворам АРМАТЭК серии АМ — только у производителя)</t>
+          <t>КП АРМАТЭК: КП № 3484 от 28.10.2026 — Комплект ЗИП АМ DN300 41170ZZ</t>
         </is>
       </c>
       <c r="L35" s="4" t="inlineStr"/>
@@ -6677,17 +6677,17 @@
         <v>142880</v>
       </c>
       <c r="H36" s="5" t="n">
-        <v>66674.95</v>
+        <v>61317.2</v>
       </c>
       <c r="I36" s="5" t="n">
-        <v>133349.9</v>
+        <v>122634.4</v>
       </c>
       <c r="J36" s="8" t="n">
-        <v>0.06670002799552077</v>
+        <v>0.1416965285554311</v>
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>[ОЦЕНКА] цена с НДС = НМЦ×1,22×0.85 (публичной цены нет; ЗИП к затворам АРМАТЭК серии АМ — только у производителя)</t>
+          <t>КП АРМАТЭК: КП № 3484 от 28.10.2026 — Комплект ЗИП АМ DN400 41190ZZ</t>
         </is>
       </c>
       <c r="L36" s="4" t="inlineStr"/>
@@ -7405,17 +7405,17 @@
         <v>102000</v>
       </c>
       <c r="H52" s="5" t="n">
-        <v>900</v>
+        <v>1075</v>
       </c>
       <c r="I52" s="5" t="n">
-        <v>36000</v>
+        <v>43000</v>
       </c>
       <c r="J52" s="9" t="n">
-        <v>0.6470588235294117</v>
+        <v>0.5784313725490196</v>
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>techsteklo.ru: трубка кварцевая 18х2х1500, с НДС</t>
+          <t>КП Доминик: письмо 28.10.2026 (Наумов А.) — Трубка кварцевая 18х2-1500 мм</t>
         </is>
       </c>
       <c r="L52" s="4" t="inlineStr"/>
@@ -7449,17 +7449,17 @@
         <v>696000</v>
       </c>
       <c r="H53" s="5" t="n">
-        <v>99000</v>
+        <v>110000</v>
       </c>
       <c r="I53" s="5" t="n">
-        <v>396000</v>
+        <v>440000</v>
       </c>
       <c r="J53" s="9" t="n">
-        <v>0.4310344827586207</v>
+        <v>0.367816091954023</v>
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>techsteklo.ru (ООО «Компания Доминик»): Т-229б Ду20 Ру165, цена с НДС, ©2026</t>
+          <t>КП Доминик: письмо 28.10.2026 (Наумов А.) — Указатель уровня Т-229Б прямого действия</t>
         </is>
       </c>
       <c r="L53" s="4" t="inlineStr"/>
@@ -7981,17 +7981,17 @@
         <v>192000</v>
       </c>
       <c r="H65" s="5" t="n">
-        <v>64287.9</v>
+        <v>93580.10000000001</v>
       </c>
       <c r="I65" s="5" t="n">
-        <v>128575.8</v>
-      </c>
-      <c r="J65" s="9" t="n">
-        <v>0.330334375</v>
+        <v>187160.2</v>
+      </c>
+      <c r="J65" s="10" t="n">
+        <v>0.02520729166666658</v>
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>[ЦЕНА-аналог] elaparat.shop на 27.10.2026: МЭО-250/25-0,25У-99К ЧЗ Электроаппарат 71 431 (фланцевый МЭОФ-250/63-0,25И-99</t>
+          <t>КП ПЭК: КП № П-8596 от 28.10.2026 — МЭОФ-250/25-0,25У-99К У2, 380В, IP65</t>
         </is>
       </c>
       <c r="L65" s="4" t="inlineStr">
@@ -8293,17 +8293,17 @@
         <v>42000</v>
       </c>
       <c r="H72" s="5" t="n">
-        <v>3420</v>
+        <v>3800</v>
       </c>
       <c r="I72" s="5" t="n">
-        <v>20520</v>
+        <v>22800</v>
       </c>
       <c r="J72" s="9" t="n">
-        <v>0.5114285714285715</v>
+        <v>0.4571428571428572</v>
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>techsteklo.ru: 15ч93эм Ду25, с НДС</t>
+          <t>КП Доминик: письмо 28.10.2026 (Наумов А.) — Вентиль диафрагмовый эмалированный 15ч93эм Ду25</t>
         </is>
       </c>
       <c r="L72" s="4" t="inlineStr"/>

--- a/SAKHALIN_11201_11202.xlsx
+++ b/SAKHALIN_11201_11202.xlsx
@@ -8205,17 +8205,17 @@
         <v>133640</v>
       </c>
       <c r="H70" s="5" t="n">
-        <v>62363.11</v>
+        <v>30252.34</v>
       </c>
       <c r="I70" s="5" t="n">
-        <v>124726.22</v>
-      </c>
-      <c r="J70" s="8" t="n">
-        <v>0.06669994013768332</v>
+        <v>60504.68</v>
+      </c>
+      <c r="J70" s="9" t="n">
+        <v>0.5472562107153547</v>
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">[ОЦЕНКА] цена с НДС = НМЦ×1,22×0.85 (публичной цены нет; Классик ФБ39.210.050.000-02 — карточки с ценой нет; РФ-аналог: </t>
+          <t>КП rost (ФОБОС): Кран шаровый фланцевый «УНИВЕРСАЛ» DN50 PN16-40 12Х18Н9ТЛ/УХЛ1 L=230, -60…+160, кл. А, ФБ3</t>
         </is>
       </c>
       <c r="L70" s="4" t="inlineStr"/>

--- a/SAKHALIN_11201_11202.xlsx
+++ b/SAKHALIN_11201_11202.xlsx
@@ -5685,17 +5685,17 @@
         <v>276000</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>4020.17</v>
+        <v>4287.88</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>160806.8</v>
+        <v>171515.2</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>0.4173666666666667</v>
+        <v>0.378568115942029</v>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>БК-Арматура: 31ч6бр DN50 PN10 (Казанский арм. з-д) + КОФ</t>
+          <t>Счёт ЛМЗ № 3028 от 28.10.2026: 30ч6бр DN50 2854 ₽ без НДС (+22%) + КОФ 2 фланца ВФЗ по 403 ₽</t>
         </is>
       </c>
       <c r="L14" s="4" t="inlineStr"/>
@@ -5729,17 +5729,17 @@
         <v>406000</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>9277.65</v>
+        <v>9516.02</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>259774.2</v>
+        <v>266448.56</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>0.3601620689655173</v>
+        <v>0.3437227586206896</v>
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>БК-Арматура: 31ч6бр DN100 (КАЗ) + КОФ</t>
+          <t>Счёт ЛМЗ № 3028 от 28.10.2026: 30ч6бр DN100 6741 ₽ без НДС (+22%) + КОФ 2 фланца ВФЗ по 646 ₽</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr"/>
@@ -5773,17 +5773,17 @@
         <v>397800</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>20469.33</v>
+        <v>21610.58</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>266101.29</v>
+        <v>280937.54</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>0.3310676470588235</v>
+        <v>0.2937718954248365</v>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>БК-Арматура: 31ч6бр DN150 (КАЗ) + КОФ</t>
+          <t>Счёт ЛМЗ № 3028 от 28.10.2026: 30ч6бр DN150 15789 ₽ без НДС (+22%) + КОФ 2 фланца ВФЗ по 1174 ₽</t>
         </is>
       </c>
       <c r="L16" s="4" t="inlineStr"/>
@@ -5817,17 +5817,17 @@
         <v>920000</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>34862.36</v>
+        <v>42212.5</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>557797.76</v>
+        <v>675400</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>0.3936980869565218</v>
+        <v>0.2658695652173914</v>
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>БК-Арматура: 31ч6бр DN200 PN10 (КАЗ) + КОФ</t>
+          <t>Счёт ЛМЗ № 3028 от 28.10.2026: 30ч6бр DN200 31425 ₽ без НДС (+22%) + КОФ 2 фланца ВФЗ по 1937 ₽</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr"/>
@@ -5861,17 +5861,17 @@
         <v>229740</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>52182.32</v>
+        <v>60215.66</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>156546.96</v>
-      </c>
-      <c r="J18" s="9" t="n">
-        <v>0.3185907547662575</v>
+        <v>180646.98</v>
+      </c>
+      <c r="J18" s="8" t="n">
+        <v>0.213689475058762</v>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>БК-Арматура: 31ч6бр DN250 PN10 (КАЗ) + КОФ</t>
+          <t>Счёт ЛМЗ № 3028 от 28.10.2026: 30ч6бр DN250 44603 ₽ без НДС (+22%) + КОФ 2 фланца ВФЗ по 2900 ₽</t>
         </is>
       </c>
       <c r="L18" s="4" t="inlineStr"/>

--- a/SAKHALIN_11201_11202.xlsx
+++ b/SAKHALIN_11201_11202.xlsx
@@ -7717,17 +7717,17 @@
         <v>30000</v>
       </c>
       <c r="H59" s="5" t="n">
-        <v>13999.5</v>
+        <v>12709.96</v>
       </c>
       <c r="I59" s="5" t="n">
-        <v>27999</v>
+        <v>25419.92</v>
       </c>
       <c r="J59" s="8" t="n">
-        <v>0.06669999999999998</v>
+        <v>0.1526693333333334</v>
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>[ОЦЕНКА] цена с НДС = НМЦ×1,22×0.85 (публичной цены нет; краны ЗАРД/ЗАРДП Ярдос (РФ) — у дилеров «цена договорная» (petr</t>
+          <t>КП Ярдос: ЗАРД 032.016.21-01Р DN32 PN16</t>
         </is>
       </c>
       <c r="L59" s="4" t="inlineStr"/>
@@ -7761,17 +7761,17 @@
         <v>15720</v>
       </c>
       <c r="H60" s="5" t="n">
-        <v>7335.74</v>
+        <v>6612.4</v>
       </c>
       <c r="I60" s="5" t="n">
-        <v>14671.48</v>
+        <v>13224.8</v>
       </c>
       <c r="J60" s="8" t="n">
-        <v>0.06669974554707381</v>
+        <v>0.1587277353689568</v>
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>[ОЦЕНКА] цена с НДС = НМЦ×1,22×0.85 (публичной цены нет; краны ЗАРД/ЗАРДП Ярдос (РФ) — у дилеров «цена договорная» (petr</t>
+          <t>КП Ярдос: ЗАРДП 010.080.30-01Р DN10 PN80</t>
         </is>
       </c>
       <c r="L60" s="4" t="inlineStr"/>
@@ -7805,17 +7805,17 @@
         <v>429240</v>
       </c>
       <c r="H61" s="5" t="n">
-        <v>200304.85</v>
+        <v>180575.86</v>
       </c>
       <c r="I61" s="5" t="n">
-        <v>400609.7</v>
+        <v>361151.72</v>
       </c>
       <c r="J61" s="8" t="n">
-        <v>0.06669998136240796</v>
+        <v>0.1586251980244153</v>
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>[ОЦЕНКА] цена с НДС = НМЦ×1,22×0.85 (публичной цены нет; краны ЗАРД/ЗАРДП Ярдос (РФ) — у дилеров «цена договорная» (petr</t>
+          <t>КП Ярдос: ЗАРДП 065.063.22-01Р DN65 PN63</t>
         </is>
       </c>
       <c r="L61" s="4" t="inlineStr"/>
@@ -7849,17 +7849,17 @@
         <v>45440</v>
       </c>
       <c r="H62" s="5" t="n">
-        <v>21204.58</v>
+        <v>19116.18</v>
       </c>
       <c r="I62" s="5" t="n">
-        <v>42409.16</v>
+        <v>38232.36</v>
       </c>
       <c r="J62" s="8" t="n">
-        <v>0.06669982394366192</v>
+        <v>0.158618838028169</v>
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>[ОЦЕНКА] цена с НДС = НМЦ×1,22×0.85 (публичной цены нет; краны ЗАРД/ЗАРДП Ярдос (РФ) — у дилеров «цена договорная» (petr</t>
+          <t>КП Ярдос: ЗАРД 040.016.21-01Р DN40 PN16</t>
         </is>
       </c>
       <c r="L62" s="4" t="inlineStr"/>
@@ -7893,17 +7893,17 @@
         <v>22000</v>
       </c>
       <c r="H63" s="5" t="n">
-        <v>10266.3</v>
+        <v>8824.26</v>
       </c>
       <c r="I63" s="5" t="n">
-        <v>20532.6</v>
+        <v>17648.52</v>
       </c>
       <c r="J63" s="8" t="n">
-        <v>0.06670000000000009</v>
+        <v>0.1977945454545454</v>
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>[ОЦЕНКА] цена с НДС = НМЦ×1,22×0.85 (публичной цены нет; краны ЗАРД/ЗАРДП Ярдос (РФ) — у дилеров «цена договорная» (petr</t>
+          <t>КП Ярдос: ЗАРД 020.016.21-01Р DN20 PN16</t>
         </is>
       </c>
       <c r="L63" s="4" t="inlineStr"/>
@@ -7937,17 +7937,17 @@
         <v>58000</v>
       </c>
       <c r="H64" s="5" t="n">
-        <v>27065.7</v>
+        <v>24979.5</v>
       </c>
       <c r="I64" s="5" t="n">
-        <v>54131.4</v>
+        <v>49959</v>
       </c>
       <c r="J64" s="8" t="n">
-        <v>0.06669999999999998</v>
+        <v>0.1386379310344827</v>
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>[ОЦЕНКА] цена с НДС = НМЦ×1,22×0.85 (публичной цены нет; краны ЗАРД/ЗАРДП Ярдос (РФ) — у дилеров «цена договорная» (petr</t>
+          <t>КП Ярдос: ЗАРДП 025.160.23-02Р DN25 PN160</t>
         </is>
       </c>
       <c r="L64" s="4" t="inlineStr"/>
@@ -8649,17 +8649,17 @@
         <v>114000</v>
       </c>
       <c r="H80" s="5" t="n">
-        <v>17732.7</v>
+        <v>15933.2</v>
       </c>
       <c r="I80" s="5" t="n">
-        <v>106396.2</v>
+        <v>95599.20000000001</v>
       </c>
       <c r="J80" s="8" t="n">
-        <v>0.06669999999999998</v>
+        <v>0.1614105263157894</v>
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>[ОЦЕНКА] цена с НДС = НМЦ×1,22×0.85 (публичной цены нет; КШ250.8Д1-Н23Б1ГН (манометрический) — производитель не установл</t>
+          <t>КП Гималаи: Кран шаровой манометрический КШ250.8Д1-Н23Б1ГН с приварным сбросным клапаном, PN25 МПа, DN8, нерж., AISI316</t>
         </is>
       </c>
       <c r="L80" s="4" t="inlineStr"/>

--- a/SAKHALIN_11201_11202.xlsx
+++ b/SAKHALIN_11201_11202.xlsx
@@ -6721,17 +6721,17 @@
         <v>27540</v>
       </c>
       <c r="H37" s="5" t="n">
-        <v>7262.24</v>
+        <v>7789.24</v>
       </c>
       <c r="I37" s="5" t="n">
-        <v>21786.72</v>
+        <v>23367.72</v>
       </c>
       <c r="J37" s="8" t="n">
-        <v>0.2089063180827887</v>
+        <v>0.1514989106753812</v>
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>прайс АДЛ BD01I12792 ЗПВС-FL(W)-3-100-MN-E = 67,7 у.е. × 119,19</t>
+          <t>КП АДЛ УТД000114530 от 30.10.2026: ГРАНВЭЛ ЗПВС FL(w)-3-100-MN-Е Ду100</t>
         </is>
       </c>
       <c r="L37" s="4" t="inlineStr"/>
@@ -6765,17 +6765,17 @@
         <v>69250</v>
       </c>
       <c r="H38" s="5" t="n">
-        <v>10952.37</v>
+        <v>11747.14</v>
       </c>
       <c r="I38" s="5" t="n">
-        <v>54761.85000000001</v>
+        <v>58735.7</v>
       </c>
       <c r="J38" s="8" t="n">
-        <v>0.2092151624548736</v>
+        <v>0.151831046931408</v>
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>прайс АДЛ BD01I12795 ЗПВС-FL(W)-3-150-MN-E = 102,1 у.е. × 119,19</t>
+          <t>КП АДЛ УТД000114530 от 30.10.2026: ГРАНВЭЛ ЗПВС FL(w)-3-150-MN-Е Ду150</t>
         </is>
       </c>
       <c r="L38" s="4" t="inlineStr"/>
@@ -6941,17 +6941,17 @@
         <v>119490</v>
       </c>
       <c r="H42" s="5" t="n">
-        <v>27762.38</v>
+        <v>37289.39</v>
       </c>
       <c r="I42" s="5" t="n">
-        <v>83287.14</v>
-      </c>
-      <c r="J42" s="9" t="n">
-        <v>0.3029781571679638</v>
+        <v>111868.17</v>
+      </c>
+      <c r="J42" s="8" t="n">
+        <v>0.06378634195330157</v>
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>dn.ru, Benarmo обратный шаровой Ду150 Ру16 чугун/сталь NBR, на 30.10.2026</t>
+          <t>КП АДЛ УТД000114530 от 30.10.2026: ГРАНЛОК клапан обратный шаровой RD12.02.150.16.Ф/Ф DN150, Tмакс 70°С</t>
         </is>
       </c>
       <c r="L42" s="4" t="inlineStr"/>
@@ -6985,17 +6985,17 @@
         <v>56760</v>
       </c>
       <c r="H43" s="5" t="n">
-        <v>13974.25</v>
+        <v>19260.24</v>
       </c>
       <c r="I43" s="5" t="n">
-        <v>41922.75</v>
-      </c>
-      <c r="J43" s="9" t="n">
-        <v>0.2614032769556025</v>
+        <v>57780.72</v>
+      </c>
+      <c r="J43" s="10" t="n">
+        <v>-0.0179830866807611</v>
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>dn.ru, Benarmo обратный шаровой Ду100 Ру16, на 30.10.2026</t>
+          <t>КП АДЛ УТД000114530 от 30.10.2026: ГРАНЛОК клапан обратный шаровой RD12.02.100.16.Ф/Ф DN100, Tмакс 70°С</t>
         </is>
       </c>
       <c r="L43" s="4" t="inlineStr"/>
